--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.76</v>
+        <v>2.12</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,37 +1131,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.2</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>1.65</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>2.06</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.94</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,54 +1713,54 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.32</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>3.85</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="K10" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.24</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.89</v>
+        <v>2.84</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.27</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
         <v>7.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.44</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>2.72</v>
+        <v>1.89</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>2.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4</v>
+        <v>1.73</v>
       </c>
       <c r="H16" t="n">
-        <v>2.02</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>1.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.47</v>
       </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="G20" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>2.22</v>
       </c>
       <c r="J20" t="n">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 00:50:14</t>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,1154 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.86</v>
+        <v>2.44</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="J21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.25</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
         <v>7</v>
       </c>
-      <c r="AC21" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT21" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.9</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-11 03:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-11 03:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tondela</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-11 03:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-11 03:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-11 03:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
         <v>18</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AW26" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AX26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AY26" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="AZ26" t="n">
         <v>21</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BA26" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB26" t="n">
         <v>19</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BC26" t="n">
         <v>21</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BD26" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BE26" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BF26" t="n">
         <v>16</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BG26" t="n">
         <v>8.4</v>
       </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-04-11 00:50:14</t>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-11 03:22:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
@@ -766,7 +766,7 @@
         <v>2.22</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
         <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I7" t="n">
         <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
         <v>7.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
         <v>7.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>1.73</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -3488,7 +3488,7 @@
         <v>1.09</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.39</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G20" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H20" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="I20" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
         <v>2.48</v>
@@ -4560,7 +4560,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>1.66</v>
       </c>
       <c r="G22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I22" t="n">
         <v>5.8</v>
@@ -4715,13 +4715,13 @@
         <v>75</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
         <v>9.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
         <v>70</v>
@@ -4730,7 +4730,7 @@
         <v>16.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4754,10 +4754,10 @@
         <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
         <v>9</v>
@@ -4775,10 +4775,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
         <v>15.5</v>
@@ -4796,11 +4796,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG22" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
         <v>3.45</v>
@@ -5076,7 +5076,7 @@
         <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
         <v>2.78</v>
@@ -5443,16 +5443,16 @@
         <v>1.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
         <v>2.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
         <v>2.14</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-11 03:22:30</t>
+          <t>2026-04-11 05:54:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,37 +1131,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.2</v>
       </c>
-      <c r="G4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,54 +1325,54 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.32</v>
       </c>
-      <c r="H5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,33 +1907,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="H8" t="n">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,50 +2300,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.32</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.76</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="H14" t="n">
-        <v>2.24</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.3</v>
       </c>
-      <c r="K14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
@@ -3464,55 +3464,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>2.68</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="G18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.15</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="G20" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="I20" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>1.11</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>1.11</v>
       </c>
       <c r="AS21" t="n">
-        <v>55</v>
+        <v>1.11</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>1.11</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>1.11</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>1.11</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>1.11</v>
       </c>
       <c r="AX21" t="n">
-        <v>13.5</v>
+        <v>1.11</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>1.11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>1.11</v>
       </c>
       <c r="BA21" t="n">
-        <v>32</v>
+        <v>1.11</v>
       </c>
       <c r="BB21" t="n">
-        <v>19.5</v>
+        <v>1.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>1.11</v>
       </c>
       <c r="BD21" t="n">
-        <v>27</v>
+        <v>1.11</v>
       </c>
       <c r="BE21" t="n">
-        <v>15</v>
+        <v>1.11</v>
       </c>
       <c r="BF21" t="n">
-        <v>21</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
-        <v>28</v>
+        <v>1.11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68</v>
+        <v>3.85</v>
       </c>
       <c r="H22" t="n">
-        <v>5.7</v>
+        <v>2.96</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,766 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>1.86</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>2.04</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2.28</v>
+        <v>5.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P23" t="n">
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.14</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 05:54:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>16:30:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sarmiento de Junin</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Gimnasia La Plata</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2026-04-11 05:54:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>16:30:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Defensa y Justicia</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Talleres</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-04-11 05:54:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Lanus</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Banfield</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-04-11 05:54:46</t>
+          <t>2026-04-11 08:27:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.2</v>
+        <v>2.72</v>
       </c>
       <c r="G3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="I5" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>1.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.85</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.86</v>
+        <v>1.69</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,11 +2145,11 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.36</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="K12" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.93</v>
+        <v>2.84</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.27</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1.72</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
         <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I17" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="I20" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="I21" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="G22" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="H22" t="n">
-        <v>2.96</v>
+        <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="J22" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.54</v>
+        <v>1.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 08:27:09</t>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,1154 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="G23" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.42</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC23" t="n">
         <v>7</v>
       </c>
-      <c r="AC23" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO23" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT23" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.9</v>
       </c>
       <c r="AU23" t="n">
         <v>6.6</v>
       </c>
       <c r="AV23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-11 10:59:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>18</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="BA24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-11 10:59:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tondela</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-11 10:59:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-11 10:59:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-11 10:59:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC28" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AD28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AY28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="AZ28" t="n">
         <v>21</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BA28" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB28" t="n">
         <v>19</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BC28" t="n">
         <v>21</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BD28" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BE28" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BF28" t="n">
         <v>16</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BG28" t="n">
         <v>8.4</v>
       </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-11 08:27:09</t>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-11 10:59:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>LNZ-Lebedyn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>13</v>
       </c>
-      <c r="Z3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BA3" t="n">
         <v>30</v>
       </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>40</v>
-      </c>
       <c r="BB3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC3" t="n">
         <v>32</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>25</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BG3" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H4" t="n">
         <v>3.05</v>
       </c>
-      <c r="H4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="I4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>1.77</v>
       </c>
       <c r="G5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.18</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.39</v>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beroe Stara Za</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.46</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="K8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>4.7</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.69</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>3.35</v>
       </c>
       <c r="G10" t="n">
-        <v>2.94</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="G12" t="n">
-        <v>3.85</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>2.48</v>
+        <v>5.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.84</v>
+        <v>1.43</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>1.67</v>
       </c>
       <c r="J13" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>1.86</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>2.34</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="H17" t="n">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
-        <v>1.95</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>1.69</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>2.04</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
         <v>1.01</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,11 +4473,11 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,36 +4623,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9</v>
+        <v>2.74</v>
       </c>
       <c r="I22" t="n">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.42</v>
+        <v>1.69</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>1.93</v>
       </c>
       <c r="I23" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>2.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,66 +5011,66 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67</v>
+        <v>2.84</v>
       </c>
       <c r="H24" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,123 +5079,123 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I25" t="n">
         <v>4.2</v>
       </c>
-      <c r="G25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.16</v>
-      </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H26" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="J26" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,378 +5593,2512 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="G27" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="H27" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="K27" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-11 10:59:24</t>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Universitatea Cluj</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Benevento</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cavese 1919</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Renate</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pro Vercelli</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ESTAC Troyes</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tondela</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Banfield</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G39" t="n">
         <v>1.98</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H39" t="n">
         <v>4.9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I39" t="n">
         <v>5.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J39" t="n">
         <v>3.35</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K39" t="n">
         <v>3.55</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
         <v>1.11</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N39" t="n">
         <v>2.68</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="O39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.21</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S39" t="n">
         <v>4.8</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T39" t="n">
         <v>2.14</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U39" t="n">
         <v>1.74</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V39" t="n">
         <v>1.22</v>
       </c>
-      <c r="W28" t="n">
+      <c r="W39" t="n">
         <v>2.02</v>
       </c>
-      <c r="X28" t="n">
+      <c r="X39" t="n">
         <v>10</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y39" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="Z39" t="n">
         <v>42</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AA39" t="n">
         <v>180</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AB39" t="n">
         <v>7</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AC39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AD39" t="n">
         <v>23</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AE39" t="n">
         <v>110</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AF39" t="n">
         <v>11</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AG39" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AH39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK39" t="n">
         <v>27</v>
       </c>
-      <c r="AI28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL28" t="n">
+      <c r="AL39" t="n">
         <v>60</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AM39" t="n">
         <v>230</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AN39" t="n">
         <v>22</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AO39" t="n">
         <v>180</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AP39" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AQ39" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AR39" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AS39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW39" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX28" t="n">
+      <c r="AX39" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="AY39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="AZ39" t="n">
         <v>21</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BA39" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BB39" t="n">
         <v>19</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BC39" t="n">
         <v>21</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BD39" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BE39" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BF39" t="n">
         <v>16</v>
       </c>
-      <c r="BG28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-04-11 10:59:24</t>
+      <c r="BG39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-11 13:31:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="H2" t="n">
         <v>1.75</v>
@@ -769,13 +769,13 @@
         <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
@@ -784,7 +784,7 @@
         <v>2.74</v>
       </c>
       <c r="O2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
         <v>1.59</v>
@@ -808,7 +808,7 @@
         <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
         <v>2.22</v>
@@ -978,7 +978,7 @@
         <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
         <v>1.81</v>
@@ -990,7 +990,7 @@
         <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
         <v>1.67</v>
@@ -1002,7 +1002,7 @@
         <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1059,7 +1059,7 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>7</v>
@@ -1068,16 +1068,16 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>19</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>48</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>75</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BG3" t="n">
         <v>15.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.15</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,19 +1169,19 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4.1</v>
@@ -1190,13 +1190,13 @@
         <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>12</v>
@@ -1205,16 +1205,16 @@
         <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
         <v>17.5</v>
@@ -1223,13 +1223,13 @@
         <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
@@ -1244,71 +1244,71 @@
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO4" t="n">
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -1363,10 +1363,10 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
         <v>2.18</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -1557,10 +1557,10 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.24</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
         <v>3.85</v>
@@ -1742,16 +1742,16 @@
         <v>2.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1766,19 +1766,19 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
         <v>10</v>
@@ -1844,19 +1844,19 @@
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
         <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>42</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -1865,32 +1865,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>60</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>46</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>130</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>55</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -1924,22 +1924,22 @@
         <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
         <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
@@ -1948,7 +1948,7 @@
         <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
         <v>1.39</v>
@@ -1963,19 +1963,19 @@
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W8" t="n">
         <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
         <v>7.4</v>
@@ -2029,7 +2029,7 @@
         <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.7</v>
@@ -2038,22 +2038,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
         <v>9.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>27</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
         <v>15.5</v>
@@ -2062,29 +2062,29 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>55</v>
+        <v>4.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>95</v>
+        <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>70</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>95</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>90</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>120</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
@@ -2130,7 +2130,7 @@
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,40 +2139,40 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
         <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
@@ -2181,7 +2181,7 @@
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2199,10 +2199,10 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
         <v>30</v>
@@ -2214,71 +2214,71 @@
         <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>95</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>50</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>60</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>85</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="I10" t="n">
         <v>2.46</v>
       </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2336,7 +2336,7 @@
         <v>1.59</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.59</v>
@@ -2345,10 +2345,10 @@
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eyupspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.4</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>4.7</v>
+        <v>1.86</v>
       </c>
       <c r="H11" t="n">
-        <v>1.99</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>1.21</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>1.99</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7.8</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>1.29</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.43</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="I14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.36</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.84</v>
+        <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>4.3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="J15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>2.54</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I19" t="n">
         <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>980</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
         <v>2.3</v>
@@ -4267,16 +4267,16 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
         <v>2.3</v>
@@ -4285,141 +4285,141 @@
         <v>1.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J21" t="n">
         <v>2.42</v>
       </c>
-      <c r="G21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.3</v>
-      </c>
       <c r="K21" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.54</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="G22" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="H22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I22" t="n">
         <v>2.74</v>
       </c>
-      <c r="I22" t="n">
-        <v>4.1</v>
-      </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.84</v>
       </c>
       <c r="H23" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J23" t="n">
-        <v>1.95</v>
+        <v>2.92</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2.92</v>
+        <v>1.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="H24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I24" t="n">
         <v>3.1</v>
       </c>
-      <c r="I24" t="n">
-        <v>3.65</v>
-      </c>
       <c r="J24" t="n">
-        <v>2.9</v>
+        <v>1.47</v>
       </c>
       <c r="K24" t="n">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="H25" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.32</v>
+        <v>1.43</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="I26" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P26" t="n">
-        <v>1.76</v>
+        <v>2.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="H27" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J28" t="n">
         <v>2.78</v>
       </c>
-      <c r="G28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.62</v>
-      </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P28" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>2.76</v>
       </c>
       <c r="G29" t="n">
-        <v>1.71</v>
+        <v>3.1</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>2.76</v>
       </c>
       <c r="I29" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="K29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
         <v>4.8</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.76</v>
+        <v>1.33</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="H31" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="J31" t="n">
-        <v>2.98</v>
+        <v>1.54</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="P31" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR31" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS31" t="n">
         <v>36</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX31" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
         <v>42</v>
       </c>
       <c r="BB31" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD31" t="n">
         <v>36</v>
       </c>
-      <c r="BC31" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>42</v>
-      </c>
       <c r="BE31" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BF31" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>2.02</v>
       </c>
       <c r="I32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.65</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>3.65</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K33" t="n">
         <v>3.25</v>
@@ -6801,7 +6801,7 @@
         <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q33" t="n">
         <v>2.24</v>
@@ -6813,28 +6813,28 @@
         <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U33" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W33" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y33" t="n">
         <v>11.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA33" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB33" t="n">
         <v>8.800000000000001</v>
@@ -6843,16 +6843,16 @@
         <v>7</v>
       </c>
       <c r="AD33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF33" t="n">
         <v>15</v>
       </c>
-      <c r="AE33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>16</v>
-      </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
         <v>19</v>
@@ -6861,22 +6861,22 @@
         <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
         <v>48</v>
       </c>
       <c r="AM33" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
         <v>26</v>
       </c>
       <c r="AO33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP33" t="n">
         <v>9.800000000000001</v>
@@ -6888,10 +6888,10 @@
         <v>20</v>
       </c>
       <c r="AS33" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU33" t="n">
         <v>6.6</v>
@@ -6900,7 +6900,7 @@
         <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6909,32 +6909,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
         <v>32</v>
       </c>
       <c r="BB33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BD33" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BF33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG33" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G34" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J34" t="n">
         <v>4.4</v>
@@ -6995,7 +6995,7 @@
         <v>1.26</v>
       </c>
       <c r="P34" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
         <v>1.79</v>
@@ -7070,7 +7070,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO34" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AP34" t="n">
         <v>17.5</v>
@@ -7097,13 +7097,13 @@
         <v>55</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA34" t="n">
         <v>50</v>
@@ -7118,7 +7118,7 @@
         <v>27</v>
       </c>
       <c r="BE34" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF34" t="n">
         <v>8</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
         <v>2.86</v>
       </c>
       <c r="H35" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
         <v>3.1</v>
@@ -7195,7 +7195,7 @@
         <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -7300,7 +7300,7 @@
         <v>21</v>
       </c>
       <c r="BA35" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BB35" t="n">
         <v>42</v>
@@ -7309,10 +7309,10 @@
         <v>24</v>
       </c>
       <c r="BD35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF35" t="n">
         <v>27</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G36" t="n">
         <v>4.7</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -7538,28 +7538,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="H37" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="K37" t="n">
         <v>3.1</v>
@@ -7568,149 +7568,149 @@
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="O37" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="P37" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S37" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="X37" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -7732,28 +7732,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="G38" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="H38" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J38" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="K38" t="n">
         <v>3.1</v>
@@ -7762,149 +7762,149 @@
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P38" t="n">
         <v>1.47</v>
       </c>
-      <c r="P38" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Q38" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="R38" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE38" t="n">
         <v>4.8</v>
       </c>
-      <c r="T38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>1.87</v>
       </c>
       <c r="G39" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>4.9</v>
@@ -7947,7 +7947,7 @@
         <v>5.5</v>
       </c>
       <c r="J39" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K39" t="n">
         <v>3.55</v>
@@ -7959,13 +7959,13 @@
         <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="O39" t="n">
         <v>1.5</v>
       </c>
       <c r="P39" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q39" t="n">
         <v>2.44</v>
@@ -7986,7 +7986,7 @@
         <v>1.22</v>
       </c>
       <c r="W39" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
         <v>14.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA39" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB39" t="n">
         <v>7</v>
@@ -8040,7 +8040,7 @@
         <v>22</v>
       </c>
       <c r="AO39" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP39" t="n">
         <v>8.6</v>
@@ -8052,7 +8052,7 @@
         <v>7.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT39" t="n">
         <v>5.9</v>
@@ -8076,7 +8076,7 @@
         <v>21</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB39" t="n">
         <v>19</v>
@@ -8085,20 +8085,214 @@
         <v>21</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF39" t="n">
         <v>16</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-11 13:31:25</t>
+          <t>2026-04-11 16:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-11 16:03:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH40"/>
+  <dimension ref="A1:BH43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.75</v>
@@ -808,7 +808,7 @@
         <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
         <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -993,16 +993,16 @@
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
         <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1059,22 +1059,22 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.85</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
         <v>9.800000000000001</v>
@@ -1089,16 +1089,16 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
         <v>3.55</v>
@@ -1196,25 +1196,25 @@
         <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y4" t="n">
         <v>12</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
         <v>17.5</v>
@@ -1226,31 +1226,31 @@
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
         <v>8.199999999999999</v>
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1.22</v>
@@ -1378,7 +1378,7 @@
         <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
         <v>1.61</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
         <v>3.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -1924,25 +1924,25 @@
         <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="n">
         <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
         <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N8" t="n">
         <v>2.2</v>
@@ -1954,13 +1954,13 @@
         <v>1.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
         <v>1.13</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.36</v>
@@ -1969,13 +1969,13 @@
         <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W8" t="n">
         <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y8" t="n">
         <v>7.4</v>
@@ -2029,10 +2029,10 @@
         <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
         <v>8.800000000000001</v>
@@ -2041,50 +2041,50 @@
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
         <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
         <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2148,19 +2148,19 @@
         <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.86</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.74</v>
       </c>
       <c r="V9" t="n">
         <v>1.27</v>
@@ -2169,10 +2169,10 @@
         <v>1.88</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
@@ -2181,7 +2181,7 @@
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2223,40 +2223,40 @@
         <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
         <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2265,20 +2265,20 @@
         <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
         <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -2527,28 +2527,28 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>1.21</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
@@ -2557,116 +2557,116 @@
         <v>2.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS11" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>34</v>
       </c>
       <c r="BB11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE11" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB12" t="n">
         <v>8.199999999999999</v>
@@ -2847,7 +2847,7 @@
         <v>40</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
         <v>8.199999999999999</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
         <v>1.13</v>
@@ -2924,7 +2924,7 @@
         <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.59</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -3085,34 +3085,34 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
         <v>2.26</v>
@@ -3121,22 +3121,22 @@
         <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>2.04</v>
@@ -3294,31 +3294,31 @@
         <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3330,52 +3330,52 @@
         <v>1.87</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>2.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>1.95</v>
       </c>
       <c r="AR15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>19</v>
+        <v>2.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>2.04</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>16.5</v>
+        <v>2.08</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>2.12</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>2.04</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>2.04</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>2.14</v>
       </c>
       <c r="BB15" t="n">
-        <v>44</v>
+        <v>2.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>29</v>
+        <v>2.16</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>2.16</v>
       </c>
       <c r="BE15" t="n">
-        <v>48</v>
+        <v>2.24</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,19 +3497,19 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O16" t="n">
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
         <v>2.08</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
         <v>1.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
         <v>1.64</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.36</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
         <v>2.86</v>
@@ -3885,16 +3885,16 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
@@ -3903,16 +3903,16 @@
         <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
         <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -3921,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
         <v>60</v>
@@ -3936,13 +3936,13 @@
         <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
         <v>20</v>
@@ -3957,7 +3957,7 @@
         <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>100</v>
@@ -3978,7 +3978,7 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT18" t="n">
         <v>9.800000000000001</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
         <v>14</v>
@@ -4002,19 +4002,19 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="G19" t="n">
         <v>2.46</v>
       </c>
       <c r="H19" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>980</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.2</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.68</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE19" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC19" t="n">
+      <c r="BF19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>17</v>
       </c>
-      <c r="BD19" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -4264,10 +4264,10 @@
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>1.09</v>
       </c>
       <c r="G21" t="n">
         <v>3.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>2.42</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="L21" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
@@ -4494,7 +4494,7 @@
         <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4551,52 +4551,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
         <v>1.76</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -4849,13 +4849,13 @@
         <v>3.35</v>
       </c>
       <c r="L23" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.49</v>
@@ -4867,10 +4867,10 @@
         <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4885,7 +4885,7 @@
         <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
         <v>13</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="AR23" t="n">
         <v>14</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AV23" t="n">
         <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.74</v>
+        <v>2.26</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="BB23" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -5016,55 +5016,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="H24" t="n">
-        <v>1.17</v>
+        <v>2.74</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>6.6</v>
+        <v>110</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="O24" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5133,52 +5133,52 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -5210,55 +5210,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>2.18</v>
       </c>
       <c r="G25" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="H25" t="n">
-        <v>2.74</v>
+        <v>2.02</v>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="K25" t="n">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -5413,58 +5413,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="H26" t="n">
-        <v>1.93</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.07</v>
       </c>
       <c r="P26" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5521,52 +5521,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G27" t="n">
         <v>1.72</v>
@@ -5622,7 +5622,7 @@
         <v>3.95</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.39</v>
@@ -5646,7 +5646,7 @@
         <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
         <v>1.89</v>
@@ -5658,49 +5658,49 @@
         <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
         <v>200</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>110</v>
       </c>
       <c r="AF27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>100</v>
       </c>
       <c r="AJ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK27" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>21</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5709,7 +5709,7 @@
         <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO27" t="n">
         <v>130</v>
@@ -5718,13 +5718,13 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
         <v>36</v>
       </c>
       <c r="AS27" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
         <v>7.8</v>
@@ -5760,17 +5760,17 @@
         <v>27</v>
       </c>
       <c r="BE27" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
@@ -5840,7 +5840,7 @@
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -6207,10 +6207,10 @@
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
         <v>1.54</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -6383,177 +6383,177 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.33</v>
+        <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="H31" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="I31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.45</v>
       </c>
-      <c r="J31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="K31" t="n">
-        <v>950</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.25</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR31" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG31" t="n">
         <v>36</v>
       </c>
-      <c r="AT31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="G32" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>3.65</v>
       </c>
       <c r="J32" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="G33" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="H33" t="n">
-        <v>3.55</v>
+        <v>2.02</v>
       </c>
       <c r="I33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J33" t="n">
         <v>3.65</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K33" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="T33" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="U33" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="W33" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC33" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AD33" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW33" t="n">
         <v>7</v>
       </c>
-      <c r="AD33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>40</v>
-      </c>
       <c r="AX33" t="n">
-        <v>13.5</v>
+        <v>2.72</v>
       </c>
       <c r="AY33" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ33" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>32</v>
+        <v>2.74</v>
       </c>
       <c r="BB33" t="n">
-        <v>30</v>
+        <v>2.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="BD33" t="n">
-        <v>42</v>
+        <v>2.7</v>
       </c>
       <c r="BE33" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="BF33" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>44</v>
+        <v>9.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.66</v>
+        <v>2.84</v>
       </c>
       <c r="G34" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="H34" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="I34" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="O34" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="R34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.47</v>
       </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="Y34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>22</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="BA34" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF34" t="n">
         <v>46</v>
       </c>
-      <c r="AA34" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA34" t="n">
+      <c r="BG34" t="n">
         <v>50</v>
       </c>
-      <c r="BB34" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>65</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,179 +7150,179 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.84</v>
+        <v>1.66</v>
       </c>
       <c r="G35" t="n">
-        <v>2.86</v>
+        <v>1.67</v>
       </c>
       <c r="H35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S35" t="n">
         <v>3</v>
       </c>
-      <c r="I35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6</v>
-      </c>
       <c r="T35" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="U35" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X35" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF35" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD35" t="n">
+      <c r="BG35" t="n">
         <v>34</v>
       </c>
-      <c r="BE35" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>29</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G36" t="n">
         <v>4.7</v>
@@ -7371,152 +7371,152 @@
         <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
         <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R37" t="n">
         <v>1.14</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>3.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M38" t="n">
         <v>1.15</v>
@@ -7792,7 +7792,7 @@
         <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X38" t="n">
         <v>7.8</v>
@@ -7888,7 +7888,7 @@
         <v>4.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD38" t="n">
         <v>4.6</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,378 +7921,960 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="H39" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="I39" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>1.57</v>
       </c>
       <c r="O39" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="P39" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S39" t="n">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="T39" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="X39" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-11 16:03:33</t>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-11 18:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-04-11 18:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Penarol</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Liverpool Montevideo</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F42" t="n">
         <v>1.56</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G42" t="n">
         <v>1.9</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H42" t="n">
         <v>2.16</v>
       </c>
-      <c r="I40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="I42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J42" t="n">
         <v>2.18</v>
       </c>
-      <c r="K40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="K42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q42" t="n">
         <v>2.08</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="inlineStr">
-        <is>
-          <t>2026-04-11 16:03:33</t>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-04-11 18:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20:05:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-04-11 18:33:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
         <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -993,16 +993,16 @@
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1077,7 +1077,7 @@
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
         <v>19</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
         <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1256,13 +1256,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
         <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
         <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>4.9</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.52</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
@@ -1551,16 +1551,16 @@
         <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
         <v>2.24</v>
@@ -1569,16 +1569,16 @@
         <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
         <v>1.1</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>180</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -1936,13 +1936,13 @@
         <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
         <v>2.2</v>
@@ -1954,7 +1954,7 @@
         <v>1.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>1.13</v>
@@ -1963,7 +1963,7 @@
         <v>6.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
         <v>1.59</v>
@@ -1972,10 +1972,10 @@
         <v>1.72</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
         <v>7.4</v>
@@ -2050,7 +2050,7 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
         <v>4</v>
@@ -2059,32 +2059,32 @@
         <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB8" t="n">
         <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
         <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2142,7 +2142,7 @@
         <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
         <v>1.66</v>
@@ -2163,10 +2163,10 @@
         <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="I10" t="n">
         <v>2.46</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
         <v>2.28</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
         <v>2.12</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>4.4</v>
       </c>
       <c r="G12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H12" t="n">
         <v>1.99</v>
@@ -2709,7 +2709,7 @@
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
@@ -2739,10 +2739,10 @@
         <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
@@ -2778,7 +2778,7 @@
         <v>36</v>
       </c>
       <c r="AG12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
@@ -2787,13 +2787,13 @@
         <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL12" t="n">
         <v>70</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>75</v>
       </c>
       <c r="AM12" t="n">
         <v>140</v>
@@ -2829,7 +2829,7 @@
         <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
         <v>15.5</v>
@@ -2838,29 +2838,29 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
         <v>40</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF12" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>11.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -2915,16 +2915,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
         <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>1.59</v>
+        <v>2.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
         <v>1.59</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>1.63</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
         <v>5.7</v>
@@ -3121,7 +3121,7 @@
         <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
         <v>2.46</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
@@ -3318,7 +3318,7 @@
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,16 +3497,16 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
         <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.09</v>
+        <v>2.54</v>
       </c>
       <c r="G21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.3</v>
       </c>
-      <c r="H21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K21" t="n">
-        <v>110</v>
-      </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>1.45</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
         <v>1.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>2.38</v>
       </c>
       <c r="I22" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -4661,22 +4661,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="O22" t="n">
         <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,7 +4685,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
         <v>1.43</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="G24" t="n">
         <v>2.54</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="G25" t="n">
         <v>3.4</v>
       </c>
       <c r="H25" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="I25" t="n">
         <v>3.1</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="T26" t="n">
         <v>1.36</v>
@@ -5461,7 +5461,7 @@
         <v>2.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
         <v>2.02</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -5718,13 +5718,13 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX27" t="n">
         <v>7.8</v>
@@ -5748,7 +5748,7 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>60</v>
+        <v>7.4</v>
       </c>
       <c r="BB27" t="n">
         <v>12.5</v>
@@ -5757,20 +5757,20 @@
         <v>13.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF27" t="n">
         <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
         <v>2.76</v>
@@ -5816,7 +5816,7 @@
         <v>2.78</v>
       </c>
       <c r="K28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5852,7 +5852,7 @@
         <v>1.27</v>
       </c>
       <c r="W28" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -6049,10 +6049,10 @@
         <v>1.47</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y29" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>23</v>
@@ -6061,22 +6061,22 @@
         <v>65</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
         <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE29" t="n">
         <v>50</v>
       </c>
       <c r="AF29" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH29" t="n">
         <v>25</v>
@@ -6109,10 +6109,10 @@
         <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
         <v>6.8</v>
@@ -6124,41 +6124,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -6297,52 +6297,52 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H31" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I31" t="n">
         <v>3.35</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K31" t="n">
         <v>3.45</v>
@@ -6482,7 +6482,7 @@
         <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN31" t="n">
         <v>34</v>
@@ -6527,10 +6527,10 @@
         <v>7.4</v>
       </c>
       <c r="BB31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC31" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.6</v>
       </c>
       <c r="BD31" t="n">
         <v>7.2</v>
@@ -6539,14 +6539,14 @@
         <v>8</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG31" t="n">
         <v>36</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>3.55</v>
       </c>
       <c r="I32" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>3.2</v>
@@ -6595,13 +6595,13 @@
         <v>3.25</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.42</v>
@@ -6610,7 +6610,7 @@
         <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
         <v>1.28</v>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB32" t="n">
         <v>30</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -6822,28 +6822,28 @@
         <v>1.84</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X33" t="n">
         <v>20</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA33" t="n">
         <v>27</v>
       </c>
       <c r="AB33" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
         <v>10.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
         <v>22</v>
@@ -6852,10 +6852,10 @@
         <v>29</v>
       </c>
       <c r="AG33" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI33" t="n">
         <v>32</v>
@@ -6876,7 +6876,7 @@
         <v>34</v>
       </c>
       <c r="AO33" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AP33" t="n">
         <v>6.6</v>
@@ -6888,7 +6888,7 @@
         <v>6</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AT33" t="n">
         <v>6.4</v>
@@ -6903,7 +6903,7 @@
         <v>7</v>
       </c>
       <c r="AX33" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AY33" t="n">
         <v>6.2</v>
@@ -6912,16 +6912,16 @@
         <v>6.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BB33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BC33" t="n">
         <v>3</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BE33" t="n">
         <v>9</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G34" t="n">
         <v>2.84</v>
       </c>
-      <c r="G34" t="n">
-        <v>2.88</v>
-      </c>
       <c r="H34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
         <v>3.05</v>
@@ -6983,13 +6983,13 @@
         <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M34" t="n">
         <v>1.14</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.61</v>
@@ -6998,25 +6998,25 @@
         <v>1.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R34" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T34" t="n">
         <v>2.24</v>
       </c>
       <c r="U34" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V34" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
         <v>7.8</v>
@@ -7028,19 +7028,19 @@
         <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC34" t="n">
         <v>6.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE34" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF34" t="n">
         <v>16</v>
@@ -7085,19 +7085,19 @@
         <v>50</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY34" t="n">
         <v>12.5</v>
@@ -7106,7 +7106,7 @@
         <v>22</v>
       </c>
       <c r="BA34" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="BB34" t="n">
         <v>42</v>
@@ -7115,20 +7115,20 @@
         <v>38</v>
       </c>
       <c r="BD34" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BE34" t="n">
         <v>48</v>
       </c>
       <c r="BF34" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="BG34" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G35" t="n">
         <v>1.67</v>
@@ -7222,10 +7222,10 @@
         <v>46</v>
       </c>
       <c r="AA35" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC35" t="n">
         <v>9.4</v>
@@ -7246,7 +7246,7 @@
         <v>19</v>
       </c>
       <c r="AI35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ35" t="n">
         <v>16</v>
@@ -7279,7 +7279,7 @@
         <v>70</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU35" t="n">
         <v>9</v>
@@ -7288,7 +7288,7 @@
         <v>20</v>
       </c>
       <c r="AW35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX35" t="n">
         <v>9.6</v>
@@ -7312,17 +7312,17 @@
         <v>27</v>
       </c>
       <c r="BE35" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BF35" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -7395,10 +7395,10 @@
         <v>4.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="V36" t="n">
         <v>1.86</v>
@@ -7410,34 +7410,34 @@
         <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AB36" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF36" t="n">
         <v>32</v>
       </c>
       <c r="AG36" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AH36" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI36" t="n">
         <v>50</v>
@@ -7446,7 +7446,7 @@
         <v>140</v>
       </c>
       <c r="AK36" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AL36" t="n">
         <v>100</v>
@@ -7458,19 +7458,19 @@
         <v>120</v>
       </c>
       <c r="AO36" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AP36" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ36" t="n">
         <v>6.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AT36" t="n">
         <v>11</v>
@@ -7479,44 +7479,44 @@
         <v>6.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.6</v>
+        <v>3.45</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AX36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY36" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BD36" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BG36" t="n">
         <v>16</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
         <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.58</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
         <v>1.14</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
         <v>1.57</v>
       </c>
       <c r="O39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P39" t="n">
         <v>1.57</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -8153,22 +8153,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P40" t="n">
         <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S40" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -8523,28 +8523,28 @@
         <v>1.9</v>
       </c>
       <c r="H42" t="n">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>2.18</v>
+        <v>3.25</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P42" t="n">
         <v>1.6</v>
@@ -8553,134 +8553,134 @@
         <v>2.08</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>
@@ -8729,152 +8729,152 @@
         <v>1000</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P43" t="n">
         <v>1.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-11 18:33:42</t>
+          <t>2026-04-11 21:03:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -760,7 +760,7 @@
         <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
         <v>1.75</v>
@@ -808,7 +808,7 @@
         <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -832,7 +832,7 @@
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
         <v>55</v>
@@ -856,13 +856,13 @@
         <v>140</v>
       </c>
       <c r="AM2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
         <v>7.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -978,13 +978,13 @@
         <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
         <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -993,13 +993,13 @@
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
         <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
         <v>1.36</v>
@@ -1023,16 +1023,16 @@
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
         <v>22</v>
@@ -1062,7 +1062,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>10.5</v>
@@ -1071,13 +1071,13 @@
         <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3" t="n">
         <v>19</v>
@@ -1089,16 +1089,16 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
         <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1148,34 @@
         <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
         <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
         <v>2.22</v>
@@ -1193,10 +1193,10 @@
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1205,7 +1205,7 @@
         <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>60</v>
@@ -1235,7 +1235,7 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
         <v>38</v>
@@ -1253,7 +1253,7 @@
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.4</v>
@@ -1262,19 +1262,19 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1283,32 +1283,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
         <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -1351,13 +1351,13 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1366,7 +1366,7 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.18</v>
@@ -1378,7 +1378,7 @@
         <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
         <v>1.61</v>
@@ -1387,7 +1387,7 @@
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
         <v>2.08</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.41</v>
       </c>
       <c r="G6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H6" t="n">
         <v>6.4</v>
@@ -1572,7 +1572,7 @@
         <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.74</v>
@@ -1584,7 +1584,7 @@
         <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1665,7 +1665,7 @@
         <v>80</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY6" t="n">
         <v>7.6</v>
@@ -1674,7 +1674,7 @@
         <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB6" t="n">
         <v>9.4</v>
@@ -1692,11 +1692,11 @@
         <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
         <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
         <v>2.9</v>
@@ -1757,7 +1757,7 @@
         <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
         <v>2.64</v>
@@ -1778,7 +1778,7 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
         <v>10</v>
@@ -1805,10 +1805,10 @@
         <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
         <v>28</v>
@@ -1820,7 +1820,7 @@
         <v>48</v>
       </c>
       <c r="AK7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
         <v>80</v>
@@ -1844,7 +1844,7 @@
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
         <v>5.7</v>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -1865,32 +1865,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
         <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
         <v>2.14</v>
@@ -1936,13 +1936,13 @@
         <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N8" t="n">
         <v>2.2</v>
@@ -1963,7 +1963,7 @@
         <v>6.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
         <v>1.59</v>
@@ -1975,7 +1975,7 @@
         <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y8" t="n">
         <v>7.4</v>
@@ -1999,7 +1999,7 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
         <v>26</v>
@@ -2011,7 +2011,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK8" t="n">
         <v>120</v>
@@ -2065,13 +2065,13 @@
         <v>4.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC8" t="n">
         <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
         <v>4.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2142,13 +2142,13 @@
         <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
         <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2157,10 +2157,10 @@
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
         <v>1.26</v>
@@ -2169,10 +2169,10 @@
         <v>1.89</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
@@ -2181,7 +2181,7 @@
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2223,40 +2223,40 @@
         <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2265,20 +2265,20 @@
         <v>19</v>
       </c>
       <c r="BD9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
         <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -2530,22 +2530,22 @@
         <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
         <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
         <v>2.28</v>
@@ -2554,7 +2554,7 @@
         <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
@@ -2569,7 +2569,7 @@
         <v>100</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
         <v>9.4</v>
@@ -2620,7 +2620,7 @@
         <v>32</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
         <v>25</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
         <v>8.199999999999999</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -2736,13 +2736,13 @@
         <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -3121,10 +3121,10 @@
         <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
         <v>1.76</v>
@@ -3142,10 +3142,10 @@
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3154,10 +3154,10 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3190,65 +3190,65 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -3300,31 +3300,31 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
         <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
         <v>1.87</v>
@@ -3333,116 +3333,116 @@
         <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>15</v>
       </c>
-      <c r="Z15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BA15" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -3497,22 +3497,22 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O16" t="n">
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
         <v>1.23</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -3667,145 +3667,145 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.2</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
         <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>1.01</v>
@@ -3814,7 +3814,7 @@
         <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>1.01</v>
@@ -3823,14 +3823,14 @@
         <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
         <v>1.68</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -4264,10 +4264,10 @@
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
@@ -4288,7 +4288,7 @@
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
         <v>1.59</v>
@@ -4321,19 +4321,19 @@
         <v>10.5</v>
       </c>
       <c r="AD20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG20" t="n">
         <v>14</v>
       </c>
-      <c r="AE20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>16</v>
-      </c>
       <c r="AH20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
         <v>32</v>
@@ -4342,13 +4342,13 @@
         <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL20" t="n">
         <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
         <v>24</v>
@@ -4366,7 +4366,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AT20" t="n">
         <v>14</v>
@@ -4390,19 +4390,19 @@
         <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB20" t="n">
         <v>34</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
         <v>18</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
         <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
         <v>1.85</v>
@@ -4491,16 +4491,16 @@
         <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
         <v>26</v>
@@ -4548,65 +4548,65 @@
         <v>50</v>
       </c>
       <c r="AO21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR21" t="n">
         <v>15.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU21" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>5.4</v>
       </c>
       <c r="AV21" t="n">
         <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
         <v>4</v>
       </c>
-      <c r="BC21" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF21" t="n">
         <v>4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.95</v>
       </c>
       <c r="BG21" t="n">
         <v>4.1</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>2.38</v>
       </c>
       <c r="I22" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -4670,13 +4670,13 @@
         <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -4855,10 +4855,10 @@
         <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P23" t="n">
         <v>1.54</v>
@@ -4867,16 +4867,16 @@
         <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V23" t="n">
         <v>1.37</v>
@@ -4885,49 +4885,49 @@
         <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH23" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AK23" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR23" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.92</v>
+        <v>6.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.88</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>2.24</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.32</v>
+        <v>8</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.32</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H25" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W25" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -5413,46 +5413,46 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
         <v>5.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P26" t="n">
         <v>3.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S26" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="T26" t="n">
         <v>1.36</v>
@@ -5461,122 +5461,122 @@
         <v>2.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
         <v>2.76</v>
@@ -5816,7 +5816,7 @@
         <v>2.78</v>
       </c>
       <c r="K28" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H31" t="n">
         <v>3.15</v>
@@ -6413,10 +6413,10 @@
         <v>1.43</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R31" t="n">
         <v>1.25</v>
@@ -6449,7 +6449,7 @@
         <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC31" t="n">
         <v>7.8</v>
@@ -6500,7 +6500,7 @@
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT31" t="n">
         <v>7.6</v>
@@ -6512,7 +6512,7 @@
         <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6524,29 +6524,29 @@
         <v>17.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC31" t="n">
         <v>7</v>
       </c>
-      <c r="BC31" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD31" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG31" t="n">
         <v>36</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
         <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
         <v>1.68</v>
@@ -6643,7 +6643,7 @@
         <v>65</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC32" t="n">
         <v>7</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>2.02</v>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J33" t="n">
         <v>3.65</v>
@@ -6789,7 +6789,7 @@
         <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
@@ -6810,7 +6810,7 @@
         <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T33" t="n">
         <v>1.57</v>
@@ -6819,7 +6819,7 @@
         <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="W33" t="n">
         <v>1.34</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -7121,14 +7121,14 @@
         <v>48</v>
       </c>
       <c r="BF34" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="BG34" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.65</v>
       </c>
       <c r="G35" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H35" t="n">
         <v>5.8</v>
@@ -7171,10 +7171,10 @@
         <v>5.9</v>
       </c>
       <c r="J35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.35</v>
@@ -7210,7 +7210,7 @@
         <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
@@ -7240,7 +7240,7 @@
         <v>10</v>
       </c>
       <c r="AG35" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AH35" t="n">
         <v>19</v>
@@ -7261,7 +7261,7 @@
         <v>95</v>
       </c>
       <c r="AN35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO35" t="n">
         <v>75</v>
@@ -7270,16 +7270,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS35" t="n">
         <v>70</v>
       </c>
       <c r="AT35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU35" t="n">
         <v>9</v>
@@ -7309,20 +7309,20 @@
         <v>15</v>
       </c>
       <c r="BD35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE35" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="BF35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG35" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>4.7</v>
       </c>
       <c r="H36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I36" t="n">
         <v>2.16</v>
@@ -7395,10 +7395,10 @@
         <v>4.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="V36" t="n">
         <v>1.86</v>
@@ -7422,10 +7422,10 @@
         <v>15.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE36" t="n">
         <v>32</v>
@@ -7443,7 +7443,7 @@
         <v>50</v>
       </c>
       <c r="AJ36" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK36" t="n">
         <v>85</v>
@@ -7458,7 +7458,7 @@
         <v>120</v>
       </c>
       <c r="AO36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP36" t="n">
         <v>9</v>
@@ -7470,7 +7470,7 @@
         <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT36" t="n">
         <v>11</v>
@@ -7479,44 +7479,44 @@
         <v>6.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AW36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC36" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG36" t="n">
         <v>16</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O37" t="n">
         <v>1.01</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
         <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X38" t="n">
         <v>7.8</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="G39" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H39" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>2.96</v>
       </c>
       <c r="K39" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7986,7 +7986,7 @@
         <v>1.23</v>
       </c>
       <c r="W39" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="I40" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J40" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -8153,22 +8153,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="O40" t="n">
         <v>1.02</v>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
         <v>1.13</v>
       </c>
       <c r="S40" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -8177,10 +8177,10 @@
         <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>1.87</v>
       </c>
       <c r="G41" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>4.9</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
         <v>1.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P42" t="n">
         <v>1.6</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>
@@ -8735,10 +8735,10 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P43" t="n">
         <v>1.24</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-11 21:03:25</t>
+          <t>2026-04-11 23:30:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH50"/>
+  <dimension ref="A1:BH51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="G2" t="n">
         <v>7.4</v>
@@ -772,37 +772,37 @@
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
         <v>2.1</v>
@@ -865,25 +865,25 @@
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
@@ -892,10 +892,10 @@
         <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
         <v>3.6</v>
@@ -975,13 +975,13 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
         <v>2.08</v>
@@ -996,7 +996,7 @@
         <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
         <v>1.72</v>
@@ -1005,34 +1005,34 @@
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
         <v>17.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF3" t="n">
         <v>32</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
@@ -1044,22 +1044,22 @@
         <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
         <v>2.76</v>
@@ -1193,19 +1193,19 @@
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
         <v>60</v>
@@ -1220,7 +1220,7 @@
         <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1235,10 +1235,10 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1247,7 +1247,7 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AO4" t="n">
         <v>46</v>
@@ -1262,10 +1262,10 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>5.8</v>
@@ -1274,19 +1274,19 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>7</v>
@@ -1295,20 +1295,20 @@
         <v>6.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1351,7 +1351,7 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.9</v>
@@ -1369,28 +1369,28 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1426,7 +1426,7 @@
         <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>23</v>
@@ -1435,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
         <v>100</v>
@@ -1459,19 +1459,19 @@
         <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
         <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5" t="n">
         <v>8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G7" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H7" t="n">
         <v>6.6</v>
@@ -1766,7 +1766,7 @@
         <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
         <v>1.74</v>
@@ -1778,7 +1778,7 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1865,13 +1865,13 @@
         <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
         <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC7" t="n">
         <v>11</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
@@ -1933,7 +1933,7 @@
         <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
         <v>3.15</v>
@@ -1945,19 +1945,19 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
         <v>2.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
         <v>5.5</v>
@@ -1972,7 +1972,7 @@
         <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
         <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
         <v>75</v>
@@ -2008,7 +2008,7 @@
         <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
         <v>48</v>
@@ -2020,10 +2020,10 @@
         <v>80</v>
       </c>
       <c r="AM8" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO8" t="n">
         <v>100</v>
@@ -2038,10 +2038,10 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2056,16 +2056,16 @@
         <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
         <v>4.1</v>
@@ -2074,17 +2074,17 @@
         <v>4.3</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>2.14</v>
@@ -2127,28 +2127,28 @@
         <v>2.38</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
         <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.13</v>
@@ -2157,16 +2157,16 @@
         <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
         <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
         <v>7.4</v>
@@ -2175,10 +2175,10 @@
         <v>7.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
         <v>12.5</v>
@@ -2190,7 +2190,7 @@
         <v>15.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
         <v>34</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,41 +2244,41 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.5</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
@@ -2342,19 +2342,19 @@
         <v>1.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
         <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
         <v>1.26</v>
@@ -2369,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
         <v>130</v>
@@ -2420,13 +2420,13 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>6.6</v>
@@ -2438,19 +2438,19 @@
         <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
         <v>19.5</v>
@@ -2462,17 +2462,17 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
         <v>4.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
         <v>4.9</v>
@@ -2518,7 +2518,7 @@
         <v>2.86</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H12" t="n">
         <v>2.02</v>
@@ -2748,7 +2748,7 @@
         <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>2.14</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
@@ -3109,13 +3109,13 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
         <v>1.69</v>
@@ -3127,16 +3127,16 @@
         <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
         <v>21</v>
@@ -3148,13 +3148,13 @@
         <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB14" t="n">
         <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>19</v>
@@ -3184,13 +3184,13 @@
         <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP14" t="n">
         <v>17.5</v>
@@ -3202,10 +3202,10 @@
         <v>32</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
         <v>8.4</v>
@@ -3220,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
@@ -3229,7 +3229,7 @@
         <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC14" t="n">
         <v>15.5</v>
@@ -3238,7 +3238,7 @@
         <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
         <v>8.199999999999999</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H15" t="n">
         <v>1.99</v>
@@ -3291,10 +3291,10 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3321,10 +3321,10 @@
         <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
         <v>2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -3476,55 +3476,55 @@
         <v>1.29</v>
       </c>
       <c r="G16" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J16" t="n">
         <v>5.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
         <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3593,7 +3593,7 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
         <v>1.01</v>
@@ -3605,10 +3605,10 @@
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.01</v>
@@ -3617,7 +3617,7 @@
         <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
         <v>1.01</v>
@@ -3629,14 +3629,14 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>8.6</v>
@@ -3682,40 +3682,40 @@
         <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
@@ -3724,7 +3724,7 @@
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z17" t="n">
         <v>11.5</v>
@@ -3772,16 +3772,16 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS17" t="n">
         <v>11</v>
@@ -3790,7 +3790,7 @@
         <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV17" t="n">
         <v>7.8</v>
@@ -3826,11 +3826,11 @@
         <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>3.65</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
@@ -3879,7 +3879,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -3888,55 +3888,55 @@
         <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
         <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
         <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.87</v>
       </c>
       <c r="W18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
         <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF18" t="n">
         <v>34</v>
@@ -3969,62 +3969,62 @@
         <v>16</v>
       </c>
       <c r="AP18" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18" t="n">
         <v>10.5</v>
       </c>
       <c r="AS18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX18" t="n">
         <v>21</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.3</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G19" t="n">
         <v>2.46</v>
@@ -4070,7 +4070,7 @@
         <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4088,7 +4088,7 @@
         <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.51</v>
@@ -4103,7 +4103,7 @@
         <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.68</v>
@@ -4196,7 +4196,7 @@
         <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BB19" t="n">
         <v>7</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
         <v>3.5</v>
@@ -4270,7 +4270,7 @@
         <v>1.42</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
         <v>3.35</v>
@@ -4282,7 +4282,7 @@
         <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
         <v>1.31</v>
@@ -4297,16 +4297,16 @@
         <v>1.92</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
         <v>1.72</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4363,7 +4363,7 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H21" t="n">
         <v>2.88</v>
@@ -4455,13 +4455,13 @@
         <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4476,7 +4476,7 @@
         <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R21" t="n">
         <v>1.38</v>
@@ -4485,10 +4485,10 @@
         <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.44</v>
@@ -4521,7 +4521,7 @@
         <v>36</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>14</v>
@@ -4548,7 +4548,7 @@
         <v>24</v>
       </c>
       <c r="AO21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP21" t="n">
         <v>13</v>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
         <v>9.800000000000001</v>
@@ -4572,7 +4572,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX21" t="n">
         <v>14</v>
@@ -4584,19 +4584,19 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF21" t="n">
         <v>14</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="I22" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.8</v>
@@ -4661,16 +4661,16 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R22" t="n">
         <v>1.55</v>
@@ -4685,7 +4685,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W22" t="n">
         <v>1.23</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>2.9</v>
       </c>
       <c r="G23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I23" t="n">
         <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>1.28</v>
@@ -4864,13 +4864,13 @@
         <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
         <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
         <v>1.57</v>
@@ -4879,7 +4879,7 @@
         <v>2.46</v>
       </c>
       <c r="V23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W23" t="n">
         <v>1.45</v>
@@ -4948,7 +4948,7 @@
         <v>15.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>5.7</v>
       </c>
       <c r="AT23" t="n">
         <v>14</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>2.94</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>1.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>1.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="H25" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>2.72</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.91</v>
+        <v>2.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.57</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="I26" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="J26" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE26" t="n">
         <v>5</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF26" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="G27" t="n">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="H27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.6</v>
       </c>
-      <c r="I27" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="K27" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB27" t="n">
         <v>8</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>20</v>
-      </c>
       <c r="BC27" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BG27" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G28" t="n">
         <v>2.54</v>
@@ -5852,7 +5852,7 @@
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G29" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I29" t="n">
         <v>2.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
         <v>4.3</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="G30" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP30" t="n">
         <v>4.6</v>
       </c>
-      <c r="L30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X30" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AQ30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU30" t="n">
         <v>10</v>
       </c>
-      <c r="AD30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV30" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="G31" t="n">
-        <v>2.76</v>
+        <v>1.72</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="K31" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>1.6</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -6568,127 +6568,127 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="H32" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.76</v>
+        <v>1.59</v>
       </c>
       <c r="O32" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="P32" t="n">
         <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>1.98</v>
       </c>
       <c r="T32" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="X32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
         <v>1.01</v>
@@ -6697,13 +6697,13 @@
         <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
         <v>1.01</v>
@@ -6712,7 +6712,7 @@
         <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
         <v>1.01</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,127 +6762,127 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="I33" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="K33" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>1.54</v>
+        <v>2.76</v>
       </c>
       <c r="O33" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="P33" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR33" t="n">
         <v>1.01</v>
@@ -6891,13 +6891,13 @@
         <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
         <v>1.01</v>
@@ -6906,7 +6906,7 @@
         <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ33" t="n">
         <v>1.01</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="G34" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="H34" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="I34" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="O34" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="P34" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W34" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="X34" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I35" t="n">
         <v>3.45</v>
       </c>
-      <c r="G35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.22</v>
-      </c>
       <c r="J35" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
         <v>4.4</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.66</v>
-      </c>
       <c r="T35" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="U35" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="V35" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="X35" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA35" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AB35" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AF35" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH35" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI35" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AJ35" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AK35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL35" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AN35" t="n">
         <v>34</v>
       </c>
       <c r="AO35" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR35" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU35" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU35" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AV35" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC35" t="n">
         <v>7</v>
       </c>
-      <c r="AX35" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>3</v>
-      </c>
       <c r="BD35" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,186 +7344,186 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="G36" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="H36" t="n">
-        <v>3.55</v>
+        <v>2.02</v>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="U36" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V36" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="W36" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="X36" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA36" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AB36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE36" t="n">
         <v>9</v>
       </c>
-      <c r="AC36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>46</v>
-      </c>
       <c r="BF36" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BG36" t="n">
-        <v>44</v>
+        <v>9.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,184 +7533,184 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.64</v>
+        <v>2.44</v>
       </c>
       <c r="G37" t="n">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="H37" t="n">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="P37" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="R37" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>2.52</v>
+        <v>1.68</v>
       </c>
       <c r="X37" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Z37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE37" t="n">
         <v>46</v>
       </c>
-      <c r="AA37" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>75</v>
-      </c>
       <c r="AF37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AG37" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AH37" t="n">
         <v>19</v>
       </c>
       <c r="AI37" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ37" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AK37" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="AL37" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM37" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="AO37" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AP37" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR37" t="n">
         <v>20</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD37" t="n">
         <v>42</v>
       </c>
-      <c r="AS37" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>27</v>
-      </c>
       <c r="BE37" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="BF37" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BG37" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
         <v>1.14</v>
       </c>
       <c r="N38" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.61</v>
@@ -7777,7 +7777,7 @@
         <v>2.88</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S38" t="n">
         <v>6.2</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,191 +7921,191 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.2</v>
+        <v>1.63</v>
       </c>
       <c r="G39" t="n">
-        <v>4.8</v>
+        <v>1.64</v>
       </c>
       <c r="H39" t="n">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U39" t="n">
         <v>2.14</v>
       </c>
-      <c r="J39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V39" t="n">
-        <v>1.87</v>
+        <v>1.19</v>
       </c>
       <c r="W39" t="n">
-        <v>1.26</v>
+        <v>2.56</v>
       </c>
       <c r="X39" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="AA39" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="AB39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK39" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK39" t="n">
+      <c r="AL39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE39" t="n">
         <v>85</v>
       </c>
-      <c r="AL39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF39" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8115,184 +8115,184 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="G40" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="H40" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="I40" t="n">
-        <v>3.75</v>
+        <v>2.14</v>
       </c>
       <c r="J40" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="K40" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O40" t="n">
         <v>1.46</v>
       </c>
-      <c r="O40" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P40" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="R40" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V40" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="W40" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -8314,186 +8314,186 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="G41" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="H41" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="I41" t="n">
         <v>3.75</v>
       </c>
       <c r="J41" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="K41" t="n">
         <v>3.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="O41" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="P41" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R41" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S41" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="T41" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="X41" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR41" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY41" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8503,184 +8503,184 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="H42" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="J42" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K42" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W42" t="n">
         <v>1.59</v>
       </c>
-      <c r="O42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.72</v>
-      </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
@@ -8697,36 +8697,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="G43" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H43" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -8735,22 +8735,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="O43" t="n">
         <v>1.4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="R43" t="n">
         <v>1.13</v>
       </c>
       <c r="S43" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W43" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,14 +8874,14 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,191 +8891,191 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H44" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K44" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="O44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P44" t="n">
         <v>1.5</v>
       </c>
-      <c r="P44" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Q44" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="R44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V44" t="n">
         <v>1.21</v>
       </c>
-      <c r="S44" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.22</v>
-      </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="X44" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,191 +9085,191 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="G45" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H45" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="J45" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N45" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P45" t="n">
         <v>1.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="R45" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S45" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V45" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="W45" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,36 +9279,36 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20:05:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="G46" t="n">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="H46" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9317,34 +9317,34 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="O46" t="n">
         <v>1.02</v>
       </c>
       <c r="P46" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V46" t="n">
         <v>1.13</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W46" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,14 +9456,14 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,36 +9473,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:05:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G47" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="I47" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="K47" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9514,19 +9514,19 @@
         <v>1.25</v>
       </c>
       <c r="O47" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="P47" t="n">
         <v>1.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="R47" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9535,10 +9535,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,14 +9650,14 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9672,31 +9672,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68</v>
+        <v>110</v>
       </c>
       <c r="H48" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,22 +9705,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="O48" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="P48" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="R48" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S48" t="n">
-        <v>3.55</v>
+        <v>1.22</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,14 +9844,14 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9861,378 +9861,572 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Deportes Concepcion</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="G49" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.59</v>
       </c>
-      <c r="H49" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>2.68</v>
-      </c>
       <c r="X49" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 01:57:17</t>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>410</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>2026-04-12 04:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>22:10:00</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Envigado</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="F51" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I51" t="n">
         <v>2.84</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J51" t="n">
         <v>2.82</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K51" t="n">
         <v>5.9</v>
       </c>
-      <c r="L50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N50" t="n">
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N51" t="n">
         <v>1.25</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O51" t="n">
         <v>1.02</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P51" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q51" t="n">
         <v>2.08</v>
       </c>
-      <c r="R50" t="n">
+      <c r="R51" t="n">
         <v>1.13</v>
       </c>
-      <c r="S50" t="n">
+      <c r="S51" t="n">
         <v>2.08</v>
       </c>
-      <c r="T50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V50" t="n">
+      <c r="T51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V51" t="n">
         <v>1.54</v>
       </c>
-      <c r="W50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH50" t="inlineStr">
-        <is>
-          <t>2026-04-12 01:57:17</t>
+      <c r="W51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>2026-04-12 04:24:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -760,7 +760,7 @@
         <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.75</v>
@@ -799,7 +799,7 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
         <v>1.73</v>
@@ -808,7 +808,7 @@
         <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
         <v>2.22</v>
@@ -1023,7 +1023,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
@@ -1059,7 +1059,7 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -1068,10 +1068,10 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I4" t="n">
         <v>3.35</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
         <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1205,13 +1205,13 @@
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
         <v>6.8</v>
@@ -1220,7 +1220,7 @@
         <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1232,16 +1232,16 @@
         <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>130</v>
@@ -1250,22 +1250,22 @@
         <v>44</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
         <v>5.8</v>
@@ -1274,7 +1274,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1283,32 +1283,32 @@
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1351,7 +1351,7 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>4.9</v>
@@ -1384,13 +1384,13 @@
         <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1533,91 +1533,91 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
         <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
         <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1626,7 +1626,7 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,37 +1641,37 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
         <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
         <v>1.74</v>
@@ -1778,7 +1778,7 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1850,7 +1850,7 @@
         <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
         <v>1.01</v>
@@ -1859,7 +1859,7 @@
         <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>7.6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
         <v>3.15</v>
@@ -1942,7 +1942,7 @@
         <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
         <v>2.62</v>
@@ -1975,7 +1975,7 @@
         <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1990,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>19.5</v>
@@ -2038,7 +2038,7 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
         <v>5.8</v>
@@ -2050,7 +2050,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2059,32 +2059,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BE8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BG8" t="n">
         <v>4.5</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
         <v>2.26</v>
@@ -2148,25 +2148,25 @@
         <v>1.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>7.4</v>
@@ -2244,7 +2244,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
         <v>4.7</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G11" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,31 +2527,31 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>1.59</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
         <v>1.3</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="I12" t="n">
         <v>2.7</v>
@@ -2712,7 +2712,7 @@
         <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2730,13 +2730,13 @@
         <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R12" t="n">
         <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2748,7 +2748,7 @@
         <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
         <v>1.86</v>
@@ -3130,7 +3130,7 @@
         <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
         <v>1.25</v>
@@ -3184,7 +3184,7 @@
         <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
         <v>9.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -3321,10 +3321,10 @@
         <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
         <v>2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="G17" t="n">
         <v>8.6</v>
@@ -3715,7 +3715,7 @@
         <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>3.65</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H18" t="n">
         <v>2.04</v>
@@ -3879,7 +3879,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -3930,7 +3930,7 @@
         <v>18.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
@@ -3972,7 +3972,7 @@
         <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
         <v>10.5</v>
@@ -3984,13 +3984,13 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
         <v>9.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX18" t="n">
         <v>21</v>
@@ -3999,32 +3999,32 @@
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4082,13 +4082,13 @@
         <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
         <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
         <v>1.51</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -4249,118 +4249,118 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
         <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.71</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.72</v>
-      </c>
       <c r="X20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
         <v>9</v>
       </c>
-      <c r="AD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
         <v>1.01</v>
@@ -4369,7 +4369,7 @@
         <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
         <v>6.2</v>
@@ -4384,10 +4384,10 @@
         <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
@@ -4396,23 +4396,23 @@
         <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE20" t="n">
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4482,13 +4482,13 @@
         <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
         <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
         <v>1.44</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H22" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="J22" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,13 +4661,13 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q22" t="n">
         <v>1.51</v>
@@ -4685,7 +4685,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="W22" t="n">
         <v>1.23</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G23" t="n">
         <v>3.2</v>
@@ -4846,7 +4846,7 @@
         <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.28</v>
@@ -4870,7 +4870,7 @@
         <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
         <v>1.57</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>2.56</v>
       </c>
       <c r="G25" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H25" t="n">
         <v>3.2</v>
@@ -5252,19 +5252,19 @@
         <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
         <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
         <v>1.41</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H26" t="n">
         <v>2.4</v>
@@ -5446,7 +5446,7 @@
         <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G27" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H27" t="n">
         <v>3.15</v>
@@ -5652,7 +5652,7 @@
         <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
         <v>1.38</v>
@@ -5721,7 +5721,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="AS27" t="n">
         <v>8.6</v>
@@ -5745,7 +5745,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA27" t="n">
         <v>8.6</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
         <v>2.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
         <v>4.3</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.82</v>
       </c>
       <c r="G30" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H30" t="n">
         <v>3.6</v>
@@ -6222,13 +6222,13 @@
         <v>3.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R30" t="n">
         <v>1.99</v>
       </c>
       <c r="S30" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="T30" t="n">
         <v>1.36</v>
@@ -6300,7 +6300,7 @@
         <v>4.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="AR30" t="n">
         <v>4.5</v>
@@ -6309,7 +6309,7 @@
         <v>4.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU30" t="n">
         <v>10</v>
@@ -6333,7 +6333,7 @@
         <v>4.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="BC30" t="n">
         <v>13</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>1.61</v>
       </c>
       <c r="G31" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
@@ -6398,7 +6398,7 @@
         <v>3.95</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.39</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -6601,13 +6601,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.02</v>
       </c>
       <c r="P32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q32" t="n">
         <v>1.96</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
         <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>2.48</v>
       </c>
       <c r="G35" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="H35" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I35" t="n">
         <v>3.45</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7186,10 +7186,10 @@
         <v>2.98</v>
       </c>
       <c r="O35" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P35" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q35" t="n">
         <v>2.3</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>3.55</v>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
@@ -7577,7 +7577,7 @@
         <v>1.42</v>
       </c>
       <c r="P37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q37" t="n">
         <v>2.28</v>
@@ -7649,16 +7649,16 @@
         <v>120</v>
       </c>
       <c r="AN37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO37" t="n">
         <v>50</v>
       </c>
       <c r="AP37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR37" t="n">
         <v>20</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -7756,10 +7756,10 @@
         <v>3.05</v>
       </c>
       <c r="K38" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M38" t="n">
         <v>1.14</v>
@@ -7774,10 +7774,10 @@
         <v>1.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R38" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
         <v>6.2</v>
@@ -7861,7 +7861,7 @@
         <v>50</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
         <v>6.6</v>
@@ -7897,14 +7897,14 @@
         <v>48</v>
       </c>
       <c r="BF38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG38" t="n">
         <v>55</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -7941,10 +7941,10 @@
         <v>1.64</v>
       </c>
       <c r="H39" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I39" t="n">
         <v>6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>4.4</v>
@@ -7971,7 +7971,7 @@
         <v>1.79</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -7983,7 +7983,7 @@
         <v>2.14</v>
       </c>
       <c r="V39" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
         <v>2.56</v>
@@ -8079,26 +8079,26 @@
         <v>60</v>
       </c>
       <c r="BB39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC39" t="n">
         <v>15</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD39" t="n">
         <v>26</v>
       </c>
       <c r="BE39" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG39" t="n">
         <v>70</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G40" t="n">
         <v>4.8</v>
@@ -8159,7 +8159,7 @@
         <v>1.46</v>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
         <v>2.34</v>
@@ -8183,7 +8183,7 @@
         <v>1.26</v>
       </c>
       <c r="X40" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y40" t="n">
         <v>8.4</v>
@@ -8198,7 +8198,7 @@
         <v>15.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD40" t="n">
         <v>12.5</v>
@@ -8222,7 +8222,7 @@
         <v>130</v>
       </c>
       <c r="AK40" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL40" t="n">
         <v>100</v>
@@ -8234,7 +8234,7 @@
         <v>120</v>
       </c>
       <c r="AO40" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP40" t="n">
         <v>9</v>
@@ -8246,7 +8246,7 @@
         <v>10</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT40" t="n">
         <v>11</v>
@@ -8255,44 +8255,44 @@
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX40" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY40" t="n">
         <v>16</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BB40" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG40" t="n">
         <v>16</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>2.96</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H41" t="n">
         <v>2.96</v>
@@ -8338,7 +8338,7 @@
         <v>2.46</v>
       </c>
       <c r="K41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8347,7 +8347,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="O41" t="n">
         <v>1.01</v>
@@ -8362,7 +8362,7 @@
         <v>1.14</v>
       </c>
       <c r="S41" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -8374,7 +8374,7 @@
         <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G42" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H42" t="n">
         <v>3.45</v>
@@ -8535,7 +8535,7 @@
         <v>3.1</v>
       </c>
       <c r="L42" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M42" t="n">
         <v>1.15</v>
@@ -8547,10 +8547,10 @@
         <v>1.63</v>
       </c>
       <c r="P42" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
         <v>1.16</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -8714,10 +8714,10 @@
         <v>2.02</v>
       </c>
       <c r="G43" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H43" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I43" t="n">
         <v>5.2</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G45" t="n">
         <v>1.94</v>
@@ -9159,7 +9159,7 @@
         <v>14.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA45" t="n">
         <v>170</v>
@@ -9189,7 +9189,7 @@
         <v>130</v>
       </c>
       <c r="AJ45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK45" t="n">
         <v>26</v>
@@ -9207,28 +9207,28 @@
         <v>170</v>
       </c>
       <c r="AP45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ45" t="n">
         <v>11.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT45" t="n">
         <v>5.9</v>
       </c>
       <c r="AU45" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV45" t="n">
         <v>18</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX45" t="n">
         <v>8.800000000000001</v>
@@ -9240,7 +9240,7 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB45" t="n">
         <v>19</v>
@@ -9249,20 +9249,20 @@
         <v>21</v>
       </c>
       <c r="BD45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE45" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF45" t="n">
         <v>16</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G46" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H46" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I46" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K46" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9320,7 +9320,7 @@
         <v>1.6</v>
       </c>
       <c r="O46" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="P46" t="n">
         <v>1.6</v>
@@ -9341,10 +9341,10 @@
         <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W46" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G47" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="H47" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="I47" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="K47" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9514,19 +9514,19 @@
         <v>1.25</v>
       </c>
       <c r="O47" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P47" t="n">
         <v>1.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R47" t="n">
         <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9535,10 +9535,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
         <v>110</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W49" t="n">
         <v>1.59</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H50" t="n">
         <v>8.800000000000001</v>
@@ -10081,10 +10081,10 @@
         <v>10.5</v>
       </c>
       <c r="J50" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K50" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10120,7 +10120,7 @@
         <v>1.1</v>
       </c>
       <c r="W50" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X50" t="n">
         <v>11.5</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 04:24:19</t>
+          <t>2026-04-12 06:50:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -757,76 +757,76 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I2" t="n">
         <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.54</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
         <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
         <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -853,16 +853,16 @@
         <v>130</v>
       </c>
       <c r="AL2" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AM2" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AN2" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AP2" t="n">
         <v>7.6</v>
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1041,13 +1041,13 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>130</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
         <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
         <v>2.74</v>
@@ -1166,13 +1166,13 @@
         <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
         <v>1.59</v>
@@ -1196,16 +1196,16 @@
         <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
         <v>60</v>
@@ -1220,7 +1220,7 @@
         <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1244,7 +1244,7 @@
         <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
         <v>44</v>
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
@@ -1274,7 +1274,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.9</v>
@@ -1387,7 +1387,7 @@
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1641,37 +1641,37 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -2115,28 +2115,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
         <v>2.26</v>
@@ -2148,7 +2148,7 @@
         <v>1.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.13</v>
@@ -2157,22 +2157,22 @@
         <v>6.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
         <v>7.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z9" t="n">
         <v>12.5</v>
@@ -2184,7 +2184,7 @@
         <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
         <v>15.5</v>
@@ -2220,7 +2220,7 @@
         <v>210</v>
       </c>
       <c r="AO9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,41 +2244,41 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -2339,16 +2339,16 @@
         <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
@@ -2405,7 +2405,7 @@
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
         <v>180</v>
@@ -2423,7 +2423,7 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
         <v>5.2</v>
@@ -2447,7 +2447,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
         <v>5.1</v>
@@ -2462,7 +2462,7 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
         <v>4.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -2503,40 +2503,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
         <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
         <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
@@ -2548,13 +2548,13 @@
         <v>1.87</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU11" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB11" t="n">
         <v>3.3</v>
       </c>
-      <c r="AV11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5</v>
-      </c>
       <c r="BC11" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
         <v>1.99</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -2915,16 +2915,16 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
         <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
         <v>2.3</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
         <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS15" t="n">
         <v>18.5</v>
@@ -3423,7 +3423,7 @@
         <v>7.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC15" t="n">
         <v>40</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -3709,10 +3709,10 @@
         <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
         <v>2.56</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>3.65</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H18" t="n">
         <v>2.04</v>
@@ -3879,7 +3879,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -3891,10 +3891,10 @@
         <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
         <v>1.43</v>
@@ -3903,16 +3903,16 @@
         <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.87</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X18" t="n">
         <v>20</v>
@@ -4008,13 +4008,13 @@
         <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD18" t="n">
         <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
         <v>4.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
         <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
         <v>2.26</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
         <v>1.49</v>
@@ -4291,25 +4291,25 @@
         <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -4321,19 +4321,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4360,19 +4360,19 @@
         <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS20" t="n">
         <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
@@ -4381,13 +4381,13 @@
         <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
@@ -4399,20 +4399,20 @@
         <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -4458,10 +4458,10 @@
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4488,7 +4488,7 @@
         <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.44</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -4661,13 +4661,13 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q22" t="n">
         <v>1.51</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
         <v>2.46</v>
       </c>
       <c r="V23" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W23" t="n">
         <v>1.45</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="O24" t="n">
         <v>1.18</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G25" t="n">
         <v>2.74</v>
@@ -5231,10 +5231,10 @@
         <v>3.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5252,7 +5252,7 @@
         <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R25" t="n">
         <v>1.21</v>
@@ -5261,10 +5261,10 @@
         <v>5.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
         <v>1.41</v>
@@ -5288,7 +5288,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>18</v>
@@ -5303,7 +5303,7 @@
         <v>15.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>90</v>
@@ -5336,7 +5336,7 @@
         <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -5360,29 +5360,29 @@
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC25" t="n">
         <v>4.4</v>
       </c>
       <c r="BD25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF25" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -5428,10 +5428,10 @@
         <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
@@ -5446,7 +5446,7 @@
         <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
@@ -5455,10 +5455,10 @@
         <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
         <v>1.62</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>2.54</v>
       </c>
       <c r="G27" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H27" t="n">
         <v>3.15</v>
@@ -5625,10 +5625,10 @@
         <v>3.35</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
         <v>2.66</v>
@@ -5643,10 +5643,10 @@
         <v>2.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T27" t="n">
         <v>2.02</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -6225,10 +6225,10 @@
         <v>1.31</v>
       </c>
       <c r="R30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="T30" t="n">
         <v>1.36</v>
@@ -6276,7 +6276,7 @@
         <v>17.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ30" t="n">
         <v>28</v>
@@ -6294,22 +6294,22 @@
         <v>6.8</v>
       </c>
       <c r="AO30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="AR30" t="n">
         <v>4.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT30" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU30" t="n">
         <v>10</v>
@@ -6318,7 +6318,7 @@
         <v>13.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX30" t="n">
         <v>15</v>
@@ -6333,7 +6333,7 @@
         <v>4.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC30" t="n">
         <v>13</v>
@@ -6342,7 +6342,7 @@
         <v>16</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF30" t="n">
         <v>4.7</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.96</v>
       </c>
       <c r="G34" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H34" t="n">
         <v>2.48</v>
@@ -6977,7 +6977,7 @@
         <v>3.35</v>
       </c>
       <c r="J34" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="K34" t="n">
         <v>3.9</v>
@@ -6989,7 +6989,7 @@
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O34" t="n">
         <v>1.39</v>
@@ -7013,10 +7013,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G35" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H35" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
         <v>3.35</v>
@@ -7183,37 +7183,37 @@
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>1.45</v>
       </c>
       <c r="P35" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R35" t="n">
         <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T35" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W35" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="X35" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="n">
         <v>11</v>
@@ -7228,7 +7228,7 @@
         <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD35" t="n">
         <v>14.5</v>
@@ -7240,7 +7240,7 @@
         <v>16.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH35" t="n">
         <v>21</v>
@@ -7276,53 +7276,53 @@
         <v>18</v>
       </c>
       <c r="AS35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT35" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT35" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AU35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX35" t="n">
         <v>13</v>
       </c>
       <c r="AY35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>17.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB35" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD35" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF35" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG35" t="n">
         <v>36</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G36" t="n">
         <v>3.95</v>
       </c>
       <c r="H36" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J36" t="n">
         <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>1.29</v>
@@ -7386,25 +7386,25 @@
         <v>2.18</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R36" t="n">
         <v>1.47</v>
       </c>
       <c r="S36" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T36" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U36" t="n">
         <v>2.16</v>
       </c>
       <c r="V36" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X36" t="n">
         <v>20</v>
@@ -7479,7 +7479,7 @@
         <v>4.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW36" t="n">
         <v>7</v>
@@ -7497,7 +7497,7 @@
         <v>2.76</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="BC36" t="n">
         <v>3</v>
@@ -7506,7 +7506,7 @@
         <v>2.16</v>
       </c>
       <c r="BE36" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="BF36" t="n">
         <v>7.8</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
         <v>3.65</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
         <v>3.25</v>
@@ -7595,7 +7595,7 @@
         <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
         <v>1.68</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>3.15</v>
       </c>
       <c r="L38" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M38" t="n">
         <v>1.14</v>
@@ -7777,7 +7777,7 @@
         <v>2.86</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S38" t="n">
         <v>6.2</v>
@@ -7897,14 +7897,14 @@
         <v>48</v>
       </c>
       <c r="BF38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG38" t="n">
         <v>55</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -7959,16 +7959,16 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>2.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R39" t="n">
         <v>1.48</v>
@@ -8031,13 +8031,13 @@
         <v>15.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM39" t="n">
         <v>95</v>
       </c>
       <c r="AN39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO39" t="n">
         <v>75</v>
@@ -8079,10 +8079,10 @@
         <v>60</v>
       </c>
       <c r="BB39" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC39" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD39" t="n">
         <v>26</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -8132,13 +8132,13 @@
         <v>4.3</v>
       </c>
       <c r="G40" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H40" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I40" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J40" t="n">
         <v>3.25</v>
@@ -8147,7 +8147,7 @@
         <v>3.45</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M40" t="n">
         <v>1.1</v>
@@ -8159,13 +8159,13 @@
         <v>1.46</v>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
         <v>4.5</v>
@@ -8174,19 +8174,19 @@
         <v>2.06</v>
       </c>
       <c r="U40" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="V40" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W40" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z40" t="n">
         <v>14</v>
@@ -8198,10 +8198,10 @@
         <v>15.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE40" t="n">
         <v>32</v>
@@ -8237,7 +8237,7 @@
         <v>23</v>
       </c>
       <c r="AP40" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ40" t="n">
         <v>6.6</v>
@@ -8246,7 +8246,7 @@
         <v>10</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT40" t="n">
         <v>11</v>
@@ -8255,44 +8255,44 @@
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AX40" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AY40" t="n">
         <v>16</v>
       </c>
       <c r="AZ40" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BA40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB40" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB40" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC40" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF40" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BG40" t="n">
         <v>16</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -8323,40 +8323,40 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G41" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H41" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I41" t="n">
         <v>3.75</v>
       </c>
       <c r="J41" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="K41" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N41" t="n">
-        <v>1.45</v>
+        <v>2.34</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P41" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R41" t="n">
         <v>1.14</v>
@@ -8431,62 +8431,62 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU41" t="n">
         <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -8714,13 +8714,13 @@
         <v>2.02</v>
       </c>
       <c r="G43" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H43" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>2.96</v>
@@ -8729,152 +8729,152 @@
         <v>3.85</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="O43" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P43" t="n">
         <v>1.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S43" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V43" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W43" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA43" t="n">
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM43" t="n">
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G45" t="n">
         <v>1.94</v>
@@ -9114,7 +9114,7 @@
         <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L45" t="n">
         <v>1.46</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G46" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="I46" t="n">
         <v>8.800000000000001</v>
@@ -9308,7 +9308,7 @@
         <v>3.3</v>
       </c>
       <c r="K46" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9317,16 +9317,16 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="O46" t="n">
         <v>1.38</v>
       </c>
       <c r="P46" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="R46" t="n">
         <v>1.2</v>
@@ -9344,7 +9344,7 @@
         <v>1.12</v>
       </c>
       <c r="W46" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="G47" t="n">
         <v>3.05</v>
       </c>
       <c r="H47" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="K47" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9514,19 +9514,19 @@
         <v>1.25</v>
       </c>
       <c r="O47" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="P47" t="n">
         <v>1.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R47" t="n">
         <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9535,7 +9535,7 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W47" t="n">
         <v>1.48</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
         <v>1.5</v>
       </c>
       <c r="P50" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q50" t="n">
         <v>2.44</v>
@@ -10177,7 +10177,7 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ50" t="n">
         <v>15.5</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="G51" t="n">
-        <v>4.2</v>
+        <v>970</v>
       </c>
       <c r="H51" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="I51" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="J51" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K51" t="n">
-        <v>5.9</v>
+        <v>110</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10311,10 +10311,10 @@
         <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W51" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 06:50:53</t>
+          <t>2026-04-12 09:16:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -766,28 +766,28 @@
         <v>1.89</v>
       </c>
       <c r="I2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q2" t="n">
         <v>2.58</v>
@@ -805,7 +805,7 @@
         <v>1.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -856,19 +856,19 @@
         <v>150</v>
       </c>
       <c r="AM2" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN2" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
         <v>7.6</v>
@@ -889,7 +889,7 @@
         <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -898,29 +898,29 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
         <v>5.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
@@ -981,7 +981,7 @@
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
         <v>2.08</v>
@@ -1005,16 +1005,16 @@
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
@@ -1029,7 +1029,7 @@
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
         <v>18</v>
@@ -1059,7 +1059,7 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.8</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1145,40 +1145,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I4" t="n">
         <v>3.2</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>2.92</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>3.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
         <v>1.23</v>
@@ -1193,13 +1193,13 @@
         <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1214,7 +1214,7 @@
         <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>15</v>
@@ -1229,31 +1229,31 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK4" t="n">
         <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO4" t="n">
         <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.4</v>
@@ -1262,19 +1262,19 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1283,32 +1283,32 @@
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1453,10 +1453,10 @@
         <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
@@ -1480,7 +1480,7 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1489,20 +1489,20 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
         <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1533,100 +1533,100 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="P6" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.41</v>
       </c>
       <c r="G7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H7" t="n">
         <v>6.6</v>
@@ -1742,7 +1742,7 @@
         <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
@@ -1760,7 +1760,7 @@
         <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
         <v>1.5</v>
@@ -1778,7 +1778,7 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1838,13 +1838,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
@@ -1853,10 +1853,10 @@
         <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -1868,7 +1868,7 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
         <v>9.4</v>
@@ -1877,20 +1877,20 @@
         <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
         <v>3.9</v>
@@ -1936,7 +1936,7 @@
         <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.53</v>
@@ -2050,7 +2050,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2059,32 +2059,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
         <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
         <v>4.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -2124,7 +2124,7 @@
         <v>2.12</v>
       </c>
       <c r="I9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
@@ -2172,7 +2172,7 @@
         <v>7.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z9" t="n">
         <v>12.5</v>
@@ -2181,7 +2181,7 @@
         <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.8</v>
@@ -2196,7 +2196,7 @@
         <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH9" t="n">
         <v>32</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,41 +2244,41 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
         <v>2.14</v>
@@ -2336,7 +2336,7 @@
         <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
         <v>1.64</v>
@@ -2423,7 +2423,7 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
         <v>5.2</v>
@@ -2435,10 +2435,10 @@
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>50</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2465,14 +2465,14 @@
         <v>5.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
         <v>3.75</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>1.41</v>
@@ -2551,10 +2551,10 @@
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ11" t="n">
         <v>7</v>
       </c>
       <c r="AR11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BG11" t="n">
         <v>3.35</v>
       </c>
-      <c r="BF11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
         <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.46</v>
@@ -2915,7 +2915,7 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.39</v>
@@ -2930,16 +2930,16 @@
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.35</v>
@@ -3005,56 +3005,56 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG13" t="n">
         <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -3085,64 +3085,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="G14" t="n">
         <v>1.61</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,104 +3151,104 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -3312,7 +3312,7 @@
         <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
         <v>1.51</v>
@@ -3327,10 +3327,10 @@
         <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -3339,10 +3339,10 @@
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
         <v>11.5</v>
@@ -3384,7 +3384,7 @@
         <v>9.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP15" t="n">
         <v>17.5</v>
@@ -3399,7 +3399,7 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
         <v>8.4</v>
@@ -3414,7 +3414,7 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
         <v>15</v>
@@ -3423,7 +3423,7 @@
         <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>15.5</v>
@@ -3432,7 +3432,7 @@
         <v>25</v>
       </c>
       <c r="BE15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
         <v>8.199999999999999</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -3476,22 +3476,22 @@
         <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I16" t="n">
         <v>1.99</v>
       </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -3509,7 +3509,7 @@
         <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
         <v>3.7</v>
@@ -3524,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>14</v>
@@ -3575,7 +3575,7 @@
         <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="n">
         <v>16</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>1.49</v>
       </c>
       <c r="I18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J18" t="n">
         <v>4.3</v>
@@ -3909,7 +3909,7 @@
         <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.15</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -4055,85 +4055,85 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G19" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H19" t="n">
         <v>2.04</v>
       </c>
       <c r="I19" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
         <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG19" t="n">
         <v>18.5</v>
@@ -4142,10 +4142,10 @@
         <v>19.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
         <v>50</v>
@@ -4154,71 +4154,71 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
         <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>50</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
         <v>2.46</v>
@@ -4276,10 +4276,10 @@
         <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
         <v>1.69</v>
@@ -4294,7 +4294,7 @@
         <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
         <v>1.46</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
@@ -4467,16 +4467,16 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
@@ -4488,19 +4488,19 @@
         <v>1.75</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X21" t="n">
         <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4512,7 +4512,7 @@
         <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
         <v>15</v>
@@ -4521,7 +4521,7 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
@@ -4560,10 +4560,10 @@
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AU21" t="n">
         <v>5.9</v>
@@ -4572,7 +4572,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,29 +4584,29 @@
         <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="X22" t="n">
         <v>18.5</v>
@@ -4703,22 +4703,22 @@
         <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF22" t="n">
         <v>18</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
@@ -4727,7 +4727,7 @@
         <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
         <v>32</v>
@@ -4739,10 +4739,10 @@
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -4754,10 +4754,10 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
@@ -4766,31 +4766,31 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
       </c>
       <c r="BA22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB22" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BC22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -4837,16 +4837,16 @@
         <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I23" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.24</v>
@@ -4867,16 +4867,16 @@
         <v>1.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S23" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="T23" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V23" t="n">
         <v>2.12</v>
@@ -4963,7 +4963,7 @@
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
         <v>13.5</v>
@@ -4975,16 +4975,16 @@
         <v>19.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>24</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H24" t="n">
         <v>2.34</v>
       </c>
       <c r="I24" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
@@ -5055,31 +5055,31 @@
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
         <v>1.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
         <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U24" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W24" t="n">
         <v>1.46</v>
       </c>
       <c r="X24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y24" t="n">
         <v>16</v>
@@ -5091,25 +5091,25 @@
         <v>36</v>
       </c>
       <c r="AB24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
         <v>12</v>
       </c>
       <c r="AE24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF24" t="n">
         <v>24</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>25</v>
       </c>
       <c r="AG24" t="n">
         <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
         <v>32</v>
@@ -5118,7 +5118,7 @@
         <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -5127,68 +5127,68 @@
         <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP24" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
         <v>15.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AT24" t="n">
         <v>14</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
         <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BF24" t="n">
         <v>18</v>
       </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -5219,94 +5219,94 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.16</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -5324,43 +5324,43 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
         <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
         <v>1.01</v>
@@ -5378,11 +5378,11 @@
         <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="H26" t="n">
         <v>3.1</v>
@@ -5425,88 +5425,88 @@
         <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>2.46</v>
       </c>
       <c r="O26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P26" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q26" t="n">
         <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
         <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G27" t="n">
         <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I27" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
         <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5637,10 +5637,10 @@
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
@@ -5649,10 +5649,10 @@
         <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="V27" t="n">
         <v>1.62</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G28" t="n">
         <v>2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I28" t="n">
         <v>3.6</v>
@@ -5816,7 +5816,7 @@
         <v>2.98</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L28" t="n">
         <v>1.5</v>
@@ -5834,10 +5834,10 @@
         <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
         <v>5.1</v>
@@ -5909,13 +5909,13 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
         <v>8.6</v>
@@ -5930,10 +5930,10 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
@@ -5942,10 +5942,10 @@
         <v>6.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BC28" t="n">
         <v>7.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.82</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H29" t="n">
         <v>3.6</v>
@@ -6031,10 +6031,10 @@
         <v>1.31</v>
       </c>
       <c r="R29" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="T29" t="n">
         <v>1.36</v>
@@ -6046,7 +6046,7 @@
         <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X29" t="n">
         <v>55</v>
@@ -6061,13 +6061,13 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC29" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>40</v>
@@ -6079,10 +6079,10 @@
         <v>14.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
@@ -6097,25 +6097,25 @@
         <v>48</v>
       </c>
       <c r="AN29" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU29" t="n">
         <v>10</v>
@@ -6124,7 +6124,7 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX29" t="n">
         <v>15</v>
@@ -6136,10 +6136,10 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>18.5</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,7 +6148,7 @@
         <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF29" t="n">
         <v>4.7</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>1.87</v>
       </c>
       <c r="G30" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H30" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="I30" t="n">
         <v>4.1</v>
@@ -6204,7 +6204,7 @@
         <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6213,13 +6213,13 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="O30" t="n">
         <v>1.15</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
         <v>1.43</v>
@@ -6240,7 +6240,7 @@
         <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I31" t="n">
         <v>2.7</v>
@@ -6401,31 +6401,31 @@
         <v>4.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S31" t="n">
         <v>2.56</v>
       </c>
       <c r="T31" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="U31" t="n">
         <v>2.44</v>
@@ -6470,7 +6470,7 @@
         <v>16</v>
       </c>
       <c r="AI31" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AJ31" t="n">
         <v>44</v>
@@ -6500,7 +6500,7 @@
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT31" t="n">
         <v>13</v>
@@ -6527,16 +6527,16 @@
         <v>7</v>
       </c>
       <c r="BB31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC31" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC31" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD31" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF31" t="n">
         <v>14</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -6568,179 +6568,179 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cavese 1919</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="J32" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>3.85</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="T32" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -6762,55 +6762,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Aurora Pro Patria 1919</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="G33" t="n">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="K33" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -6956,127 +6956,127 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aurora Pro Patria 1919</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="G34" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H34" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="K34" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>1.78</v>
+        <v>2.78</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="P34" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.76</v>
+        <v>2.42</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V34" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR34" t="n">
         <v>1.01</v>
@@ -7085,13 +7085,13 @@
         <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU34" t="n">
         <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW34" t="n">
         <v>1.01</v>
@@ -7100,7 +7100,7 @@
         <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -7150,127 +7150,127 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="H35" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="I35" t="n">
         <v>3.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="K35" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.76</v>
+        <v>1.57</v>
       </c>
       <c r="O35" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="P35" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="T35" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
         <v>1.47</v>
       </c>
       <c r="W35" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
         <v>1.01</v>
@@ -7279,13 +7279,13 @@
         <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
         <v>1.01</v>
@@ -7294,7 +7294,7 @@
         <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -7344,179 +7344,179 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AZ Picerno ASD</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese 1919</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.84</v>
+        <v>1.61</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3</v>
+        <v>1.65</v>
       </c>
       <c r="H36" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>1.57</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V36" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="W36" t="n">
-        <v>1.3</v>
+        <v>2.52</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>3.25</v>
@@ -7556,13 +7556,13 @@
         <v>2.66</v>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L37" t="n">
         <v>1.5</v>
@@ -7595,7 +7595,7 @@
         <v>1.93</v>
       </c>
       <c r="V37" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W37" t="n">
         <v>1.44</v>
@@ -7685,7 +7685,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BA37" t="n">
         <v>7</v>
@@ -7706,11 +7706,11 @@
         <v>6.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BB38" t="n">
         <v>8.4</v>
@@ -7900,11 +7900,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG38" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>3.6</v>
       </c>
       <c r="G39" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H39" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J39" t="n">
         <v>3.65</v>
@@ -7953,7 +7953,7 @@
         <v>4.1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
@@ -7974,7 +7974,7 @@
         <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T39" t="n">
         <v>1.56</v>
@@ -7983,13 +7983,13 @@
         <v>2.16</v>
       </c>
       <c r="V39" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W39" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X39" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y39" t="n">
         <v>970</v>
@@ -8028,7 +8028,7 @@
         <v>70</v>
       </c>
       <c r="AK39" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL39" t="n">
         <v>46</v>
@@ -8037,68 +8037,68 @@
         <v>75</v>
       </c>
       <c r="AN39" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO39" t="n">
         <v>970</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT39" t="n">
         <v>6</v>
       </c>
-      <c r="AS39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AU39" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AV39" t="n">
         <v>9.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="AY39" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BC39" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BD39" t="n">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG39" t="n">
         <v>9.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G40" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H40" t="n">
         <v>3.55</v>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K40" t="n">
         <v>3.25</v>
@@ -8162,7 +8162,7 @@
         <v>1.76</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8177,7 +8177,7 @@
         <v>2.04</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
         <v>1.68</v>
@@ -8213,7 +8213,7 @@
         <v>11.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI40" t="n">
         <v>60</v>
@@ -8243,7 +8243,7 @@
         <v>11</v>
       </c>
       <c r="AR40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS40" t="n">
         <v>55</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -8326,13 +8326,13 @@
         <v>2.78</v>
       </c>
       <c r="G41" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="n">
         <v>3.1</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J41" t="n">
         <v>3.05</v>
@@ -8347,34 +8347,34 @@
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O41" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P41" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R41" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U41" t="n">
         <v>1.77</v>
       </c>
       <c r="V41" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W41" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X41" t="n">
         <v>7.8</v>
@@ -8392,7 +8392,7 @@
         <v>7.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD41" t="n">
         <v>15</v>
@@ -8404,7 +8404,7 @@
         <v>16</v>
       </c>
       <c r="AG41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH41" t="n">
         <v>25</v>
@@ -8473,7 +8473,7 @@
         <v>38</v>
       </c>
       <c r="BD41" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE41" t="n">
         <v>48</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.62</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.63</v>
       </c>
       <c r="H42" t="n">
         <v>6.2</v>
@@ -8547,16 +8547,16 @@
         <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R42" t="n">
         <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T42" t="n">
         <v>1.82</v>
@@ -8577,28 +8577,28 @@
         <v>23</v>
       </c>
       <c r="Z42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA42" t="n">
         <v>170</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD42" t="n">
         <v>23</v>
       </c>
       <c r="AE42" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AH42" t="n">
         <v>20</v>
@@ -8613,22 +8613,22 @@
         <v>15.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM42" t="n">
         <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO42" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP42" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR42" t="n">
         <v>42</v>
@@ -8640,7 +8640,7 @@
         <v>9</v>
       </c>
       <c r="AU42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV42" t="n">
         <v>21</v>
@@ -8667,20 +8667,20 @@
         <v>14.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE42" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG42" t="n">
         <v>70</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -8711,13 +8711,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G43" t="n">
         <v>4.7</v>
       </c>
       <c r="H43" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I43" t="n">
         <v>2.12</v>
@@ -8747,10 +8747,10 @@
         <v>2.36</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T43" t="n">
         <v>2.06</v>
@@ -8843,7 +8843,7 @@
         <v>6</v>
       </c>
       <c r="AX43" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="AY43" t="n">
         <v>16</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J44" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K44" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,7 +8929,7 @@
         <v>1.14</v>
       </c>
       <c r="N44" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.58</v>
@@ -8944,41 +8944,41 @@
         <v>1.16</v>
       </c>
       <c r="S44" t="n">
-        <v>2.82</v>
+        <v>5.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U44" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V44" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W44" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD44" t="n">
         <v>20</v>
       </c>
-      <c r="AA44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>19</v>
-      </c>
       <c r="AE44" t="n">
         <v>1000</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH44" t="n">
         <v>1000</v>
@@ -9016,31 +9016,31 @@
         <v>6.4</v>
       </c>
       <c r="AQ44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR44" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS44" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AT44" t="n">
         <v>7.6</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY44" t="n">
         <v>12</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>12.5</v>
       </c>
       <c r="AZ44" t="n">
         <v>16.5</v>
@@ -9049,7 +9049,7 @@
         <v>55</v>
       </c>
       <c r="BB44" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BC44" t="n">
         <v>36</v>
@@ -9058,17 +9058,17 @@
         <v>50</v>
       </c>
       <c r="BE44" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG44" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
         <v>1.59</v>
       </c>
       <c r="X45" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y45" t="n">
         <v>11</v>
@@ -9189,7 +9189,7 @@
         <v>120</v>
       </c>
       <c r="AJ45" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK45" t="n">
         <v>50</v>
@@ -9213,10 +9213,10 @@
         <v>8</v>
       </c>
       <c r="AR45" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>55</v>
+        <v>5.2</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -9228,41 +9228,41 @@
         <v>14.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>44</v>
+        <v>5.1</v>
       </c>
       <c r="AX45" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY45" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF45" t="n">
         <v>5</v>
       </c>
-      <c r="BA45" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG45" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G46" t="n">
         <v>2.28</v>
@@ -9308,7 +9308,7 @@
         <v>2.96</v>
       </c>
       <c r="K46" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L46" t="n">
         <v>1.45</v>
@@ -9320,7 +9320,7 @@
         <v>2.76</v>
       </c>
       <c r="O46" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P46" t="n">
         <v>1.59</v>
@@ -9332,13 +9332,13 @@
         <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T46" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="U46" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="V46" t="n">
         <v>1.26</v>
@@ -9401,7 +9401,7 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ46" t="n">
         <v>9.4</v>
@@ -9446,7 +9446,7 @@
         <v>38</v>
       </c>
       <c r="BE46" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF46" t="n">
         <v>18.5</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -9487,61 +9487,61 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="G47" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H47" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J47" t="n">
         <v>2.92</v>
       </c>
       <c r="K47" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O47" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R47" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S47" t="n">
-        <v>2.16</v>
+        <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V47" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W47" t="n">
         <v>1.83</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y47" t="n">
         <v>1000</v>
@@ -9553,10 +9553,10 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K48" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L48" t="n">
         <v>1.46</v>
@@ -9732,7 +9732,7 @@
         <v>1.21</v>
       </c>
       <c r="W48" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X48" t="n">
         <v>10</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -9878,22 +9878,22 @@
         <v>1.62</v>
       </c>
       <c r="G49" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H49" t="n">
         <v>6.6</v>
       </c>
       <c r="I49" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K49" t="n">
         <v>4.4</v>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -9908,25 +9908,25 @@
         <v>1.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R49" t="n">
         <v>1.25</v>
       </c>
       <c r="S49" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="U49" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="V49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W49" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="X49" t="n">
         <v>13.5</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -10078,10 +10078,10 @@
         <v>2.78</v>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -10117,7 +10117,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W50" t="n">
         <v>1.48</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -10263,58 +10263,58 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G51" t="n">
-        <v>110</v>
+        <v>1.85</v>
       </c>
       <c r="H51" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="I51" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J51" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O51" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P51" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="R51" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W51" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10329,10 +10329,10 @@
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD51" t="n">
         <v>1000</v>
@@ -10344,7 +10344,7 @@
         <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH51" t="n">
         <v>1000</v>
@@ -10365,68 +10365,68 @@
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO51" t="n">
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -10460,16 +10460,16 @@
         <v>1.98</v>
       </c>
       <c r="G52" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H52" t="n">
         <v>3.25</v>
       </c>
       <c r="I52" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="K52" t="n">
         <v>5.5</v>
@@ -10505,10 +10505,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W52" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10675,7 @@
         <v>1.1</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
         <v>3.05</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H54" t="n">
         <v>2.38</v>
@@ -10896,7 +10896,7 @@
         <v>1.56</v>
       </c>
       <c r="W54" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-12 11:37:19</t>
+          <t>2026-04-12 13:55:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH54"/>
+  <dimension ref="A1:BH55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>1.89</v>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -886,10 +886,10 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG3" t="n">
         <v>18</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5.9</v>
       </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H4" t="n">
         <v>2.98</v>
@@ -1157,13 +1157,13 @@
         <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1172,7 +1172,7 @@
         <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
         <v>1.62</v>
@@ -1196,7 +1196,7 @@
         <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1292,7 +1292,7 @@
         <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
         <v>5.6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.9</v>
@@ -1357,40 +1357,40 @@
         <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
         <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1414,73 +1414,73 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
         <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1489,20 +1489,20 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1533,67 +1533,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="O6" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="P6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X6" t="n">
         <v>6.6</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X6" t="n">
-        <v>7.6</v>
-      </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1602,31 +1602,31 @@
         <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
         <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,19 +1641,19 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU6" t="n">
         <v>5.6</v>
@@ -1662,7 +1662,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -1671,32 +1671,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1727,49 +1727,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
         <v>1.8</v>
@@ -1778,7 +1778,7 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -1817,10 +1817,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,25 +1838,25 @@
         <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -1868,7 +1868,7 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
         <v>9.4</v>
@@ -1877,20 +1877,20 @@
         <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
         <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -1927,19 +1927,19 @@
         <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
         <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
@@ -1948,7 +1948,7 @@
         <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
         <v>1.53</v>
@@ -1966,13 +1966,13 @@
         <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>9.800000000000001</v>
@@ -2005,7 +2005,7 @@
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -2038,10 +2038,10 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2062,7 +2062,7 @@
         <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
         <v>4.5</v>
@@ -2074,17 +2074,17 @@
         <v>4.5</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I9" t="n">
         <v>2.3</v>
@@ -2181,13 +2181,13 @@
         <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
         <v>40</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,41 +2244,41 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.51</v>
@@ -2333,34 +2333,34 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
         <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
         <v>2.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
         <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
         <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
@@ -2369,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>130</v>
@@ -2384,10 +2384,10 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2399,19 +2399,19 @@
         <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>120</v>
@@ -2420,25 +2420,25 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
         <v>19.5</v>
@@ -2462,17 +2462,17 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3.75</v>
       </c>
       <c r="H11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I11" t="n">
         <v>2.46</v>
@@ -2518,34 +2518,34 @@
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
         <v>1.94</v>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AT11" t="n">
         <v>5</v>
@@ -2629,7 +2629,7 @@
         <v>4.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
         <v>21</v>
@@ -2638,10 +2638,10 @@
         <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
         <v>7.4</v>
@@ -2656,17 +2656,17 @@
         <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="G13" t="n">
         <v>4.1</v>
@@ -2900,13 +2900,13 @@
         <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J13" t="n">
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.46</v>
@@ -2933,13 +2933,13 @@
         <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
         <v>1.35</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.42</v>
       </c>
       <c r="G14" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -3097,7 +3097,7 @@
         <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
         <v>5.5</v>
@@ -3136,7 +3136,7 @@
         <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.29</v>
@@ -3309,140 +3309,140 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
         <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
         <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="n">
         <v>9.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR15" t="n">
         <v>32</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>16</v>
       </c>
-      <c r="AW15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ15" t="n">
+      <c r="BA15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC15" t="n">
         <v>15</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
         <v>25</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG15" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -3497,13 +3497,13 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
         <v>2.04</v>
@@ -3515,10 +3515,10 @@
         <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>2</v>
@@ -3533,10 +3533,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB16" t="n">
         <v>16</v>
@@ -3578,7 +3578,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3605,7 +3605,7 @@
         <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
@@ -3617,26 +3617,26 @@
         <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
         <v>11.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H17" t="n">
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.22</v>
@@ -3694,31 +3694,31 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT17" t="n">
         <v>8.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX17" t="n">
         <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I18" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.31</v>
@@ -3885,34 +3885,34 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
         <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3942,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3966,22 +3966,22 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
@@ -3990,41 +3990,41 @@
         <v>7.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -4058,167 +4058,167 @@
         <v>3.75</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="I19" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
         <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB19" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
         <v>18.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ19" t="n">
         <v>80</v>
       </c>
       <c r="AK19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
         <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BF19" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BG19" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.31</v>
@@ -4273,7 +4273,7 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
@@ -4297,10 +4297,10 @@
         <v>2.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -4348,7 +4348,7 @@
         <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
         <v>16</v>
@@ -4390,16 +4390,16 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
         <v>8</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H21" t="n">
         <v>3.2</v>
@@ -4455,10 +4455,10 @@
         <v>3.55</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
@@ -4467,16 +4467,16 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
@@ -4485,22 +4485,22 @@
         <v>4.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X21" t="n">
         <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4536,7 +4536,7 @@
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4554,7 +4554,7 @@
         <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AR21" t="n">
         <v>16.5</v>
@@ -4563,19 +4563,19 @@
         <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU21" t="n">
         <v>5.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW21" t="n">
         <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -4587,7 +4587,7 @@
         <v>7.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
         <v>6.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.31</v>
@@ -4664,13 +4664,13 @@
         <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
         <v>1.35</v>
@@ -4682,19 +4682,19 @@
         <v>1.72</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
         <v>26</v>
@@ -4703,13 +4703,13 @@
         <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
         <v>44</v>
@@ -4718,10 +4718,10 @@
         <v>18</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI22" t="n">
         <v>55</v>
@@ -4730,7 +4730,7 @@
         <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
@@ -4739,7 +4739,7 @@
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
         <v>40</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>40</v>
       </c>
       <c r="AT22" t="n">
         <v>9.199999999999999</v>
@@ -4766,7 +4766,7 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
         <v>13</v>
@@ -4778,29 +4778,29 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G23" t="n">
         <v>4.6</v>
@@ -4843,7 +4843,7 @@
         <v>1.88</v>
       </c>
       <c r="J23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
         <v>4.9</v>
@@ -4861,19 +4861,19 @@
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S23" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U23" t="n">
         <v>2.44</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4948,7 +4948,7 @@
         <v>11</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
         <v>17.5</v>
@@ -4957,44 +4957,44 @@
         <v>8.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
         <v>12.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G24" t="n">
         <v>3.05</v>
       </c>
-      <c r="G24" t="n">
-        <v>3.2</v>
-      </c>
       <c r="H24" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="I24" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -5049,67 +5049,67 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.62</v>
       </c>
-      <c r="T24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.54</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X24" t="n">
         <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
         <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>12</v>
       </c>
       <c r="AE24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI24" t="n">
         <v>32</v>
@@ -5118,40 +5118,40 @@
         <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL24" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR24" t="n">
         <v>15.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
         <v>20</v>
@@ -5163,10 +5163,10 @@
         <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>27</v>
@@ -5181,14 +5181,14 @@
         <v>29</v>
       </c>
       <c r="BF24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>7.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I25" t="n">
         <v>1.84</v>
@@ -5234,7 +5234,7 @@
         <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.24</v>
@@ -5243,7 +5243,7 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
@@ -5261,10 +5261,10 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="U25" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V25" t="n">
         <v>2.18</v>
@@ -5327,52 +5327,52 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP25" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="n">
         <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>1.51</v>
@@ -5446,7 +5446,7 @@
         <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R26" t="n">
         <v>1.17</v>
@@ -5458,16 +5458,16 @@
         <v>2.16</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V26" t="n">
         <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X26" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y26" t="n">
         <v>8.800000000000001</v>
@@ -5482,7 +5482,7 @@
         <v>8</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>15.5</v>
@@ -5503,7 +5503,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
         <v>55</v>
@@ -5521,7 +5521,7 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.8</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AX26" t="n">
         <v>14.5</v>
@@ -5554,29 +5554,29 @@
         <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J27" t="n">
         <v>3.25</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5634,10 +5634,10 @@
         <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
         <v>1.9</v>
@@ -5646,25 +5646,25 @@
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
         <v>2.18</v>
       </c>
       <c r="V27" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
         <v>19.5</v>
@@ -5691,7 +5691,7 @@
         <v>15.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
         <v>46</v>
@@ -5700,7 +5700,7 @@
         <v>60</v>
       </c>
       <c r="AK27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
@@ -5724,7 +5724,7 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT27" t="n">
         <v>9.800000000000001</v>
@@ -5742,35 +5742,35 @@
         <v>16.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC27" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC27" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF27" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>4.6</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="H28" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="K28" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L28" t="n">
         <v>1.5</v>
@@ -5825,46 +5825,46 @@
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P28" t="n">
         <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="T28" t="n">
         <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="X28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA28" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB28" t="n">
         <v>8.4</v>
@@ -5873,22 +5873,22 @@
         <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="n">
         <v>44</v>
@@ -5897,7 +5897,7 @@
         <v>40</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5909,16 +5909,16 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
         <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
@@ -5927,7 +5927,7 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>42</v>
@@ -5939,32 +5939,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BA28" t="n">
         <v>50</v>
       </c>
       <c r="BB28" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BC28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE28" t="n">
         <v>7.8</v>
       </c>
-      <c r="BD28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF28" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -5998,19 +5998,19 @@
         <v>1.82</v>
       </c>
       <c r="G29" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H29" t="n">
         <v>3.6</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.18</v>
@@ -6025,25 +6025,25 @@
         <v>1.11</v>
       </c>
       <c r="P29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T29" t="n">
         <v>1.36</v>
       </c>
       <c r="U29" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
         <v>2.02</v>
@@ -6052,7 +6052,7 @@
         <v>55</v>
       </c>
       <c r="Y29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
         <v>46</v>
@@ -6088,7 +6088,7 @@
         <v>28</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>25</v>
@@ -6097,22 +6097,22 @@
         <v>48</v>
       </c>
       <c r="AN29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO29" t="n">
         <v>20</v>
       </c>
       <c r="AP29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AR29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
         <v>17.5</v>
@@ -6124,7 +6124,7 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX29" t="n">
         <v>15</v>
@@ -6136,10 +6136,10 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,7 +6148,7 @@
         <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF29" t="n">
         <v>4.7</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="H30" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K30" t="n">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.32</v>
+        <v>5.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="R30" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="S30" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -6392,13 +6392,13 @@
         <v>2.48</v>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -6422,7 +6422,7 @@
         <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T31" t="n">
         <v>1.56</v>
@@ -6431,7 +6431,7 @@
         <v>2.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W31" t="n">
         <v>1.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -6586,55 +6586,55 @@
         <v>3.35</v>
       </c>
       <c r="I32" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J32" t="n">
         <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P32" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.96</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
         <v>1.69</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
         <v>1000</v>
@@ -6643,25 +6643,25 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6679,68 +6679,68 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -6771,64 +6771,64 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="G33" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="H33" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="J33" t="n">
         <v>3.35</v>
       </c>
       <c r="K33" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
         <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>1.78</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z33" t="n">
         <v>1000</v>
@@ -6837,25 +6837,25 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE33" t="n">
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
@@ -6864,7 +6864,7 @@
         <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
@@ -6873,68 +6873,68 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
         <v>4.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U34" t="n">
         <v>1.86</v>
@@ -7079,56 +7079,56 @@
         <v>6.8</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT34" t="n">
         <v>6.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -7159,91 +7159,91 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H35" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="J35" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.57</v>
+        <v>2.94</v>
       </c>
       <c r="O35" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P35" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S35" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V35" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
@@ -7264,65 +7264,65 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G36" t="n">
         <v>1.65</v>
@@ -7362,13 +7362,13 @@
         <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.39</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H37" t="n">
         <v>2.66</v>
       </c>
       <c r="I37" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.5</v>
@@ -7595,25 +7595,25 @@
         <v>1.93</v>
       </c>
       <c r="V37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X37" t="n">
         <v>12.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC37" t="n">
         <v>7.6</v>
@@ -7625,10 +7625,10 @@
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG37" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH37" t="n">
         <v>21</v>
@@ -7661,13 +7661,13 @@
         <v>7.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS37" t="n">
         <v>34</v>
       </c>
       <c r="AT37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU37" t="n">
         <v>6.2</v>
@@ -7676,41 +7676,41 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX37" t="n">
         <v>17</v>
       </c>
       <c r="AY37" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BB37" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BD37" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -7741,31 +7741,31 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="H38" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J38" t="n">
         <v>3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>1.45</v>
@@ -7774,61 +7774,61 @@
         <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R38" t="n">
         <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U38" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V38" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA38" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB38" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD38" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AF38" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG38" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ38" t="n">
         <v>40</v>
@@ -7837,74 +7837,74 @@
         <v>34</v>
       </c>
       <c r="AL38" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM38" t="n">
         <v>150</v>
       </c>
       <c r="AN38" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO38" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP38" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW38" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR38" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV38" t="n">
+      <c r="AX38" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>13</v>
-      </c>
       <c r="AY38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA38" t="n">
-        <v>48</v>
+        <v>9.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD38" t="n">
         <v>9</v>
       </c>
       <c r="BE38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG38" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -7935,25 +7935,25 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G39" t="n">
         <v>4.1</v>
       </c>
       <c r="H39" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="I39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K39" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
@@ -7968,28 +7968,28 @@
         <v>2.16</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R39" t="n">
         <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T39" t="n">
         <v>1.56</v>
       </c>
       <c r="U39" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V39" t="n">
         <v>1.84</v>
       </c>
       <c r="W39" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X39" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y39" t="n">
         <v>970</v>
@@ -8004,13 +8004,13 @@
         <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
         <v>970</v>
       </c>
       <c r="AE39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="n">
         <v>29</v>
@@ -8034,71 +8034,71 @@
         <v>46</v>
       </c>
       <c r="AM39" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN39" t="n">
         <v>40</v>
       </c>
       <c r="AO39" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AR39" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
         <v>9.4</v>
       </c>
       <c r="AW39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY39" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ39" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>2.12</v>
+        <v>2.98</v>
       </c>
       <c r="BC39" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE39" t="n">
         <v>2.98</v>
       </c>
-      <c r="BD39" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BF39" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BG39" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -8132,16 +8132,16 @@
         <v>2.42</v>
       </c>
       <c r="G40" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H40" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I40" t="n">
         <v>3.65</v>
       </c>
       <c r="J40" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K40" t="n">
         <v>3.25</v>
@@ -8162,7 +8162,7 @@
         <v>1.76</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8180,28 +8180,28 @@
         <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC40" t="n">
         <v>7</v>
       </c>
       <c r="AD40" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE40" t="n">
         <v>46</v>
@@ -8213,10 +8213,10 @@
         <v>11.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ40" t="n">
         <v>32</v>
@@ -8234,7 +8234,7 @@
         <v>25</v>
       </c>
       <c r="AO40" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP40" t="n">
         <v>10</v>
@@ -8255,7 +8255,7 @@
         <v>6.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW40" t="n">
         <v>40</v>
@@ -8270,16 +8270,16 @@
         <v>17</v>
       </c>
       <c r="BA40" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB40" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE40" t="n">
         <v>40</v>
@@ -8288,11 +8288,11 @@
         <v>23</v>
       </c>
       <c r="BG40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G41" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I41" t="n">
         <v>3.15</v>
@@ -8338,7 +8338,7 @@
         <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.63</v>
@@ -8347,16 +8347,16 @@
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P41" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
@@ -8365,22 +8365,22 @@
         <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U41" t="n">
         <v>1.77</v>
       </c>
       <c r="V41" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W41" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X41" t="n">
         <v>7.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z41" t="n">
         <v>18</v>
@@ -8389,7 +8389,7 @@
         <v>60</v>
       </c>
       <c r="AB41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC41" t="n">
         <v>7</v>
@@ -8422,7 +8422,7 @@
         <v>75</v>
       </c>
       <c r="AM41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN41" t="n">
         <v>55</v>
@@ -8464,7 +8464,7 @@
         <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BB41" t="n">
         <v>42</v>
@@ -8473,20 +8473,20 @@
         <v>38</v>
       </c>
       <c r="BD41" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE41" t="n">
         <v>48</v>
       </c>
       <c r="BF41" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG41" t="n">
         <v>55</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G42" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H42" t="n">
         <v>6.2</v>
@@ -8547,10 +8547,10 @@
         <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R42" t="n">
         <v>1.48</v>
@@ -8559,7 +8559,7 @@
         <v>2.98</v>
       </c>
       <c r="T42" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U42" t="n">
         <v>2.14</v>
@@ -8583,7 +8583,7 @@
         <v>170</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC42" t="n">
         <v>9.800000000000001</v>
@@ -8592,7 +8592,7 @@
         <v>23</v>
       </c>
       <c r="AE42" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF42" t="n">
         <v>9.800000000000001</v>
@@ -8619,13 +8619,13 @@
         <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO42" t="n">
         <v>90</v>
       </c>
       <c r="AP42" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ42" t="n">
         <v>21</v>
@@ -8634,10 +8634,10 @@
         <v>42</v>
       </c>
       <c r="AS42" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AT42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU42" t="n">
         <v>9.6</v>
@@ -8649,7 +8649,7 @@
         <v>65</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY42" t="n">
         <v>9.199999999999999</v>
@@ -8670,7 +8670,7 @@
         <v>28</v>
       </c>
       <c r="BE42" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF42" t="n">
         <v>7.6</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O43" t="n">
         <v>1.46</v>
@@ -8744,7 +8744,7 @@
         <v>1.65</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -8753,10 +8753,10 @@
         <v>4.6</v>
       </c>
       <c r="T43" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U43" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V43" t="n">
         <v>1.89</v>
@@ -8786,7 +8786,7 @@
         <v>12.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF43" t="n">
         <v>32</v>
@@ -8828,7 +8828,7 @@
         <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
         <v>11</v>
@@ -8855,26 +8855,26 @@
         <v>42</v>
       </c>
       <c r="BB43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD43" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC43" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>7</v>
-      </c>
       <c r="BE43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF43" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG43" t="n">
         <v>16</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
@@ -8953,13 +8953,13 @@
         <v>1.73</v>
       </c>
       <c r="V44" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W44" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y44" t="n">
         <v>10</v>
@@ -8974,10 +8974,10 @@
         <v>9.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
@@ -9022,10 +9022,10 @@
         <v>13</v>
       </c>
       <c r="AS44" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU44" t="n">
         <v>5.5</v>
@@ -9034,7 +9034,7 @@
         <v>12.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AX44" t="n">
         <v>13</v>
@@ -9049,10 +9049,10 @@
         <v>55</v>
       </c>
       <c r="BB44" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC44" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BD44" t="n">
         <v>50</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -9102,16 +9102,16 @@
         <v>2.52</v>
       </c>
       <c r="G45" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H45" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I45" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K45" t="n">
         <v>3.1</v>
@@ -9123,7 +9123,7 @@
         <v>1.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O45" t="n">
         <v>1.63</v>
@@ -9147,13 +9147,13 @@
         <v>1.71</v>
       </c>
       <c r="V45" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W45" t="n">
         <v>1.59</v>
       </c>
       <c r="X45" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y45" t="n">
         <v>11</v>
@@ -9189,7 +9189,7 @@
         <v>120</v>
       </c>
       <c r="AJ45" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK45" t="n">
         <v>50</v>
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -9228,7 +9228,7 @@
         <v>14.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX45" t="n">
         <v>13</v>
@@ -9243,26 +9243,26 @@
         <v>5.2</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC45" t="n">
         <v>4.9</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE45" t="n">
         <v>5.3</v>
       </c>
       <c r="BF45" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG45" t="n">
         <v>5.2</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -9332,13 +9332,13 @@
         <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V46" t="n">
         <v>1.26</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G47" t="n">
         <v>2.24</v>
       </c>
       <c r="H47" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>2.92</v>
@@ -9511,7 +9511,7 @@
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="O47" t="n">
         <v>1.46</v>
@@ -9535,10 +9535,10 @@
         <v>1.66</v>
       </c>
       <c r="V47" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W47" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X47" t="n">
         <v>12</v>
@@ -9568,7 +9568,7 @@
         <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH47" t="n">
         <v>1000</v>
@@ -9601,10 +9601,10 @@
         <v>9.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS47" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT47" t="n">
         <v>5.4</v>
@@ -9616,10 +9616,10 @@
         <v>14</v>
       </c>
       <c r="AW47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY47" t="n">
         <v>8.199999999999999</v>
@@ -9628,13 +9628,13 @@
         <v>16.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB47" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC47" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD47" t="n">
         <v>36</v>
@@ -9643,14 +9643,14 @@
         <v>120</v>
       </c>
       <c r="BF47" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG47" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -9684,19 +9684,19 @@
         <v>1.86</v>
       </c>
       <c r="G48" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J48" t="n">
         <v>3.4</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L48" t="n">
         <v>1.46</v>
@@ -9729,10 +9729,10 @@
         <v>1.74</v>
       </c>
       <c r="V48" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X48" t="n">
         <v>10</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G49" t="n">
         <v>1.75</v>
@@ -9884,13 +9884,13 @@
         <v>6.6</v>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L49" t="n">
         <v>1.48</v>
@@ -9914,7 +9914,7 @@
         <v>1.25</v>
       </c>
       <c r="S49" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="T49" t="n">
         <v>1.98</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -10457,170 +10457,170 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="G52" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="H52" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M52" t="n">
         <v>1.09</v>
       </c>
-      <c r="K52" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N52" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="O52" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P52" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S52" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V52" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM52" t="n">
         <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H53" t="n">
         <v>8.800000000000001</v>
@@ -10672,10 +10672,10 @@
         <v>1.46</v>
       </c>
       <c r="M53" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -10702,7 +10702,7 @@
         <v>1.1</v>
       </c>
       <c r="W53" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X53" t="n">
         <v>11.5</v>
@@ -10814,201 +10814,395 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-12 13:55:00</t>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CD Victoria</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Atletico Choloma</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>22:10:00</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Envigado</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F55" t="n">
         <v>3.05</v>
       </c>
-      <c r="G54" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H54" t="n">
+      <c r="G55" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
         <v>2.38</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>2.8</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>2.8</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K55" t="n">
         <v>3.6</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L55" t="n">
         <v>1.39</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M55" t="n">
         <v>1.09</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N55" t="n">
         <v>3.05</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O55" t="n">
         <v>1.39</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P55" t="n">
         <v>1.69</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q55" t="n">
         <v>2.16</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R55" t="n">
         <v>1.26</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S55" t="n">
         <v>3.6</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T55" t="n">
         <v>1.72</v>
       </c>
-      <c r="U54" t="n">
+      <c r="U55" t="n">
         <v>1.81</v>
       </c>
-      <c r="V54" t="n">
+      <c r="V55" t="n">
         <v>1.56</v>
       </c>
-      <c r="W54" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y54" t="n">
+      <c r="W55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y55" t="n">
         <v>11</v>
       </c>
-      <c r="Z54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC54" t="n">
+      <c r="Z55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC55" t="n">
         <v>9</v>
       </c>
-      <c r="AD54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP54" t="n">
+      <c r="AD55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP55" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AQ55" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AR55" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AS55" t="n">
         <v>27</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AT55" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AU55" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AV55" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AW55" t="n">
         <v>22</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AX55" t="n">
         <v>16</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="AY55" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="AZ55" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BA55" t="n">
         <v>34</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BB55" t="n">
         <v>42</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BC55" t="n">
         <v>30</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BD55" t="n">
         <v>40</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BE55" t="n">
         <v>85</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BF55" t="n">
         <v>32</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BG55" t="n">
         <v>20</v>
       </c>
-      <c r="BH54" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:55:00</t>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:11:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -763,16 +763,16 @@
         <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.47</v>
@@ -781,16 +781,16 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -802,10 +802,10 @@
         <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -844,7 +844,7 @@
         <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>200</v>
@@ -865,7 +865,7 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.5</v>
@@ -874,13 +874,13 @@
         <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AV2" t="n">
         <v>8.4</v>
@@ -889,28 +889,28 @@
         <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
         <v>5.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC2" t="n">
         <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
         <v>5.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -960,13 +960,13 @@
         <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
@@ -999,7 +999,7 @@
         <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
         <v>1.35</v>
@@ -1041,7 +1041,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
@@ -1053,13 +1053,13 @@
         <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA3" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
         <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1211,10 +1211,10 @@
         <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
         <v>15</v>
@@ -1229,7 +1229,7 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
@@ -1250,10 +1250,10 @@
         <v>44</v>
       </c>
       <c r="AO4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.4</v>
@@ -1262,19 +1262,19 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
         <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
@@ -1354,7 +1354,7 @@
         <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1366,7 +1366,7 @@
         <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.28</v>
@@ -1375,7 +1375,7 @@
         <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
         <v>2.64</v>
@@ -1390,7 +1390,7 @@
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H6" t="n">
         <v>3.15</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.2</v>
       </c>
       <c r="I6" t="n">
         <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
         <v>2.96</v>
@@ -1557,16 +1557,16 @@
         <v>1.17</v>
       </c>
       <c r="N6" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="O6" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1575,10 +1575,10 @@
         <v>7.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
         <v>1.36</v>
@@ -1590,7 +1590,7 @@
         <v>6.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
         <v>25</v>
@@ -1614,7 +1614,7 @@
         <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
         <v>38</v>
@@ -1650,53 +1650,53 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BE6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>8.6</v>
       </c>
-      <c r="I7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
         <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
         <v>2.84</v>
@@ -1945,22 +1945,22 @@
         <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
         <v>2.1</v>
@@ -1969,7 +1969,7 @@
         <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
         <v>1.61</v>
@@ -2050,7 +2050,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>40</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2062,16 +2062,16 @@
         <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BC8" t="n">
         <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -2169,7 +2169,7 @@
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y9" t="n">
         <v>6.4</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,41 +2244,41 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC9" t="n">
         <v>8</v>
       </c>
-      <c r="BC9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF9" t="n">
-        <v>8</v>
-      </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G10" t="n">
         <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>3.65</v>
@@ -2342,7 +2342,7 @@
         <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
@@ -2357,10 +2357,10 @@
         <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
@@ -2423,10 +2423,10 @@
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2438,7 +2438,7 @@
         <v>16.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.4</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2465,14 +2465,14 @@
         <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG10" t="n">
         <v>5.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -2530,7 +2530,7 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.67</v>
@@ -2542,22 +2542,22 @@
         <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
@@ -2611,7 +2611,7 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>7</v>
@@ -2620,53 +2620,53 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="AX11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8</v>
-      </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2853,14 +2853,14 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
         <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I13" t="n">
         <v>2.76</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
@@ -2936,10 +2936,10 @@
         <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
         <v>1.35</v>
@@ -3005,56 +3005,56 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="G14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K14" t="n">
         <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3112,31 +3112,31 @@
         <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
         <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
         <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -3199,10 +3199,10 @@
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>7.8</v>
@@ -3214,7 +3214,7 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -3226,7 +3226,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>80</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
         <v>1.81</v>
@@ -3288,7 +3288,7 @@
         <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -3297,7 +3297,7 @@
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3309,22 +3309,22 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
         <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
         <v>1.23</v>
@@ -3339,7 +3339,7 @@
         <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
         <v>120</v>
@@ -3381,7 +3381,7 @@
         <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO15" t="n">
         <v>65</v>
@@ -3393,7 +3393,7 @@
         <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
         <v>13.5</v>
@@ -3417,13 +3417,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
         <v>44</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>15</v>
@@ -3432,17 +3432,17 @@
         <v>25</v>
       </c>
       <c r="BE15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF15" t="n">
         <v>8</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
@@ -3491,19 +3491,19 @@
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>2.04</v>
@@ -3515,13 +3515,13 @@
         <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
@@ -3623,7 +3623,7 @@
         <v>50</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE16" t="n">
         <v>9.199999999999999</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G17" t="n">
         <v>1.36</v>
@@ -3679,7 +3679,7 @@
         <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K17" t="n">
         <v>6.8</v>
@@ -3691,13 +3691,13 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -3718,7 +3718,7 @@
         <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3790,7 +3790,7 @@
         <v>8.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>5</v>
@@ -3805,7 +3805,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
         <v>5.4</v>
@@ -3814,7 +3814,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BD17" t="n">
         <v>4.9</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -3861,80 +3861,80 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J18" t="n">
         <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>12</v>
-      </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS18" t="n">
         <v>10.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>7.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY18" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY18" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4082,28 +4082,28 @@
         <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
         <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
         <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
         <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W19" t="n">
         <v>1.33</v>
@@ -4112,22 +4112,22 @@
         <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" t="n">
         <v>25</v>
       </c>
       <c r="AB19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -4136,7 +4136,7 @@
         <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
         <v>16</v>
@@ -4169,7 +4169,7 @@
         <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
         <v>19.5</v>
@@ -4193,10 +4193,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
@@ -4211,14 +4211,14 @@
         <v>34</v>
       </c>
       <c r="BF19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G20" t="n">
         <v>2.44</v>
@@ -4294,7 +4294,7 @@
         <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V20" t="n">
         <v>1.47</v>
@@ -4333,7 +4333,7 @@
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>38</v>
@@ -4351,13 +4351,13 @@
         <v>65</v>
       </c>
       <c r="AN20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO20" t="n">
         <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>13</v>
@@ -4366,7 +4366,7 @@
         <v>19.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -4378,7 +4378,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
         <v>15</v>
@@ -4390,29 +4390,29 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
         <v>11.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
         <v>2.58</v>
@@ -4470,10 +4470,10 @@
         <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>2.2</v>
@@ -4563,7 +4563,7 @@
         <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
         <v>5.9</v>
@@ -4581,7 +4581,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
         <v>7.2</v>
@@ -4599,14 +4599,14 @@
         <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BG21" t="n">
         <v>7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
         <v>2.38</v>
@@ -4646,13 +4646,13 @@
         <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>1.31</v>
@@ -4670,28 +4670,28 @@
         <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
         <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.72</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="X22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
         <v>15</v>
@@ -4703,10 +4703,10 @@
         <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD22" t="n">
         <v>15.5</v>
@@ -4715,10 +4715,10 @@
         <v>44</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>19.5</v>
@@ -4727,7 +4727,7 @@
         <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
         <v>27</v>
@@ -4739,7 +4739,7 @@
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO22" t="n">
         <v>40</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="AT22" t="n">
         <v>9.199999999999999</v>
@@ -4763,16 +4763,16 @@
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
         <v>28</v>
       </c>
       <c r="AX22" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
@@ -4781,26 +4781,26 @@
         <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD22" t="n">
         <v>30</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
         <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -4837,13 +4837,13 @@
         <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I23" t="n">
         <v>1.88</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
         <v>4.9</v>
@@ -4867,7 +4867,7 @@
         <v>1.51</v>
       </c>
       <c r="R23" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S23" t="n">
         <v>2.3</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4939,46 +4939,46 @@
         <v>8.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS23" t="n">
         <v>17</v>
       </c>
       <c r="AT23" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>4.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB23" t="n">
         <v>4.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD23" t="n">
         <v>4.8</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G24" t="n">
         <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I24" t="n">
         <v>2.52</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
         <v>3.85</v>
@@ -5049,52 +5049,52 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S24" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="T24" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W24" t="n">
         <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA24" t="n">
         <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
         <v>12</v>
@@ -5103,52 +5103,52 @@
         <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
         <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS24" t="n">
         <v>20</v>
       </c>
-      <c r="AO24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>21</v>
-      </c>
       <c r="AT24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>10.5</v>
@@ -5160,25 +5160,25 @@
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BC24" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
         <v>17</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -5219,94 +5219,94 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G25" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="I25" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="T25" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB25" t="n">
         <v>30</v>
       </c>
-      <c r="Y25" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>32</v>
-      </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
         <v>60</v>
       </c>
       <c r="AG25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -5321,68 +5321,68 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J26" t="n">
         <v>2.84</v>
@@ -5458,19 +5458,19 @@
         <v>2.16</v>
       </c>
       <c r="U26" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X26" t="n">
         <v>7.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
         <v>21</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
         <v>14.5</v>
@@ -5554,29 +5554,29 @@
         <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -5610,40 +5610,40 @@
         <v>2.96</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H27" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I27" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
         <v>3.4</v>
@@ -5652,13 +5652,13 @@
         <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
         <v>1.58</v>
       </c>
       <c r="W27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X27" t="n">
         <v>16</v>
@@ -5676,7 +5676,7 @@
         <v>14.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>13.5</v>
@@ -5712,7 +5712,7 @@
         <v>36</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
@@ -5724,7 +5724,7 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT27" t="n">
         <v>9.800000000000001</v>
@@ -5748,29 +5748,29 @@
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE27" t="n">
         <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -5804,76 +5804,76 @@
         <v>2.32</v>
       </c>
       <c r="G28" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P28" t="n">
         <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="X28" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA28" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>75</v>
@@ -5882,19 +5882,19 @@
         <v>16</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ28" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL28" t="n">
         <v>60</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>42</v>
+        <v>5.3</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BA28" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G29" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
         <v>4</v>
@@ -6010,7 +6010,7 @@
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="L29" t="n">
         <v>1.18</v>
@@ -6028,16 +6028,16 @@
         <v>3.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="T29" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="U29" t="n">
         <v>3.05</v>
@@ -6046,7 +6046,7 @@
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X29" t="n">
         <v>55</v>
@@ -6058,13 +6058,13 @@
         <v>46</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD29" t="n">
         <v>20</v>
@@ -6085,13 +6085,13 @@
         <v>36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
         <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM29" t="n">
         <v>48</v>
@@ -6103,19 +6103,19 @@
         <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU29" t="n">
         <v>10</v>
@@ -6124,10 +6124,10 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY29" t="n">
         <v>9.4</v>
@@ -6136,10 +6136,10 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,17 +6148,17 @@
         <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG29" t="n">
         <v>13</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J30" t="n">
         <v>3.95</v>
@@ -6222,7 +6222,7 @@
         <v>2.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R30" t="n">
         <v>1.65</v>
@@ -6297,10 +6297,10 @@
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>3.6</v>
       </c>
       <c r="AR30" t="n">
         <v>19.5</v>
@@ -6324,7 +6324,7 @@
         <v>13</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
         <v>11</v>
@@ -6336,7 +6336,7 @@
         <v>3.75</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="BD30" t="n">
         <v>19</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G31" t="n">
         <v>2.98</v>
       </c>
       <c r="H31" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J31" t="n">
         <v>3.7</v>
@@ -6413,7 +6413,7 @@
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
         <v>1.63</v>
@@ -6434,7 +6434,7 @@
         <v>1.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X31" t="n">
         <v>23</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G32" t="n">
         <v>2.44</v>
       </c>
       <c r="H32" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I32" t="n">
         <v>3.85</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
         <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -6783,13 +6783,13 @@
         <v>5.7</v>
       </c>
       <c r="J33" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
         <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -6810,7 +6810,7 @@
         <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
         <v>1.7</v>
@@ -6861,7 +6861,7 @@
         <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK33" t="n">
         <v>23</v>
@@ -6879,13 +6879,13 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
         <v>5</v>
@@ -6897,13 +6897,13 @@
         <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY33" t="n">
         <v>8</v>
@@ -6918,10 +6918,10 @@
         <v>16</v>
       </c>
       <c r="BC33" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE33" t="n">
         <v>5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G34" t="n">
         <v>3.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I34" t="n">
         <v>3.1</v>
@@ -7019,7 +7019,7 @@
         <v>1.47</v>
       </c>
       <c r="X34" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y34" t="n">
         <v>970</v>
@@ -7088,7 +7088,7 @@
         <v>6.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AV34" t="n">
         <v>9.800000000000001</v>
@@ -7118,7 +7118,7 @@
         <v>6.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.26</v>
+        <v>3.85</v>
       </c>
       <c r="BF34" t="n">
         <v>6</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>3.25</v>
       </c>
       <c r="G35" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="H35" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I35" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="J35" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L35" t="n">
         <v>1.44</v>
@@ -7192,13 +7192,13 @@
         <v>1.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
         <v>1.24</v>
       </c>
       <c r="S35" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
         <v>1.92</v>
@@ -7207,10 +7207,10 @@
         <v>1.92</v>
       </c>
       <c r="V35" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="W35" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X35" t="n">
         <v>12</v>
@@ -7270,59 +7270,59 @@
         <v>8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT35" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX35" t="n">
         <v>17</v>
       </c>
       <c r="AY35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB35" t="n">
         <v>4.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
         <v>5</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
         <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB36" t="n">
         <v>12.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G37" t="n">
         <v>3.35</v>
@@ -7556,13 +7556,13 @@
         <v>2.66</v>
       </c>
       <c r="I37" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.5</v>
@@ -7598,7 +7598,7 @@
         <v>1.54</v>
       </c>
       <c r="W37" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X37" t="n">
         <v>12.5</v>
@@ -7625,10 +7625,10 @@
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG37" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH37" t="n">
         <v>21</v>
@@ -7676,7 +7676,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX37" t="n">
         <v>17</v>
@@ -7685,32 +7685,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC37" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -7741,70 +7741,70 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G38" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I38" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J38" t="n">
         <v>3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P38" t="n">
         <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R38" t="n">
         <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T38" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U38" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X38" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA38" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB38" t="n">
         <v>8.4</v>
@@ -7813,98 +7813,98 @@
         <v>7</v>
       </c>
       <c r="AD38" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE38" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK38" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL38" t="n">
         <v>50</v>
       </c>
       <c r="AM38" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO38" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP38" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY38" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR38" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA38" t="n">
         <v>17</v>
       </c>
-      <c r="BA38" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BB38" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BC38" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BD38" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BE38" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BF38" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="BG38" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G39" t="n">
         <v>4.1</v>
       </c>
       <c r="H39" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I39" t="n">
         <v>2.2</v>
@@ -7950,7 +7950,7 @@
         <v>3.45</v>
       </c>
       <c r="K39" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L39" t="n">
         <v>1.34</v>
@@ -7968,28 +7968,28 @@
         <v>2.16</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T39" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U39" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V39" t="n">
         <v>1.84</v>
       </c>
       <c r="W39" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X39" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="Y39" t="n">
         <v>970</v>
@@ -8004,7 +8004,7 @@
         <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
         <v>970</v>
@@ -8040,22 +8040,22 @@
         <v>40</v>
       </c>
       <c r="AO39" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AP39" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR39" t="n">
         <v>12.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU39" t="n">
         <v>6.6</v>
@@ -8064,41 +8064,41 @@
         <v>9.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX39" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AY39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ39" t="n">
         <v>11.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>2.98</v>
+        <v>10</v>
       </c>
       <c r="BC39" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BF39" t="n">
         <v>24</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G40" t="n">
         <v>2.42</v>
       </c>
-      <c r="G40" t="n">
-        <v>2.44</v>
-      </c>
       <c r="H40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>3.2</v>
@@ -8159,7 +8159,7 @@
         <v>1.42</v>
       </c>
       <c r="P40" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
         <v>2.28</v>
@@ -8171,16 +8171,16 @@
         <v>4.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U40" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V40" t="n">
         <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
@@ -8288,11 +8288,11 @@
         <v>23</v>
       </c>
       <c r="BG40" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="G41" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
         <v>3.05</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.63</v>
@@ -8347,43 +8347,43 @@
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O41" t="n">
         <v>1.6</v>
       </c>
       <c r="P41" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U41" t="n">
         <v>1.77</v>
       </c>
       <c r="V41" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W41" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X41" t="n">
         <v>7.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA41" t="n">
         <v>60</v>
@@ -8437,7 +8437,7 @@
         <v>8</v>
       </c>
       <c r="AR41" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS41" t="n">
         <v>50</v>
@@ -8464,7 +8464,7 @@
         <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB41" t="n">
         <v>42</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -8529,10 +8529,10 @@
         <v>6.4</v>
       </c>
       <c r="J42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K42" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.6</v>
       </c>
       <c r="L42" t="n">
         <v>1.35</v>
@@ -8547,28 +8547,28 @@
         <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R42" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T42" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U42" t="n">
         <v>2.14</v>
       </c>
       <c r="V42" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X42" t="n">
         <v>19.5</v>
@@ -8583,7 +8583,7 @@
         <v>170</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC42" t="n">
         <v>9.800000000000001</v>
@@ -8592,16 +8592,16 @@
         <v>23</v>
       </c>
       <c r="AE42" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG42" t="n">
         <v>9.6</v>
       </c>
       <c r="AH42" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI42" t="n">
         <v>75</v>
@@ -8610,7 +8610,7 @@
         <v>15.5</v>
       </c>
       <c r="AK42" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL42" t="n">
         <v>30</v>
@@ -8631,28 +8631,28 @@
         <v>21</v>
       </c>
       <c r="AR42" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS42" t="n">
         <v>140</v>
       </c>
       <c r="AT42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV42" t="n">
         <v>21</v>
       </c>
       <c r="AW42" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
         <v>19</v>
@@ -8673,14 +8673,14 @@
         <v>90</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG42" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -8717,13 +8717,13 @@
         <v>4.7</v>
       </c>
       <c r="H43" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I43" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J43" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K43" t="n">
         <v>3.45</v>
@@ -8735,7 +8735,7 @@
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>1.46</v>
@@ -8744,22 +8744,22 @@
         <v>1.65</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
       </c>
       <c r="S43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T43" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U43" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V43" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W43" t="n">
         <v>1.27</v>
@@ -8768,10 +8768,10 @@
         <v>10.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA43" t="n">
         <v>32</v>
@@ -8786,7 +8786,7 @@
         <v>12.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF43" t="n">
         <v>32</v>
@@ -8828,7 +8828,7 @@
         <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT43" t="n">
         <v>11</v>
@@ -8840,7 +8840,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW43" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX43" t="n">
         <v>27</v>
@@ -8855,26 +8855,26 @@
         <v>42</v>
       </c>
       <c r="BB43" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC43" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD43" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF43" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG43" t="n">
         <v>16</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G44" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
@@ -8917,22 +8917,22 @@
         <v>3.25</v>
       </c>
       <c r="J44" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K44" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N44" t="n">
         <v>2.5</v>
       </c>
       <c r="O44" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P44" t="n">
         <v>1.46</v>
@@ -8944,7 +8944,7 @@
         <v>1.16</v>
       </c>
       <c r="S44" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T44" t="n">
         <v>2.18</v>
@@ -8956,13 +8956,13 @@
         <v>1.45</v>
       </c>
       <c r="W44" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X44" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
@@ -8971,13 +8971,13 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
@@ -8986,7 +8986,7 @@
         <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH44" t="n">
         <v>1000</v>
@@ -9013,10 +9013,10 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR44" t="n">
         <v>13</v>
@@ -9025,19 +9025,19 @@
         <v>32</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW44" t="n">
         <v>30</v>
       </c>
       <c r="AX44" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY44" t="n">
         <v>12</v>
@@ -9049,26 +9049,26 @@
         <v>55</v>
       </c>
       <c r="BB44" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BC44" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BD44" t="n">
         <v>50</v>
       </c>
       <c r="BE44" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG44" t="n">
         <v>29</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -9102,16 +9102,16 @@
         <v>2.52</v>
       </c>
       <c r="G45" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H45" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J45" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K45" t="n">
         <v>3.1</v>
@@ -9129,10 +9129,10 @@
         <v>1.63</v>
       </c>
       <c r="P45" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R45" t="n">
         <v>1.16</v>
@@ -9150,7 +9150,7 @@
         <v>1.37</v>
       </c>
       <c r="W45" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X45" t="n">
         <v>9.4</v>
@@ -9159,19 +9159,19 @@
         <v>11</v>
       </c>
       <c r="Z45" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA45" t="n">
         <v>100</v>
       </c>
       <c r="AB45" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE45" t="n">
         <v>80</v>
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -9228,7 +9228,7 @@
         <v>14.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX45" t="n">
         <v>13</v>
@@ -9237,32 +9237,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -9293,19 +9293,19 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H46" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K46" t="n">
         <v>3.55</v>
@@ -9317,13 +9317,13 @@
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
         <v>1.45</v>
       </c>
       <c r="P46" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q46" t="n">
         <v>2.32</v>
@@ -9332,19 +9332,19 @@
         <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V46" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W46" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X46" t="n">
         <v>11.5</v>
@@ -9368,10 +9368,10 @@
         <v>21</v>
       </c>
       <c r="AE46" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF46" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG46" t="n">
         <v>13</v>
@@ -9380,13 +9380,13 @@
         <v>26</v>
       </c>
       <c r="AI46" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ46" t="n">
         <v>34</v>
       </c>
       <c r="AK46" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL46" t="n">
         <v>60</v>
@@ -9395,22 +9395,22 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ46" t="n">
         <v>9.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="AS46" t="n">
-        <v>75</v>
+        <v>5.4</v>
       </c>
       <c r="AT46" t="n">
         <v>5.8</v>
@@ -9422,7 +9422,7 @@
         <v>13.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>50</v>
+        <v>5.1</v>
       </c>
       <c r="AX46" t="n">
         <v>9.4</v>
@@ -9434,7 +9434,7 @@
         <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>60</v>
+        <v>5.2</v>
       </c>
       <c r="BB46" t="n">
         <v>21</v>
@@ -9443,20 +9443,20 @@
         <v>21</v>
       </c>
       <c r="BD46" t="n">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>120</v>
+        <v>5.4</v>
       </c>
       <c r="BF46" t="n">
         <v>18.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>70</v>
+        <v>5.3</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="G47" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="H47" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K47" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="O47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P47" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S47" t="n">
         <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="U47" t="n">
         <v>1.66</v>
       </c>
       <c r="V47" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W47" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="X47" t="n">
         <v>12</v>
@@ -9553,7 +9553,7 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC47" t="n">
         <v>9.199999999999999</v>
@@ -9565,10 +9565,10 @@
         <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
         <v>1000</v>
@@ -9598,25 +9598,25 @@
         <v>7.2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="AR47" t="n">
-        <v>23</v>
+        <v>4.2</v>
       </c>
       <c r="AS47" t="n">
-        <v>80</v>
+        <v>4.6</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU47" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="AW47" t="n">
-        <v>50</v>
+        <v>4.5</v>
       </c>
       <c r="AX47" t="n">
         <v>8.6</v>
@@ -9625,32 +9625,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ47" t="n">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA47" t="n">
-        <v>60</v>
+        <v>4.5</v>
       </c>
       <c r="BB47" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="BC47" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD47" t="n">
-        <v>36</v>
+        <v>4.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>120</v>
+        <v>4.6</v>
       </c>
       <c r="BF47" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="BG47" t="n">
-        <v>75</v>
+        <v>4.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
@@ -9693,7 +9693,7 @@
         <v>5.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K48" t="n">
         <v>3.6</v>
@@ -9720,10 +9720,10 @@
         <v>1.21</v>
       </c>
       <c r="S48" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U48" t="n">
         <v>1.74</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G49" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H49" t="n">
         <v>6.6</v>
       </c>
       <c r="I49" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K49" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L49" t="n">
         <v>1.48</v>
@@ -9917,16 +9917,16 @@
         <v>3.8</v>
       </c>
       <c r="T49" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U49" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="V49" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W49" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X49" t="n">
         <v>13.5</v>
@@ -9983,16 +9983,16 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ49" t="n">
         <v>13</v>
       </c>
       <c r="AR49" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>180</v>
+        <v>4.3</v>
       </c>
       <c r="AT49" t="n">
         <v>4.9</v>
@@ -10001,44 +10001,44 @@
         <v>6.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="AW49" t="n">
-        <v>95</v>
+        <v>4.2</v>
       </c>
       <c r="AX49" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY49" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ49" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA49" t="n">
-        <v>95</v>
+        <v>4.2</v>
       </c>
       <c r="BB49" t="n">
         <v>12</v>
       </c>
       <c r="BC49" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="BD49" t="n">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="BE49" t="n">
-        <v>140</v>
+        <v>4.2</v>
       </c>
       <c r="BF49" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="BG49" t="n">
-        <v>160</v>
+        <v>4.3</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -10177,52 +10177,52 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF50" t="n">
         <v>1.01</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.65</v>
       </c>
       <c r="G51" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H51" t="n">
         <v>4.2</v>
@@ -10275,7 +10275,7 @@
         <v>6.6</v>
       </c>
       <c r="J51" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K51" t="n">
         <v>4.7</v>
@@ -10293,7 +10293,7 @@
         <v>1.24</v>
       </c>
       <c r="P51" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q51" t="n">
         <v>1.72</v>
@@ -10311,10 +10311,10 @@
         <v>2.04</v>
       </c>
       <c r="V51" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W51" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10329,10 +10329,10 @@
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
         <v>1000</v>
@@ -10344,7 +10344,7 @@
         <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
         <v>1000</v>
@@ -10365,68 +10365,68 @@
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="AR51" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT51" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS51" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AU51" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AW51" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY51" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX51" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AZ51" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB51" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC51" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD51" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -10460,10 +10460,10 @@
         <v>2.24</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H52" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I52" t="n">
         <v>4.1</v>
@@ -10496,19 +10496,19 @@
         <v>1.26</v>
       </c>
       <c r="S52" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T52" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U52" t="n">
         <v>1.92</v>
       </c>
       <c r="V52" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W52" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X52" t="n">
         <v>14</v>
@@ -10526,7 +10526,7 @@
         <v>10.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD52" t="n">
         <v>19</v>
@@ -10565,62 +10565,62 @@
         <v>75</v>
       </c>
       <c r="AP52" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ52" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR52" t="n">
         <v>18.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT52" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU52" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>5.7</v>
       </c>
       <c r="AV52" t="n">
         <v>11.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX52" t="n">
         <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ52" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB52" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BC52" t="n">
         <v>20</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BF52" t="n">
         <v>17.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G53" t="n">
         <v>1.57</v>
@@ -10660,7 +10660,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J53" t="n">
         <v>3.9</v>
@@ -10675,13 +10675,13 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q53" t="n">
         <v>2.48</v>
@@ -10693,13 +10693,13 @@
         <v>5.1</v>
       </c>
       <c r="T53" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U53" t="n">
         <v>1.54</v>
       </c>
       <c r="V53" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W53" t="n">
         <v>2.74</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -10953,52 +10953,52 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H55" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J55" t="n">
         <v>2.8</v>
@@ -11057,28 +11057,28 @@
         <v>3.6</v>
       </c>
       <c r="L55" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M55" t="n">
         <v>1.09</v>
       </c>
       <c r="N55" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O55" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P55" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="R55" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S55" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T55" t="n">
         <v>1.72</v>
@@ -11087,10 +11087,10 @@
         <v>1.81</v>
       </c>
       <c r="V55" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W55" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11156,7 +11156,7 @@
         <v>11.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>27</v>
+        <v>3.95</v>
       </c>
       <c r="AT55" t="n">
         <v>8.199999999999999</v>
@@ -11168,7 +11168,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW55" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="AX55" t="n">
         <v>16</v>
@@ -11180,29 +11180,29 @@
         <v>13.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>34</v>
+        <v>3.95</v>
       </c>
       <c r="BB55" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="BC55" t="n">
-        <v>30</v>
+        <v>4.3</v>
       </c>
       <c r="BD55" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BE55" t="n">
-        <v>85</v>
+        <v>4.1</v>
       </c>
       <c r="BF55" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="BG55" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-12 16:11:06</t>
+          <t>2026-04-12 18:24:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -766,13 +766,13 @@
         <v>1.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.47</v>
@@ -802,10 +802,10 @@
         <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -823,13 +823,13 @@
         <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
         <v>32</v>
@@ -847,7 +847,7 @@
         <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>130</v>
@@ -859,7 +859,7 @@
         <v>280</v>
       </c>
       <c r="AN2" t="n">
-        <v>220</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -874,53 +874,53 @@
         <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
         <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>5.9</v>
       </c>
-      <c r="BF2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
         <v>3.85</v>
@@ -960,10 +960,10 @@
         <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>3.6</v>
@@ -981,13 +981,13 @@
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
         <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
         <v>3.85</v>
@@ -1026,7 +1026,7 @@
         <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>32</v>
@@ -1041,16 +1041,16 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>60</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
         <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -1154,16 +1154,16 @@
         <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
         <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1172,7 +1172,7 @@
         <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
         <v>1.58</v>
@@ -1193,13 +1193,13 @@
         <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1208,7 +1208,7 @@
         <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
         <v>9.4</v>
@@ -1229,7 +1229,7 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
@@ -1238,10 +1238,10 @@
         <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>7.6</v>
@@ -1274,7 +1274,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB4" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
         <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
         <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
         <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1396,37 +1396,37 @@
         <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AJ5" t="n">
         <v>22</v>
@@ -1435,28 +1435,28 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>9.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1480,7 +1480,7 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1489,20 +1489,20 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1551,13 +1551,13 @@
         <v>2.96</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
         <v>1.17</v>
       </c>
       <c r="N6" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
         <v>1.82</v>
@@ -1575,7 +1575,7 @@
         <v>7.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
         <v>1.52</v>
@@ -1587,13 +1587,13 @@
         <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Y6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1605,19 +1605,19 @@
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1626,7 +1626,7 @@
         <v>60</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1650,19 +1650,19 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -1671,32 +1671,32 @@
         <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="I7" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX7" t="n">
         <v>6.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
         <v>2.62</v>
@@ -1933,7 +1933,7 @@
         <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
         <v>3.05</v>
@@ -1942,10 +1942,10 @@
         <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.56</v>
@@ -1954,7 +1954,7 @@
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -1963,7 +1963,7 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
         <v>1.79</v>
@@ -1984,7 +1984,7 @@
         <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>9</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="AJ8" t="n">
         <v>48</v>
@@ -2017,16 +2017,16 @@
         <v>44</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AM8" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>48</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="AP8" t="n">
         <v>6.2</v>
@@ -2035,10 +2035,10 @@
         <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2059,32 +2059,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>28</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
         <v>4.6</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.7</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L9" t="n">
         <v>1.56</v>
@@ -2163,13 +2163,13 @@
         <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="n">
         <v>6.4</v>
@@ -2184,7 +2184,7 @@
         <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
@@ -2196,22 +2196,22 @@
         <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ9" t="n">
         <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AL9" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AM9" t="n">
         <v>360</v>
@@ -2220,19 +2220,19 @@
         <v>210</v>
       </c>
       <c r="AO9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,41 +2244,41 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG9" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2318,13 +2318,13 @@
         <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.51</v>
@@ -2333,16 +2333,16 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
@@ -2360,7 +2360,7 @@
         <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
@@ -2372,7 +2372,7 @@
         <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>8.6</v>
@@ -2381,22 +2381,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ10" t="n">
         <v>28</v>
@@ -2405,16 +2405,16 @@
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AM10" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="AP10" t="n">
         <v>9</v>
@@ -2423,19 +2423,19 @@
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
         <v>50</v>
@@ -2447,32 +2447,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
         <v>19.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -2551,34 +2551,34 @@
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W11" t="n">
         <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
@@ -2608,7 +2608,7 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>8.4</v>
@@ -2620,53 +2620,53 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2820,7 +2820,7 @@
         <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV12" t="n">
         <v>1.03</v>
@@ -2832,7 +2832,7 @@
         <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.03</v>
@@ -2853,14 +2853,14 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H13" t="n">
         <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
         <v>3.1</v>
@@ -2915,7 +2915,7 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.39</v>
@@ -2936,16 +2936,16 @@
         <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
         <v>1000</v>
@@ -2954,16 +2954,16 @@
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2975,13 +2975,13 @@
         <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR13" t="n">
         <v>7</v>
       </c>
-      <c r="AR13" t="n">
-        <v>4</v>
-      </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
         <v>1.55</v>
@@ -3094,7 +3094,7 @@
         <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.6</v>
@@ -3121,10 +3121,10 @@
         <v>1.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
         <v>1.79</v>
@@ -3133,16 +3133,16 @@
         <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
       </c>
       <c r="Y14" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,22 +3151,22 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>13.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -3175,13 +3175,13 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3196,13 +3196,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AT14" t="n">
         <v>7.8</v>
@@ -3211,10 +3211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -3226,7 +3226,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
         <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -3327,13 +3327,13 @@
         <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
         <v>22</v>
@@ -3348,7 +3348,7 @@
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>19</v>
@@ -3393,13 +3393,13 @@
         <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
         <v>8.199999999999999</v>
@@ -3408,7 +3408,7 @@
         <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
@@ -3423,7 +3423,7 @@
         <v>44</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC15" t="n">
         <v>15</v>
@@ -3432,17 +3432,17 @@
         <v>25</v>
       </c>
       <c r="BE15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG15" t="n">
         <v>13</v>
       </c>
-      <c r="BF15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>48</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I16" t="n">
         <v>1.97</v>
@@ -3491,19 +3491,19 @@
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
         <v>2.04</v>
@@ -3515,10 +3515,10 @@
         <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>2.02</v>
@@ -3548,7 +3548,7 @@
         <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF16" t="n">
         <v>36</v>
@@ -3569,10 +3569,10 @@
         <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>80</v>
@@ -3581,7 +3581,7 @@
         <v>15.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>7.2</v>
@@ -3605,7 +3605,7 @@
         <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
@@ -3617,7 +3617,7 @@
         <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC16" t="n">
         <v>50</v>
@@ -3626,17 +3626,17 @@
         <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
         <v>11.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.22</v>
@@ -3691,34 +3691,34 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3736,7 +3736,7 @@
         <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
         <v>1000</v>
@@ -3757,10 +3757,10 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3769,46 +3769,46 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
         <v>8.800000000000001</v>
@@ -3817,20 +3817,20 @@
         <v>10.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>5.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3915,28 +3915,28 @@
         <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AB18" t="n">
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD18" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
         <v>1000</v>
@@ -3966,7 +3966,7 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
@@ -3981,7 +3981,7 @@
         <v>10.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
@@ -3993,38 +3993,38 @@
         <v>12</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
         <v>6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>3.8</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I19" t="n">
         <v>2.04</v>
@@ -4079,7 +4079,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
@@ -4088,25 +4088,25 @@
         <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V19" t="n">
         <v>1.96</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
         <v>24</v>
@@ -4118,52 +4118,52 @@
         <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF19" t="n">
         <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="n">
         <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
         <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>10.5</v>
@@ -4172,34 +4172,34 @@
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
         <v>16.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX19" t="n">
         <v>19.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
         <v>32</v>
@@ -4208,7 +4208,7 @@
         <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
         <v>22</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.31</v>
@@ -4273,146 +4273,146 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
         <v>24</v>
       </c>
-      <c r="AA20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN20" t="n">
         <v>15.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU20" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AV20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY20" t="n">
         <v>11</v>
       </c>
-      <c r="AU20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
         <v>18.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4497,10 +4497,10 @@
         <v>1.63</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4515,25 +4515,25 @@
         <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK21" t="n">
         <v>32</v>
@@ -4554,13 +4554,13 @@
         <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR21" t="n">
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4569,13 +4569,13 @@
         <v>5.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -4584,29 +4584,29 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG21" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
         <v>3.5</v>
@@ -4652,10 +4652,10 @@
         <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -4667,10 +4667,10 @@
         <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
         <v>1.35</v>
@@ -4679,16 +4679,16 @@
         <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>18</v>
@@ -4706,7 +4706,7 @@
         <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>15.5</v>
@@ -4715,7 +4715,7 @@
         <v>44</v>
       </c>
       <c r="AF22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4733,10 +4733,10 @@
         <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN22" t="n">
         <v>19.5</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT22" t="n">
         <v>9.199999999999999</v>
@@ -4766,41 +4766,41 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
         <v>30</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF22" t="n">
         <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G23" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="I23" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="J23" t="n">
         <v>4.2</v>
@@ -4849,7 +4849,7 @@
         <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -4861,85 +4861,85 @@
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R23" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S23" t="n">
         <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U23" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V23" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Y23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE23" t="n">
         <v>17</v>
       </c>
-      <c r="AA23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AG23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>38</v>
+        <v>260</v>
       </c>
       <c r="AO23" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ23" t="n">
         <v>11.5</v>
@@ -4948,7 +4948,7 @@
         <v>12</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="AT23" t="n">
         <v>19.5</v>
@@ -4963,7 +4963,7 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY23" t="n">
         <v>15</v>
@@ -4972,29 +4972,29 @@
         <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
         <v>6.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -5025,100 +5025,100 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
         <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W24" t="n">
         <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="n">
         <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>12</v>
       </c>
       <c r="AE24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -5127,28 +5127,28 @@
         <v>70</v>
       </c>
       <c r="AN24" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
         <v>10.5</v>
@@ -5157,38 +5157,38 @@
         <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AY24" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
         <v>38</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G25" t="n">
         <v>6.6</v>
@@ -5228,10 +5228,10 @@
         <v>1.56</v>
       </c>
       <c r="I25" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
         <v>5.1</v>
@@ -5243,7 +5243,7 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O25" t="n">
         <v>1.2</v>
@@ -5258,7 +5258,7 @@
         <v>1.51</v>
       </c>
       <c r="S25" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
         <v>1.69</v>
@@ -5267,7 +5267,7 @@
         <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="W25" t="n">
         <v>1.17</v>
@@ -5285,7 +5285,7 @@
         <v>17</v>
       </c>
       <c r="AB25" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AC25" t="n">
         <v>11.5</v>
@@ -5297,7 +5297,7 @@
         <v>17</v>
       </c>
       <c r="AF25" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
@@ -5312,77 +5312,77 @@
         <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
         <v>7.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G26" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H26" t="n">
         <v>3.25</v>
@@ -5425,10 +5425,10 @@
         <v>3.45</v>
       </c>
       <c r="J26" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L26" t="n">
         <v>1.51</v>
@@ -5446,7 +5446,7 @@
         <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R26" t="n">
         <v>1.17</v>
@@ -5464,10 +5464,10 @@
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y26" t="n">
         <v>11</v>
@@ -5476,19 +5476,19 @@
         <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB26" t="n">
         <v>8</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
         <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
@@ -5497,19 +5497,19 @@
         <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
         <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK26" t="n">
         <v>55</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5530,19 +5530,19 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV26" t="n">
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
         <v>14.5</v>
@@ -5551,32 +5551,32 @@
         <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC26" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB26" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>7</v>
-      </c>
       <c r="BD26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
         <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z27" t="n">
         <v>19.5</v>
@@ -5697,7 +5697,7 @@
         <v>46</v>
       </c>
       <c r="AJ27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
         <v>40</v>
@@ -5706,7 +5706,7 @@
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>36</v>
@@ -5724,7 +5724,7 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT27" t="n">
         <v>9.800000000000001</v>
@@ -5748,29 +5748,29 @@
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -5804,28 +5804,28 @@
         <v>2.32</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
         <v>3.75</v>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
         <v>2.82</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O28" t="n">
         <v>1.51</v>
@@ -5855,49 +5855,49 @@
         <v>1.67</v>
       </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG28" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="AK28" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>460</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5909,16 +5909,16 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>9</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>6.4</v>
@@ -5930,7 +5930,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -5939,32 +5939,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.88</v>
       </c>
       <c r="G29" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H29" t="n">
         <v>3.85</v>
@@ -6052,7 +6052,7 @@
         <v>55</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Z29" t="n">
         <v>46</v>
@@ -6070,7 +6070,7 @@
         <v>20</v>
       </c>
       <c r="AE29" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -6085,7 +6085,7 @@
         <v>36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK29" t="n">
         <v>19</v>
@@ -6103,10 +6103,10 @@
         <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR29" t="n">
         <v>6</v>
@@ -6115,7 +6115,7 @@
         <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU29" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,7 +6148,7 @@
         <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
         <v>5.2</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -6243,10 +6243,10 @@
         <v>1.74</v>
       </c>
       <c r="X30" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Z30" t="n">
         <v>34</v>
@@ -6255,10 +6255,10 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
         <v>18</v>
@@ -6273,10 +6273,10 @@
         <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
         <v>34</v>
@@ -6288,25 +6288,25 @@
         <v>34</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR30" t="n">
         <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6318,7 +6318,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -6330,19 +6330,19 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD30" t="n">
         <v>19</v>
       </c>
       <c r="BE30" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
         <v>7.6</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>2.66</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K31" t="n">
         <v>4.2</v>
@@ -6407,28 +6407,28 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q31" t="n">
         <v>1.63</v>
       </c>
       <c r="R31" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S31" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T31" t="n">
         <v>1.56</v>
       </c>
       <c r="U31" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V31" t="n">
         <v>1.6</v>
@@ -6458,7 +6458,7 @@
         <v>13</v>
       </c>
       <c r="AE31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF31" t="n">
         <v>23</v>
@@ -6470,7 +6470,7 @@
         <v>16</v>
       </c>
       <c r="AI31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ31" t="n">
         <v>44</v>
@@ -6479,16 +6479,16 @@
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN31" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP31" t="n">
         <v>18.5</v>
@@ -6500,7 +6500,7 @@
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AT31" t="n">
         <v>13</v>
@@ -6524,19 +6524,19 @@
         <v>12.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BF31" t="n">
         <v>14</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
         <v>2.16</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
         <v>3.9</v>
@@ -6637,16 +6637,16 @@
         <v>12.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD32" t="n">
         <v>18.5</v>
@@ -6664,22 +6664,22 @@
         <v>24</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT32" t="n">
         <v>6.6</v>
@@ -6706,41 +6706,41 @@
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32" t="n">
         <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB32" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC32" t="n">
         <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF32" t="n">
         <v>17.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
         <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
         <v>1.7</v>
@@ -6867,10 +6867,10 @@
         <v>23</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
         <v>14.5</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AR33" t="n">
         <v>5</v>
       </c>
       <c r="AS33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW33" t="n">
         <v>5</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.9</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB33" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB33" t="n">
-        <v>16</v>
-      </c>
       <c r="BC33" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG33" t="n">
         <v>5</v>
       </c>
-      <c r="BE33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -7019,28 +7019,28 @@
         <v>1.47</v>
       </c>
       <c r="X34" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z34" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AA34" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC34" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD34" t="n">
         <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
@@ -7049,28 +7049,28 @@
         <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI34" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ34" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL34" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO34" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP34" t="n">
         <v>7.2</v>
@@ -7079,56 +7079,56 @@
         <v>6.8</v>
       </c>
       <c r="AR34" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT34" t="n">
         <v>6.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="AV34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW34" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AY34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB34" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC34" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="BF34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>2.4</v>
       </c>
       <c r="I35" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J35" t="n">
         <v>3.05</v>
@@ -7246,16 +7246,16 @@
         <v>23</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -7264,7 +7264,7 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP35" t="n">
         <v>8</v>
@@ -7276,7 +7276,7 @@
         <v>13</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AT35" t="n">
         <v>9.4</v>
@@ -7288,7 +7288,7 @@
         <v>10.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX35" t="n">
         <v>17</v>
@@ -7300,29 +7300,29 @@
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -7407,16 +7407,16 @@
         <v>2.52</v>
       </c>
       <c r="X36" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y36" t="n">
         <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA36" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AB36" t="n">
         <v>8.6</v>
@@ -7428,7 +7428,7 @@
         <v>25</v>
       </c>
       <c r="AE36" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="AF36" t="n">
         <v>10.5</v>
@@ -7440,7 +7440,7 @@
         <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AJ36" t="n">
         <v>17</v>
@@ -7449,16 +7449,16 @@
         <v>18.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AN36" t="n">
         <v>10.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP36" t="n">
         <v>12</v>
@@ -7470,7 +7470,7 @@
         <v>36</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT36" t="n">
         <v>6.6</v>
@@ -7482,7 +7482,7 @@
         <v>17.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX36" t="n">
         <v>7.8</v>
@@ -7494,7 +7494,7 @@
         <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB36" t="n">
         <v>12.5</v>
@@ -7506,17 +7506,17 @@
         <v>27</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF36" t="n">
         <v>8.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>3.05</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H37" t="n">
         <v>2.66</v>
@@ -7562,7 +7562,7 @@
         <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
         <v>1.5</v>
@@ -7592,16 +7592,16 @@
         <v>1.88</v>
       </c>
       <c r="U37" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V37" t="n">
         <v>1.54</v>
       </c>
       <c r="W37" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X37" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y37" t="n">
         <v>9.199999999999999</v>
@@ -7610,19 +7610,19 @@
         <v>22</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD37" t="n">
         <v>13.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="n">
         <v>22</v>
@@ -7631,13 +7631,13 @@
         <v>15</v>
       </c>
       <c r="AH37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK37" t="n">
         <v>50</v>
@@ -7664,7 +7664,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="AT37" t="n">
         <v>9.199999999999999</v>
@@ -7676,7 +7676,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AX37" t="n">
         <v>17</v>
@@ -7685,32 +7685,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.7</v>
+        <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB37" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD37" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I38" t="n">
         <v>3.55</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L38" t="n">
         <v>1.45</v>
@@ -7783,7 +7783,7 @@
         <v>4.7</v>
       </c>
       <c r="T38" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U38" t="n">
         <v>1.95</v>
@@ -7792,13 +7792,13 @@
         <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X38" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
         <v>22</v>
@@ -7810,7 +7810,7 @@
         <v>8.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD38" t="n">
         <v>15</v>
@@ -7822,7 +7822,7 @@
         <v>14</v>
       </c>
       <c r="AG38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
@@ -7858,10 +7858,10 @@
         <v>20</v>
       </c>
       <c r="AS38" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
@@ -7870,7 +7870,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AX38" t="n">
         <v>13</v>
@@ -7879,10 +7879,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB38" t="n">
         <v>30</v>
@@ -7891,20 +7891,20 @@
         <v>27</v>
       </c>
       <c r="BD38" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BE38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BF38" t="n">
         <v>25</v>
       </c>
       <c r="BG38" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -7968,10 +7968,10 @@
         <v>2.16</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.7</v>
@@ -7989,88 +7989,88 @@
         <v>1.32</v>
       </c>
       <c r="X39" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="Y39" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="n">
         <v>970</v>
       </c>
       <c r="AA39" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="AB39" t="n">
         <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE39" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AF39" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="AG39" t="n">
         <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AJ39" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AK39" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AL39" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM39" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AN39" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="AO39" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR39" t="n">
         <v>12.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV39" t="n">
         <v>9.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AY39" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ39" t="n">
         <v>11.5</v>
@@ -8082,13 +8082,13 @@
         <v>10</v>
       </c>
       <c r="BC39" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD39" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>3</v>
+        <v>17.5</v>
       </c>
       <c r="BF39" t="n">
         <v>24</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -8156,13 +8156,13 @@
         <v>3.3</v>
       </c>
       <c r="O40" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P40" t="n">
         <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8171,10 +8171,10 @@
         <v>4.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U40" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V40" t="n">
         <v>1.37</v>
@@ -8207,7 +8207,7 @@
         <v>46</v>
       </c>
       <c r="AF40" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
         <v>11.5</v>
@@ -8282,7 +8282,7 @@
         <v>40</v>
       </c>
       <c r="BE40" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BF40" t="n">
         <v>23</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -8335,19 +8335,19 @@
         <v>3.25</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M41" t="n">
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.6</v>
@@ -8476,7 +8476,7 @@
         <v>65</v>
       </c>
       <c r="BE41" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF41" t="n">
         <v>46</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G42" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H42" t="n">
         <v>6.2</v>
@@ -8550,10 +8550,10 @@
         <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S42" t="n">
         <v>2.96</v>
@@ -8568,16 +8568,16 @@
         <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X42" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y42" t="n">
         <v>23</v>
       </c>
       <c r="Z42" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA42" t="n">
         <v>170</v>
@@ -8586,7 +8586,7 @@
         <v>9.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD42" t="n">
         <v>23</v>
@@ -8595,7 +8595,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG42" t="n">
         <v>9.6</v>
@@ -8607,13 +8607,13 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK42" t="n">
         <v>15</v>
       </c>
       <c r="AL42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM42" t="n">
         <v>95</v>
@@ -8622,10 +8622,10 @@
         <v>8</v>
       </c>
       <c r="AO42" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP42" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>21</v>
@@ -8634,13 +8634,13 @@
         <v>44</v>
       </c>
       <c r="AS42" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AT42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV42" t="n">
         <v>21</v>
@@ -8649,19 +8649,19 @@
         <v>70</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ42" t="n">
         <v>19</v>
       </c>
       <c r="BA42" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB42" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC42" t="n">
         <v>14.5</v>
@@ -8673,14 +8673,14 @@
         <v>90</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -8714,10 +8714,10 @@
         <v>4.4</v>
       </c>
       <c r="G43" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H43" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I43" t="n">
         <v>2.08</v>
@@ -8726,7 +8726,7 @@
         <v>3.4</v>
       </c>
       <c r="K43" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L43" t="n">
         <v>1.42</v>
@@ -8735,16 +8735,16 @@
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O43" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P43" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -8753,16 +8753,16 @@
         <v>4.7</v>
       </c>
       <c r="T43" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U43" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V43" t="n">
         <v>1.92</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
         <v>10.5</v>
@@ -8771,7 +8771,7 @@
         <v>7.4</v>
       </c>
       <c r="Z43" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="n">
         <v>32</v>
@@ -8786,40 +8786,40 @@
         <v>12.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF43" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AG43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH43" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI43" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ43" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK43" t="n">
-        <v>75</v>
+        <v>480</v>
       </c>
       <c r="AL43" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="AM43" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN43" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AO43" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AP43" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ43" t="n">
         <v>6.6</v>
@@ -8828,7 +8828,7 @@
         <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT43" t="n">
         <v>11</v>
@@ -8840,7 +8840,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AX43" t="n">
         <v>27</v>
@@ -8855,26 +8855,26 @@
         <v>42</v>
       </c>
       <c r="BB43" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD43" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>9</v>
-      </c>
       <c r="BE43" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BF43" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG43" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -8905,28 +8905,28 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I44" t="n">
         <v>3.15</v>
       </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.25</v>
-      </c>
       <c r="J44" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K44" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N44" t="n">
         <v>2.5</v>
@@ -8941,34 +8941,34 @@
         <v>2.82</v>
       </c>
       <c r="R44" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S44" t="n">
-        <v>5.7</v>
+        <v>2.82</v>
       </c>
       <c r="T44" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U44" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.45</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.46</v>
       </c>
       <c r="X44" t="n">
         <v>8</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
         <v>9.199999999999999</v>
@@ -8977,7 +8977,7 @@
         <v>6.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
@@ -8986,7 +8986,7 @@
         <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH44" t="n">
         <v>1000</v>
@@ -8995,13 +8995,13 @@
         <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
         <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>990</v>
+        <v>450</v>
       </c>
       <c r="AM44" t="n">
         <v>1000</v>
@@ -9013,7 +9013,7 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ44" t="n">
         <v>7.4</v>
@@ -9022,7 +9022,7 @@
         <v>13</v>
       </c>
       <c r="AS44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT44" t="n">
         <v>7.2</v>
@@ -9034,7 +9034,7 @@
         <v>12</v>
       </c>
       <c r="AW44" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AX44" t="n">
         <v>13.5</v>
@@ -9046,19 +9046,19 @@
         <v>16.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BB44" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BC44" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD44" t="n">
         <v>36</v>
       </c>
-      <c r="BD44" t="n">
-        <v>50</v>
-      </c>
       <c r="BE44" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF44" t="n">
         <v>30</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -9111,16 +9111,16 @@
         <v>3.65</v>
       </c>
       <c r="J45" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K45" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L45" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N45" t="n">
         <v>2.42</v>
@@ -9153,7 +9153,7 @@
         <v>1.6</v>
       </c>
       <c r="X45" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="Y45" t="n">
         <v>11</v>
@@ -9189,7 +9189,7 @@
         <v>120</v>
       </c>
       <c r="AJ45" t="n">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="AK45" t="n">
         <v>50</v>
@@ -9207,7 +9207,7 @@
         <v>120</v>
       </c>
       <c r="AP45" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ45" t="n">
         <v>8</v>
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.8</v>
+        <v>55</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -9228,7 +9228,7 @@
         <v>14.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="AX45" t="n">
         <v>13</v>
@@ -9237,32 +9237,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BA45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB45" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB45" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC45" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE45" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF45" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>2.2</v>
       </c>
       <c r="H46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
         <v>4.8</v>
@@ -9356,7 +9356,7 @@
         <v>36</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB46" t="n">
         <v>8.6</v>
@@ -9389,7 +9389,7 @@
         <v>28</v>
       </c>
       <c r="AL46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
@@ -9407,10 +9407,10 @@
         <v>9.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT46" t="n">
         <v>5.8</v>
@@ -9422,7 +9422,7 @@
         <v>13.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX46" t="n">
         <v>9.4</v>
@@ -9434,7 +9434,7 @@
         <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB46" t="n">
         <v>21</v>
@@ -9443,20 +9443,20 @@
         <v>21</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF46" t="n">
         <v>18.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         <v>2.12</v>
       </c>
       <c r="H47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
         <v>5.5</v>
@@ -9505,13 +9505,13 @@
         <v>3.65</v>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M47" t="n">
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
         <v>1.45</v>
@@ -9529,10 +9529,10 @@
         <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U47" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="V47" t="n">
         <v>1.22</v>
@@ -9541,10 +9541,10 @@
         <v>1.91</v>
       </c>
       <c r="X47" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z47" t="n">
         <v>1000</v>
@@ -9553,31 +9553,31 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE47" t="n">
         <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="n">
         <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
         <v>1000</v>
@@ -9589,7 +9589,7 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
@@ -9598,25 +9598,25 @@
         <v>7.2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT47" t="n">
         <v>6</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX47" t="n">
         <v>8.6</v>
@@ -9625,32 +9625,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ47" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BA47" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB47" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BC47" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G48" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
@@ -9693,7 +9693,7 @@
         <v>5.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K48" t="n">
         <v>3.6</v>
@@ -9714,7 +9714,7 @@
         <v>1.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R48" t="n">
         <v>1.21</v>
@@ -9723,10 +9723,10 @@
         <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V48" t="n">
         <v>1.22</v>
@@ -9744,10 +9744,10 @@
         <v>42</v>
       </c>
       <c r="AA48" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB48" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC48" t="n">
         <v>8.199999999999999</v>
@@ -9756,10 +9756,10 @@
         <v>23</v>
       </c>
       <c r="AE48" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF48" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG48" t="n">
         <v>11.5</v>
@@ -9768,7 +9768,7 @@
         <v>26</v>
       </c>
       <c r="AI48" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AJ48" t="n">
         <v>23</v>
@@ -9780,7 +9780,7 @@
         <v>60</v>
       </c>
       <c r="AM48" t="n">
-        <v>230</v>
+        <v>580</v>
       </c>
       <c r="AN48" t="n">
         <v>21</v>
@@ -9789,16 +9789,16 @@
         <v>170</v>
       </c>
       <c r="AP48" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ48" t="n">
         <v>11.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="AS48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT48" t="n">
         <v>5.9</v>
@@ -9810,7 +9810,7 @@
         <v>18</v>
       </c>
       <c r="AW48" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AX48" t="n">
         <v>8.800000000000001</v>
@@ -9822,7 +9822,7 @@
         <v>21</v>
       </c>
       <c r="BA48" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB48" t="n">
         <v>19</v>
@@ -9831,20 +9831,20 @@
         <v>21</v>
       </c>
       <c r="BD48" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BE48" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF48" t="n">
         <v>16</v>
       </c>
       <c r="BG48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -9878,22 +9878,22 @@
         <v>1.66</v>
       </c>
       <c r="G49" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H49" t="n">
         <v>6.6</v>
       </c>
       <c r="I49" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J49" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K49" t="n">
         <v>4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -9914,16 +9914,16 @@
         <v>1.25</v>
       </c>
       <c r="S49" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U49" t="n">
         <v>1.72</v>
       </c>
       <c r="V49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W49" t="n">
         <v>2.4</v>
@@ -9986,7 +9986,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ49" t="n">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="AR49" t="n">
         <v>4.2</v>
@@ -9998,7 +9998,7 @@
         <v>4.9</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV49" t="n">
         <v>4.1</v>
@@ -10007,25 +10007,25 @@
         <v>4.2</v>
       </c>
       <c r="AX49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY49" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY49" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ49" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BA49" t="n">
         <v>4.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="BC49" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD49" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4.2</v>
       </c>
       <c r="BE49" t="n">
         <v>4.2</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="G50" t="n">
         <v>3.05</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.65</v>
       </c>
       <c r="G51" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H51" t="n">
         <v>4.2</v>
@@ -10275,7 +10275,7 @@
         <v>6.6</v>
       </c>
       <c r="J51" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K51" t="n">
         <v>4.7</v>
@@ -10293,7 +10293,7 @@
         <v>1.24</v>
       </c>
       <c r="P51" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q51" t="n">
         <v>1.72</v>
@@ -10308,7 +10308,7 @@
         <v>1.73</v>
       </c>
       <c r="U51" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V51" t="n">
         <v>1.18</v>
@@ -10380,7 +10380,7 @@
         <v>6</v>
       </c>
       <c r="AS51" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT51" t="n">
         <v>4.2</v>
@@ -10395,7 +10395,7 @@
         <v>6.4</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY51" t="n">
         <v>4.3</v>
@@ -10416,7 +10416,7 @@
         <v>5.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF51" t="n">
         <v>4.1</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
         <v>3.6</v>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J52" t="n">
         <v>3.2</v>
@@ -10475,7 +10475,7 @@
         <v>3.55</v>
       </c>
       <c r="L52" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10487,22 +10487,22 @@
         <v>1.39</v>
       </c>
       <c r="P52" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R52" t="n">
         <v>1.26</v>
       </c>
       <c r="S52" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U52" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V52" t="n">
         <v>1.34</v>
@@ -10526,7 +10526,7 @@
         <v>10.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD52" t="n">
         <v>19</v>
@@ -10568,25 +10568,25 @@
         <v>9.6</v>
       </c>
       <c r="AQ52" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR52" t="n">
         <v>18.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT52" t="n">
         <v>7.2</v>
       </c>
       <c r="AU52" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AV52" t="n">
         <v>11.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX52" t="n">
         <v>10</v>
@@ -10598,29 +10598,29 @@
         <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB52" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BC52" t="n">
         <v>20</v>
       </c>
       <c r="BD52" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF52" t="n">
         <v>17.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H53" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J53" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K53" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L53" t="n">
         <v>1.46</v>
@@ -10675,7 +10675,7 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -10699,10 +10699,10 @@
         <v>1.54</v>
       </c>
       <c r="V53" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W53" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X53" t="n">
         <v>11.5</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>
@@ -11042,10 +11042,10 @@
         <v>3.2</v>
       </c>
       <c r="G55" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="H55" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I55" t="n">
         <v>2.76</v>
@@ -11057,7 +11057,7 @@
         <v>3.6</v>
       </c>
       <c r="L55" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M55" t="n">
         <v>1.09</v>
@@ -11069,7 +11069,7 @@
         <v>1.4</v>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q55" t="n">
         <v>2.02</v>
@@ -11090,7 +11090,7 @@
         <v>1.59</v>
       </c>
       <c r="W55" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11147,37 +11147,37 @@
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT55" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AU55" t="n">
         <v>5.6</v>
       </c>
       <c r="AV55" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW55" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AX55" t="n">
         <v>16</v>
       </c>
       <c r="AY55" t="n">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ55" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA55" t="n">
         <v>3.95</v>
@@ -11186,7 +11186,7 @@
         <v>4</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BD55" t="n">
         <v>4</v>
@@ -11198,11 +11198,11 @@
         <v>3.95</v>
       </c>
       <c r="BG55" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-12 18:24:48</t>
+          <t>2026-04-12 20:37:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -775,152 +775,152 @@
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z2" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AG2" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AM2" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="AN2" t="n">
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -957,67 +957,67 @@
         <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
         <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
         <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
@@ -1029,7 +1029,7 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
         <v>18</v>
@@ -1038,28 +1038,28 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1080,41 +1080,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
         <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1151,16 +1151,16 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>1.55</v>
@@ -1172,19 +1172,19 @@
         <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
         <v>1.94</v>
@@ -1202,7 +1202,7 @@
         <v>9.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
         <v>24</v>
@@ -1217,13 +1217,13 @@
         <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1244,7 +1244,7 @@
         <v>130</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
         <v>44</v>
@@ -1262,10 +1262,10 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>6</v>
@@ -1274,7 +1274,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,29 +1286,29 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
         <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BF4" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
         <v>1.84</v>
@@ -1348,10 +1348,10 @@
         <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1363,31 +1363,31 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
         <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
         <v>2.18</v>
@@ -1405,7 +1405,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>9.6</v>
@@ -1417,7 +1417,7 @@
         <v>320</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
@@ -1435,40 +1435,40 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1477,32 +1477,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
         <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G6" t="n">
         <v>3.1</v>
@@ -1542,7 +1542,7 @@
         <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.58</v>
@@ -1554,7 +1554,7 @@
         <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N6" t="n">
         <v>2.02</v>
@@ -1566,7 +1566,7 @@
         <v>1.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1575,25 +1575,25 @@
         <v>7.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U6" t="n">
         <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
         <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
         <v>19.5</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AK6" t="n">
         <v>440</v>
@@ -1650,7 +1650,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1662,7 +1662,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="n">
         <v>10.5</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.52</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.28</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>710</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
         <v>170</v>
       </c>
-      <c r="AA7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO7" t="n">
         <v>240</v>
       </c>
-      <c r="AN7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>380</v>
-      </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BA7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB7" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
         <v>3.7</v>
@@ -1933,13 +1933,13 @@
         <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
         <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.14</v>
@@ -1948,7 +1948,7 @@
         <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
         <v>1.52</v>
@@ -1972,7 +1972,7 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
         <v>9.800000000000001</v>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
         <v>4.9</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I9" t="n">
         <v>2.34</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1.56</v>
@@ -2145,7 +2145,7 @@
         <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
         <v>3.1</v>
@@ -2160,7 +2160,7 @@
         <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
         <v>1.75</v>
@@ -2202,10 +2202,10 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>260</v>
@@ -2214,13 +2214,13 @@
         <v>540</v>
       </c>
       <c r="AM9" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2244,7 +2244,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2259,26 +2259,26 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2315,19 +2315,19 @@
         <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2423,10 +2423,10 @@
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2453,7 +2453,7 @@
         <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -2515,10 +2515,10 @@
         <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -2545,13 +2545,13 @@
         <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W11" t="n">
         <v>1.33</v>
@@ -2620,13 +2620,13 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
@@ -2638,22 +2638,22 @@
         <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
         <v>28</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
         <v>3.45</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.97</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AU12" t="n">
         <v>5.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AY12" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BF12" t="n">
         <v>2.38</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
@@ -2915,31 +2915,31 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
         <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
         <v>1.36</v>
@@ -2999,7 +2999,7 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>4.9</v>
@@ -3008,7 +3008,7 @@
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,10 +3020,10 @@
         <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
@@ -3032,29 +3032,29 @@
         <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
         <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3088,22 +3088,22 @@
         <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H14" t="n">
         <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
         <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3118,7 +3118,7 @@
         <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
         <v>1.53</v>
@@ -3127,7 +3127,7 @@
         <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
@@ -3136,7 +3136,7 @@
         <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
         <v>75</v>
@@ -3178,7 +3178,7 @@
         <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
         <v>80</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3196,13 +3196,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
         <v>7.8</v>
@@ -3211,10 +3211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -3226,7 +3226,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
         <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -3303,43 +3303,43 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
         <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="X15" t="n">
         <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="n">
         <v>120</v>
@@ -3354,25 +3354,25 @@
         <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3381,52 +3381,52 @@
         <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR15" t="n">
         <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW15" t="n">
         <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
         <v>44</v>
       </c>
       <c r="BB15" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
         <v>25</v>
@@ -3435,14 +3435,14 @@
         <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3485,40 +3485,40 @@
         <v>1.97</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
         <v>2.02</v>
@@ -3527,40 +3527,40 @@
         <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AG16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>19</v>
       </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
         <v>120</v>
@@ -3575,46 +3575,46 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP16" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
         <v>9.4</v>
@@ -3623,7 +3623,7 @@
         <v>50</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE16" t="n">
         <v>32</v>
@@ -3632,11 +3632,11 @@
         <v>9</v>
       </c>
       <c r="BG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J17" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.22</v>
@@ -3691,34 +3691,34 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T17" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V17" t="n">
         <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3748,7 +3748,7 @@
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3769,22 +3769,22 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS17" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -3793,10 +3793,10 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
         <v>8.800000000000001</v>
@@ -3817,20 +3817,20 @@
         <v>10.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H18" t="n">
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J18" t="n">
         <v>4.4</v>
@@ -3885,34 +3885,34 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
         <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V18" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3942,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3993,7 +3993,7 @@
         <v>12</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -4002,29 +4002,29 @@
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>1.98</v>
       </c>
       <c r="I19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
@@ -4094,7 +4094,7 @@
         <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
         <v>1.67</v>
@@ -4103,7 +4103,7 @@
         <v>2.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W19" t="n">
         <v>1.32</v>
@@ -4115,7 +4115,7 @@
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
         <v>23</v>
@@ -4124,13 +4124,13 @@
         <v>22</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AF19" t="n">
         <v>34</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
         <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.31</v>
@@ -4273,34 +4273,34 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
         <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
         <v>20</v>
@@ -4315,16 +4315,16 @@
         <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
         <v>18</v>
@@ -4342,10 +4342,10 @@
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
         <v>70</v>
@@ -4354,7 +4354,7 @@
         <v>15.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>10.5</v>
@@ -4372,13 +4372,13 @@
         <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
@@ -4408,11 +4408,11 @@
         <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>2.58</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
         <v>3.55</v>
@@ -4491,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
         <v>1.63</v>
@@ -4524,7 +4524,7 @@
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>60</v>
@@ -4554,13 +4554,13 @@
         <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AR21" t="n">
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4569,13 +4569,13 @@
         <v>5.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -4584,29 +4584,29 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
@@ -4658,10 +4658,10 @@
         <v>1.32</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>1.3</v>
@@ -4670,10 +4670,10 @@
         <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
         <v>3.45</v>
@@ -4694,7 +4694,7 @@
         <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
         <v>26</v>
@@ -4703,7 +4703,7 @@
         <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
@@ -4712,7 +4712,7 @@
         <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -4754,10 +4754,10 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -4778,7 +4778,7 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
         <v>16</v>
@@ -4796,11 +4796,11 @@
         <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>4.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="I23" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J23" t="n">
         <v>4.2</v>
@@ -4879,22 +4879,22 @@
         <v>2.42</v>
       </c>
       <c r="V23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
         <v>75</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
         <v>14.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AB23" t="n">
         <v>42</v>
@@ -4933,13 +4933,13 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
         <v>7.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>11.5</v>
@@ -4948,7 +4948,7 @@
         <v>12</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT23" t="n">
         <v>19.5</v>
@@ -4963,7 +4963,7 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY23" t="n">
         <v>15</v>
@@ -4975,26 +4975,26 @@
         <v>21</v>
       </c>
       <c r="BB23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC23" t="n">
         <v>9</v>
       </c>
-      <c r="BC23" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF23" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
         <v>6.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I24" t="n">
         <v>2.56</v>
@@ -5049,28 +5049,28 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
         <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V24" t="n">
         <v>1.64</v>
@@ -5103,7 +5103,7 @@
         <v>26</v>
       </c>
       <c r="AF24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
@@ -5112,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
@@ -5130,7 +5130,7 @@
         <v>24</v>
       </c>
       <c r="AO24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
         <v>18.5</v>
@@ -5154,7 +5154,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AX24" t="n">
         <v>18.5</v>
@@ -5172,7 +5172,7 @@
         <v>38</v>
       </c>
       <c r="BC24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD24" t="n">
         <v>23</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -5222,55 +5222,55 @@
         <v>4.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="I25" t="n">
         <v>1.72</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
         <v>1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>1.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>1.21</v>
       </c>
       <c r="T25" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
         <v>2.38</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>24</v>
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="AF25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5327,7 +5327,7 @@
         <v>7.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ25" t="n">
         <v>6.4</v>
@@ -5336,10 +5336,10 @@
         <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AT25" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AU25" t="n">
         <v>5.8</v>
@@ -5348,41 +5348,41 @@
         <v>6.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G26" t="n">
         <v>2.86</v>
@@ -5422,7 +5422,7 @@
         <v>3.25</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>2.76</v>
@@ -5431,13 +5431,13 @@
         <v>2.96</v>
       </c>
       <c r="L26" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
         <v>1.14</v>
       </c>
       <c r="N26" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
         <v>1.6</v>
@@ -5473,7 +5473,7 @@
         <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
         <v>160</v>
@@ -5485,7 +5485,7 @@
         <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>60</v>
@@ -5518,7 +5518,7 @@
         <v>55</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP26" t="n">
         <v>6.8</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5554,29 +5554,29 @@
         <v>20</v>
       </c>
       <c r="BA26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE26" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
         <v>8</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>3.55</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5763,14 +5763,14 @@
         <v>5.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G28" t="n">
         <v>2.48</v>
@@ -5825,7 +5825,7 @@
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
         <v>1.51</v>
@@ -5873,7 +5873,7 @@
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
         <v>290</v>
@@ -5909,7 +5909,7 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AQ28" t="n">
         <v>9</v>
@@ -5918,7 +5918,7 @@
         <v>9</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>6.4</v>
@@ -5930,7 +5930,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -5939,10 +5939,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB28" t="n">
         <v>7.8</v>
@@ -5951,20 +5951,20 @@
         <v>16</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
         <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H30" t="n">
         <v>3.05</v>
@@ -6213,13 +6213,13 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>1.17</v>
       </c>
       <c r="P30" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
         <v>1.52</v>
@@ -6240,7 +6240,7 @@
         <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X30" t="n">
         <v>90</v>
@@ -6261,10 +6261,10 @@
         <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
         <v>22</v>
@@ -6291,22 +6291,22 @@
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO30" t="n">
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AR30" t="n">
         <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6318,7 +6318,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -6330,19 +6330,19 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD30" t="n">
         <v>19</v>
       </c>
       <c r="BE30" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF30" t="n">
         <v>7.6</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -6389,13 +6389,13 @@
         <v>2.98</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I31" t="n">
         <v>2.66</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
         <v>4.2</v>
@@ -6413,7 +6413,7 @@
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q31" t="n">
         <v>1.63</v>
@@ -6434,7 +6434,7 @@
         <v>1.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X31" t="n">
         <v>23</v>
@@ -6467,7 +6467,7 @@
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI31" t="n">
         <v>32</v>
@@ -6476,7 +6476,7 @@
         <v>44</v>
       </c>
       <c r="AK31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL31" t="n">
         <v>34</v>
@@ -6527,7 +6527,7 @@
         <v>14.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
         <v>18.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF32" t="n">
         <v>15</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT32" t="n">
         <v>6.6</v>
@@ -6718,7 +6718,7 @@
         <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB32" t="n">
         <v>14.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G33" t="n">
         <v>1.97</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J33" t="n">
         <v>3.65</v>
@@ -6798,19 +6798,19 @@
         <v>3.75</v>
       </c>
       <c r="O33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P33" t="n">
         <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R33" t="n">
         <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
         <v>1.7</v>
@@ -6819,10 +6819,10 @@
         <v>1.93</v>
       </c>
       <c r="V33" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W33" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X33" t="n">
         <v>17.5</v>
@@ -6849,10 +6849,10 @@
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH33" t="n">
         <v>22</v>
@@ -6861,13 +6861,13 @@
         <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AK33" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AL33" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
         <v>580</v>
@@ -6885,13 +6885,13 @@
         <v>8.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AU33" t="n">
         <v>7.6</v>
@@ -6900,7 +6900,7 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
@@ -6909,32 +6909,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG33" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -6995,10 +6995,10 @@
         <v>1.48</v>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
         <v>1.22</v>
@@ -7025,7 +7025,7 @@
         <v>16</v>
       </c>
       <c r="Z34" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA34" t="n">
         <v>900</v>
@@ -7082,7 +7082,7 @@
         <v>8.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT34" t="n">
         <v>6.8</v>
@@ -7094,7 +7094,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX34" t="n">
         <v>8.4</v>
@@ -7106,19 +7106,19 @@
         <v>11.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC34" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC34" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD34" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE34" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF34" t="n">
         <v>8</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>1.37</v>
       </c>
       <c r="X35" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y35" t="n">
         <v>10</v>
@@ -7300,19 +7300,19 @@
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF35" t="n">
         <v>8.6</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
         <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.39</v>
@@ -7482,7 +7482,7 @@
         <v>17.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX36" t="n">
         <v>7.8</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H37" t="n">
         <v>2.66</v>
@@ -7565,7 +7565,7 @@
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
@@ -7592,7 +7592,7 @@
         <v>1.88</v>
       </c>
       <c r="U37" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V37" t="n">
         <v>1.54</v>
@@ -7640,7 +7640,7 @@
         <v>900</v>
       </c>
       <c r="AK37" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
         <v>1000</v>
@@ -7688,7 +7688,7 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB37" t="n">
         <v>7.2</v>
@@ -7697,20 +7697,20 @@
         <v>7</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -7741,25 +7741,25 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G38" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="H38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I38" t="n">
         <v>3.5</v>
       </c>
-      <c r="I38" t="n">
-        <v>3.55</v>
-      </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K38" t="n">
         <v>3.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -7789,10 +7789,10 @@
         <v>1.95</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X38" t="n">
         <v>10.5</v>
@@ -7819,10 +7819,10 @@
         <v>48</v>
       </c>
       <c r="AF38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
@@ -7858,10 +7858,10 @@
         <v>20</v>
       </c>
       <c r="AS38" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
@@ -7894,17 +7894,17 @@
         <v>42</v>
       </c>
       <c r="BE38" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BF38" t="n">
         <v>25</v>
       </c>
       <c r="BG38" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
         <v>2.14</v>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J39" t="n">
         <v>3.45</v>
@@ -7962,16 +7962,16 @@
         <v>4.4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P39" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q39" t="n">
         <v>1.78</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S39" t="n">
         <v>2.7</v>
@@ -7983,10 +7983,10 @@
         <v>2.18</v>
       </c>
       <c r="V39" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W39" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X39" t="n">
         <v>32</v>
@@ -8010,7 +8010,7 @@
         <v>19</v>
       </c>
       <c r="AE39" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AF39" t="n">
         <v>70</v>
@@ -8019,7 +8019,7 @@
         <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
@@ -8037,13 +8037,13 @@
         <v>320</v>
       </c>
       <c r="AN39" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AO39" t="n">
         <v>55</v>
       </c>
       <c r="AP39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ39" t="n">
         <v>6.2</v>
@@ -8052,13 +8052,13 @@
         <v>12.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT39" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AV39" t="n">
         <v>9.4</v>
@@ -8076,16 +8076,16 @@
         <v>11.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB39" t="n">
         <v>10</v>
       </c>
       <c r="BC39" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE39" t="n">
         <v>17.5</v>
@@ -8094,11 +8094,11 @@
         <v>24</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -8135,10 +8135,10 @@
         <v>2.42</v>
       </c>
       <c r="H40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I40" t="n">
         <v>3.65</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>3.2</v>
@@ -8162,7 +8162,7 @@
         <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8249,7 +8249,7 @@
         <v>55</v>
       </c>
       <c r="AT40" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU40" t="n">
         <v>6.6</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -8365,10 +8365,10 @@
         <v>6.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V41" t="n">
         <v>1.44</v>
@@ -8380,7 +8380,7 @@
         <v>7.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z41" t="n">
         <v>19</v>
@@ -8410,7 +8410,7 @@
         <v>25</v>
       </c>
       <c r="AI41" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
         <v>48</v>
@@ -8467,26 +8467,26 @@
         <v>70</v>
       </c>
       <c r="BB41" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC41" t="n">
         <v>38</v>
       </c>
       <c r="BD41" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE41" t="n">
         <v>70</v>
       </c>
       <c r="BF41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG41" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G42" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I42" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J42" t="n">
         <v>4.4</v>
@@ -8544,31 +8544,31 @@
         <v>4.7</v>
       </c>
       <c r="O42" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R42" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T42" t="n">
         <v>1.84</v>
       </c>
       <c r="U42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V42" t="n">
         <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X42" t="n">
         <v>19</v>
@@ -8583,10 +8583,10 @@
         <v>170</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD42" t="n">
         <v>23</v>
@@ -8607,7 +8607,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK42" t="n">
         <v>15</v>
@@ -8619,16 +8619,16 @@
         <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO42" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP42" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR42" t="n">
         <v>44</v>
@@ -8643,7 +8643,7 @@
         <v>9.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW42" t="n">
         <v>70</v>
@@ -8664,7 +8664,7 @@
         <v>14</v>
       </c>
       <c r="BC42" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD42" t="n">
         <v>28</v>
@@ -8673,14 +8673,14 @@
         <v>90</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG42" t="n">
         <v>85</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
         <v>3.4</v>
       </c>
       <c r="K43" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L43" t="n">
         <v>1.42</v>
@@ -8741,7 +8741,7 @@
         <v>1.45</v>
       </c>
       <c r="P43" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q43" t="n">
         <v>2.38</v>
@@ -8804,10 +8804,10 @@
         <v>500</v>
       </c>
       <c r="AK43" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AL43" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AM43" t="n">
         <v>580</v>
@@ -8816,10 +8816,10 @@
         <v>500</v>
       </c>
       <c r="AO43" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AP43" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ43" t="n">
         <v>6.6</v>
@@ -8855,26 +8855,26 @@
         <v>42</v>
       </c>
       <c r="BB43" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC43" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE43" t="n">
         <v>36</v>
       </c>
       <c r="BF43" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG43" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -8908,13 +8908,13 @@
         <v>3.05</v>
       </c>
       <c r="G44" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H44" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>2.76</v>
@@ -8944,7 +8944,7 @@
         <v>1.15</v>
       </c>
       <c r="S44" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="T44" t="n">
         <v>2.16</v>
@@ -8956,7 +8956,7 @@
         <v>1.46</v>
       </c>
       <c r="W44" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X44" t="n">
         <v>8</v>
@@ -9001,10 +9001,10 @@
         <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>450</v>
+        <v>280</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN44" t="n">
         <v>1000</v>
@@ -9022,7 +9022,7 @@
         <v>13</v>
       </c>
       <c r="AS44" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT44" t="n">
         <v>7.2</v>
@@ -9034,19 +9034,19 @@
         <v>12</v>
       </c>
       <c r="AW44" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AX44" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY44" t="n">
         <v>12</v>
       </c>
       <c r="AZ44" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BB44" t="n">
         <v>28</v>
@@ -9055,7 +9055,7 @@
         <v>27</v>
       </c>
       <c r="BD44" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE44" t="n">
         <v>70</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>2.66</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I45" t="n">
         <v>3.65</v>
@@ -9198,7 +9198,7 @@
         <v>95</v>
       </c>
       <c r="AM45" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN45" t="n">
         <v>60</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
         <v>3.15</v>
       </c>
       <c r="K46" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L46" t="n">
         <v>1.45</v>
@@ -9353,13 +9353,13 @@
         <v>14</v>
       </c>
       <c r="Z46" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA46" t="n">
         <v>900</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC46" t="n">
         <v>8.6</v>
@@ -9395,7 +9395,7 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
@@ -9410,19 +9410,19 @@
         <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT46" t="n">
         <v>5.8</v>
       </c>
       <c r="AU46" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV46" t="n">
         <v>13.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX46" t="n">
         <v>9.4</v>
@@ -9434,7 +9434,7 @@
         <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB46" t="n">
         <v>21</v>
@@ -9443,20 +9443,20 @@
         <v>21</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF46" t="n">
         <v>18.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -9490,13 +9490,13 @@
         <v>1.89</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H47" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J47" t="n">
         <v>3.15</v>
@@ -9505,7 +9505,7 @@
         <v>3.65</v>
       </c>
       <c r="L47" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M47" t="n">
         <v>1.1</v>
@@ -9517,13 +9517,13 @@
         <v>1.45</v>
       </c>
       <c r="P47" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q47" t="n">
         <v>2.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S47" t="n">
         <v>4.1</v>
@@ -9532,7 +9532,7 @@
         <v>2.04</v>
       </c>
       <c r="U47" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V47" t="n">
         <v>1.22</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="AD47" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
         <v>1000</v>
@@ -9577,7 +9577,7 @@
         <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK47" t="n">
         <v>1000</v>
@@ -9601,22 +9601,22 @@
         <v>7</v>
       </c>
       <c r="AR47" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS47" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT47" t="n">
         <v>6</v>
       </c>
       <c r="AU47" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV47" t="n">
         <v>11.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX47" t="n">
         <v>8.6</v>
@@ -9628,7 +9628,7 @@
         <v>13</v>
       </c>
       <c r="BA47" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB47" t="n">
         <v>10.5</v>
@@ -9637,20 +9637,20 @@
         <v>13</v>
       </c>
       <c r="BD47" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF47" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG47" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
         <v>1.87</v>
       </c>
       <c r="G48" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
@@ -9699,7 +9699,7 @@
         <v>3.6</v>
       </c>
       <c r="L48" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M48" t="n">
         <v>1.11</v>
@@ -9708,13 +9708,13 @@
         <v>2.78</v>
       </c>
       <c r="O48" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P48" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R48" t="n">
         <v>1.21</v>
@@ -9723,7 +9723,7 @@
         <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U48" t="n">
         <v>1.75</v>
@@ -9732,7 +9732,7 @@
         <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X48" t="n">
         <v>10</v>
@@ -9786,10 +9786,10 @@
         <v>21</v>
       </c>
       <c r="AO48" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AP48" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ48" t="n">
         <v>11.5</v>
@@ -9837,14 +9837,14 @@
         <v>28</v>
       </c>
       <c r="BF48" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG48" t="n">
         <v>10</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q49" t="n">
         <v>2.26</v>
@@ -9935,7 +9935,7 @@
         <v>22</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -9959,7 +9959,7 @@
         <v>12.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
         <v>1000</v>
@@ -9986,13 +9986,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT49" t="n">
         <v>4.9</v>
@@ -10004,7 +10004,7 @@
         <v>4.1</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX49" t="n">
         <v>6.4</v>
@@ -10013,32 +10013,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ49" t="n">
-        <v>3.9</v>
+        <v>19.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB49" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BC49" t="n">
         <v>15</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="G50" t="n">
         <v>3.05</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -10263,58 +10263,58 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G51" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H51" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I51" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J51" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K51" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L51" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M51" t="n">
         <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P51" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R51" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S51" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T51" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U51" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V51" t="n">
         <v>1.18</v>
       </c>
       <c r="W51" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10344,7 +10344,7 @@
         <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH51" t="n">
         <v>1000</v>
@@ -10365,68 +10365,68 @@
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO51" t="n">
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR51" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.9</v>
+        <v>3.05</v>
       </c>
       <c r="AT51" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AU51" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV51" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW51" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA51" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG51" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G52" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H52" t="n">
         <v>3.6</v>
@@ -10472,10 +10472,10 @@
         <v>3.2</v>
       </c>
       <c r="K52" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10484,10 +10484,10 @@
         <v>3.1</v>
       </c>
       <c r="O52" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P52" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q52" t="n">
         <v>2.16</v>
@@ -10499,10 +10499,10 @@
         <v>3.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U52" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V52" t="n">
         <v>1.34</v>
@@ -10511,7 +10511,7 @@
         <v>1.71</v>
       </c>
       <c r="X52" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y52" t="n">
         <v>14.5</v>
@@ -10601,7 +10601,7 @@
         <v>4.3</v>
       </c>
       <c r="BB52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC52" t="n">
         <v>20</v>
@@ -10610,17 +10610,17 @@
         <v>4.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF52" t="n">
         <v>17.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G53" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H53" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J53" t="n">
         <v>3.85</v>
@@ -10675,7 +10675,7 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -10699,16 +10699,16 @@
         <v>1.54</v>
       </c>
       <c r="V53" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W53" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X53" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z53" t="n">
         <v>90</v>
@@ -10762,13 +10762,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR53" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT53" t="n">
         <v>4.9</v>
@@ -10777,10 +10777,10 @@
         <v>8.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AW53" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX53" t="n">
         <v>6.2</v>
@@ -10789,32 +10789,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ53" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA53" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB53" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC53" t="n">
         <v>19</v>
       </c>
       <c r="BD53" t="n">
-        <v>50</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG53" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>
@@ -11042,61 +11042,61 @@
         <v>3.2</v>
       </c>
       <c r="G55" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H55" t="n">
         <v>2.3</v>
       </c>
       <c r="I55" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K55" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L55" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M55" t="n">
         <v>1.09</v>
       </c>
       <c r="N55" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O55" t="n">
         <v>1.4</v>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="R55" t="n">
         <v>1.25</v>
       </c>
       <c r="S55" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T55" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="U55" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="V55" t="n">
         <v>1.59</v>
       </c>
       <c r="W55" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X55" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z55" t="n">
         <v>1000</v>
@@ -11147,7 +11147,7 @@
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ55" t="n">
         <v>6.6</v>
@@ -11156,10 +11156,10 @@
         <v>11</v>
       </c>
       <c r="AS55" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT55" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU55" t="n">
         <v>5.6</v>
@@ -11168,41 +11168,41 @@
         <v>8.6</v>
       </c>
       <c r="AW55" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AX55" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC55" t="n">
         <v>4</v>
       </c>
-      <c r="BC55" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF55" t="n">
         <v>4</v>
       </c>
-      <c r="BE55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG55" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-12 20:37:28</t>
+          <t>2026-04-12 22:48:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -760,76 +760,76 @@
         <v>4.9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y2" t="n">
         <v>6.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.9</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -841,7 +841,7 @@
         <v>130</v>
       </c>
       <c r="AH2" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
@@ -850,77 +850,77 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="AL2" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AN2" t="n">
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR2" t="n">
         <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BA2" t="n">
-        <v>10</v>
-      </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
         <v>2.34</v>
@@ -969,28 +969,28 @@
         <v>3.6</v>
       </c>
       <c r="L3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.37</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.38</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
         <v>1.86</v>
@@ -1014,19 +1014,19 @@
         <v>14.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>29</v>
@@ -1053,10 +1053,10 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>10.5</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1083,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1092,29 +1092,29 @@
         <v>10.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
         <v>3.2</v>
@@ -1160,10 +1160,10 @@
         <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1175,16 +1175,16 @@
         <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.94</v>
@@ -1211,7 +1211,7 @@
         <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
@@ -1220,19 +1220,19 @@
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
         <v>48</v>
@@ -1241,7 +1241,7 @@
         <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BB4" t="n">
         <v>15</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1345,25 +1345,25 @@
         <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
@@ -1372,7 +1372,7 @@
         <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
@@ -1444,19 +1444,19 @@
         <v>9.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>9.800000000000001</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1480,7 +1480,7 @@
         <v>9</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1492,17 +1492,17 @@
         <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1533,40 +1533,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G6" t="n">
         <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
         <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
         <v>1.18</v>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="P6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1575,19 +1575,19 @@
         <v>7.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Y6" t="n">
         <v>8.4</v>
@@ -1605,7 +1605,7 @@
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1614,10 +1614,10 @@
         <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1626,22 +1626,22 @@
         <v>230</v>
       </c>
       <c r="AK6" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.2</v>
@@ -1650,7 +1650,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1662,7 +1662,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
         <v>10.5</v>
@@ -1739,64 +1739,64 @@
         <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
         <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA7" t="n">
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
         <v>46</v>
@@ -1805,7 +1805,7 @@
         <v>220</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -1820,25 +1820,25 @@
         <v>10.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO7" t="n">
         <v>240</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
@@ -1850,19 +1850,19 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
         <v>8.800000000000001</v>
@@ -1871,16 +1871,16 @@
         <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
         <v>4.1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
         <v>3.7</v>
@@ -1933,7 +1933,7 @@
         <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
         <v>3.05</v>
@@ -1945,16 +1945,16 @@
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
         <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -1972,28 +1972,28 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
         <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
         <v>75</v>
@@ -2005,7 +2005,7 @@
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>450</v>
@@ -2014,7 +2014,7 @@
         <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>450</v>
@@ -2026,19 +2026,19 @@
         <v>48</v>
       </c>
       <c r="AO8" t="n">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2047,22 +2047,22 @@
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
         <v>28</v>
@@ -2071,20 +2071,20 @@
         <v>16</v>
       </c>
       <c r="BD8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE8" t="n">
         <v>28</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I9" t="n">
         <v>2.34</v>
       </c>
       <c r="J9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -2217,7 +2217,7 @@
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
         <v>42</v>
@@ -2235,7 +2235,7 @@
         <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2259,13 +2259,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC9" t="n">
         <v>9.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE9" t="n">
         <v>10</v>
@@ -2274,11 +2274,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
@@ -2339,10 +2339,10 @@
         <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
@@ -2354,10 +2354,10 @@
         <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.96</v>
@@ -2366,7 +2366,7 @@
         <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
         <v>40</v>
@@ -2375,7 +2375,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
@@ -2414,7 +2414,7 @@
         <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>9</v>
@@ -2426,7 +2426,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2450,7 +2450,7 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2462,17 +2462,17 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
         <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -2551,7 +2551,7 @@
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W11" t="n">
         <v>1.33</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.21</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3196,13 +3196,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>7.8</v>
@@ -3211,10 +3211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -3226,7 +3226,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
@@ -3297,7 +3297,7 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3324,7 +3324,7 @@
         <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
@@ -3333,7 +3333,7 @@
         <v>2.14</v>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
         <v>21</v>
@@ -3342,7 +3342,7 @@
         <v>38</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
@@ -3360,7 +3360,7 @@
         <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
@@ -3396,7 +3396,7 @@
         <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -3414,35 +3414,35 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
         <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
         <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3482,22 +3482,22 @@
         <v>1.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
@@ -3506,7 +3506,7 @@
         <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -3521,13 +3521,13 @@
         <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
         <v>9.6</v>
@@ -3569,13 +3569,13 @@
         <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="AO16" t="n">
         <v>13.5</v>
@@ -3605,7 +3605,7 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
@@ -3614,29 +3614,29 @@
         <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD16" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BE16" t="n">
         <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG16" t="n">
         <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H17" t="n">
         <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.22</v>
@@ -3697,7 +3697,7 @@
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -3718,7 +3718,7 @@
         <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3784,7 +3784,7 @@
         <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -3793,7 +3793,7 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW17" t="n">
         <v>7.4</v>
@@ -3808,19 +3808,19 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
         <v>3.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>6.6</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H18" t="n">
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J18" t="n">
         <v>4.4</v>
@@ -3882,34 +3882,34 @@
         <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
         <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W18" t="n">
         <v>1.14</v>
@@ -3966,10 +3966,10 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>6.8</v>
@@ -3987,7 +3987,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW18" t="n">
         <v>12</v>
@@ -4005,7 +4005,7 @@
         <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC18" t="n">
         <v>9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G19" t="n">
         <v>4.1</v>
@@ -4064,7 +4064,7 @@
         <v>1.98</v>
       </c>
       <c r="I19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
@@ -4079,31 +4079,31 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
         <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W19" t="n">
         <v>1.32</v>
@@ -4112,16 +4112,16 @@
         <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
         <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC19" t="n">
         <v>8.800000000000001</v>
@@ -4148,10 +4148,10 @@
         <v>75</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>200</v>
@@ -4169,19 +4169,19 @@
         <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
         <v>16.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J20" t="n">
         <v>3.85</v>
@@ -4273,7 +4273,7 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
@@ -4288,25 +4288,25 @@
         <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
         <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X20" t="n">
         <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
         <v>22</v>
@@ -4318,7 +4318,7 @@
         <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>13.5</v>
@@ -4342,16 +4342,16 @@
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL20" t="n">
         <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO20" t="n">
         <v>21</v>
@@ -4396,7 +4396,7 @@
         <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BD20" t="n">
         <v>29</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
         <v>60</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4649,10 +4649,10 @@
         <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.32</v>
@@ -4661,16 +4661,16 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R22" t="n">
         <v>1.33</v>
@@ -4679,10 +4679,10 @@
         <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
@@ -4691,7 +4691,7 @@
         <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
         <v>14.5</v>
@@ -4715,7 +4715,7 @@
         <v>100</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT22" t="n">
         <v>9</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -4778,7 +4778,7 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
         <v>16</v>
@@ -4796,11 +4796,11 @@
         <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I23" t="n">
         <v>1.81</v>
@@ -4873,7 +4873,7 @@
         <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U23" t="n">
         <v>2.42</v>
@@ -4963,7 +4963,7 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY23" t="n">
         <v>15</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -5055,22 +5055,22 @@
         <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R24" t="n">
         <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T24" t="n">
         <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="V24" t="n">
         <v>1.64</v>
@@ -5085,13 +5085,13 @@
         <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
         <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
         <v>8.199999999999999</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -5222,55 +5222,55 @@
         <v>4.5</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="I25" t="n">
         <v>1.72</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="L25" t="n">
         <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
         <v>1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="S25" t="n">
-        <v>1.21</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
         <v>2.38</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
         <v>24</v>
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5327,7 +5327,7 @@
         <v>7.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AQ25" t="n">
         <v>6.4</v>
@@ -5336,10 +5336,10 @@
         <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AU25" t="n">
         <v>5.8</v>
@@ -5348,41 +5348,41 @@
         <v>6.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -5413,31 +5413,31 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G26" t="n">
         <v>2.86</v>
       </c>
       <c r="H26" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J26" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K26" t="n">
         <v>2.96</v>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
         <v>1.14</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O26" t="n">
         <v>1.6</v>
@@ -5461,7 +5461,7 @@
         <v>1.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W26" t="n">
         <v>1.53</v>
@@ -5503,7 +5503,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="AK26" t="n">
         <v>55</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
         <v>3.55</v>
@@ -5664,7 +5664,7 @@
         <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
         <v>19.5</v>
@@ -5676,7 +5676,7 @@
         <v>14.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
         <v>13.5</v>
@@ -5697,7 +5697,7 @@
         <v>46</v>
       </c>
       <c r="AJ27" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AK27" t="n">
         <v>40</v>
@@ -5724,7 +5724,7 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT27" t="n">
         <v>9.800000000000001</v>
@@ -5748,29 +5748,29 @@
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -5804,28 +5804,28 @@
         <v>2.34</v>
       </c>
       <c r="G28" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I28" t="n">
         <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K28" t="n">
         <v>3.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O28" t="n">
         <v>1.51</v>
@@ -5909,7 +5909,7 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>9</v>
@@ -5945,7 +5945,7 @@
         <v>9</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
         <v>16</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.18</v>
@@ -6019,7 +6019,7 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O29" t="n">
         <v>1.11</v>
@@ -6079,7 +6079,7 @@
         <v>14.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI29" t="n">
         <v>36</v>
@@ -6094,7 +6094,7 @@
         <v>24</v>
       </c>
       <c r="AM29" t="n">
-        <v>48</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
         <v>6</v>
@@ -6103,19 +6103,19 @@
         <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU29" t="n">
         <v>10</v>
@@ -6124,7 +6124,7 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX29" t="n">
         <v>14.5</v>
@@ -6136,10 +6136,10 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,7 +6148,7 @@
         <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
         <v>5.2</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -6231,10 +6231,10 @@
         <v>2.26</v>
       </c>
       <c r="T30" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U30" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V30" t="n">
         <v>1.39</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>2.52</v>
       </c>
       <c r="I31" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>3.7</v>
@@ -6407,7 +6407,7 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
@@ -6431,10 +6431,10 @@
         <v>2.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X31" t="n">
         <v>23</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -6652,7 +6652,7 @@
         <v>18.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="AF32" t="n">
         <v>15</v>
@@ -6730,7 +6730,7 @@
         <v>7.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF32" t="n">
         <v>17.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G33" t="n">
         <v>1.97</v>
@@ -6783,31 +6783,31 @@
         <v>5.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>1.34</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
         <v>1.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
         <v>3.3</v>
@@ -6825,7 +6825,7 @@
         <v>2.02</v>
       </c>
       <c r="X33" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="n">
         <v>19.5</v>
@@ -6885,10 +6885,10 @@
         <v>8.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT33" t="n">
         <v>7.8</v>
@@ -6900,7 +6900,7 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
@@ -6909,32 +6909,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ33" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G34" t="n">
         <v>3.1</v>
@@ -6980,7 +6980,7 @@
         <v>2.98</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L34" t="n">
         <v>1.52</v>
@@ -6989,7 +6989,7 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
         <v>1.48</v>
@@ -7088,7 +7088,7 @@
         <v>6.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV34" t="n">
         <v>9.800000000000001</v>
@@ -7103,7 +7103,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BA34" t="n">
         <v>8.800000000000001</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>1.65</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I36" t="n">
         <v>7</v>
@@ -7482,7 +7482,7 @@
         <v>17.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX36" t="n">
         <v>7.8</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -7547,25 +7547,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G37" t="n">
         <v>3.25</v>
       </c>
       <c r="H37" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I37" t="n">
         <v>2.84</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
@@ -7592,7 +7592,7 @@
         <v>1.88</v>
       </c>
       <c r="U37" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V37" t="n">
         <v>1.54</v>
@@ -7619,7 +7619,7 @@
         <v>7.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE37" t="n">
         <v>85</v>
@@ -7649,7 +7649,7 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
@@ -7664,7 +7664,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT37" t="n">
         <v>9.199999999999999</v>
@@ -7685,22 +7685,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF37" t="n">
         <v>7.4</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.44</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H38" t="n">
         <v>3.4</v>
@@ -7759,7 +7759,7 @@
         <v>3.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -7771,19 +7771,19 @@
         <v>1.46</v>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q38" t="n">
         <v>2.38</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T38" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U38" t="n">
         <v>1.95</v>
@@ -7792,10 +7792,10 @@
         <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y38" t="n">
         <v>11</v>
@@ -7819,16 +7819,16 @@
         <v>48</v>
       </c>
       <c r="AF38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ38" t="n">
         <v>36</v>
@@ -7837,13 +7837,13 @@
         <v>32</v>
       </c>
       <c r="AL38" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM38" t="n">
         <v>140</v>
       </c>
       <c r="AN38" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO38" t="n">
         <v>60</v>
@@ -7897,14 +7897,14 @@
         <v>29</v>
       </c>
       <c r="BF38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG38" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>3.8</v>
       </c>
       <c r="G39" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H39" t="n">
         <v>2.14</v>
@@ -7947,13 +7947,13 @@
         <v>2.22</v>
       </c>
       <c r="J39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K39" t="n">
         <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
@@ -7971,7 +7971,7 @@
         <v>1.78</v>
       </c>
       <c r="R39" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.7</v>
@@ -7986,7 +7986,7 @@
         <v>1.82</v>
       </c>
       <c r="W39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X39" t="n">
         <v>32</v>
@@ -7998,19 +7998,19 @@
         <v>970</v>
       </c>
       <c r="AA39" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB39" t="n">
         <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
         <v>19</v>
       </c>
       <c r="AE39" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AF39" t="n">
         <v>70</v>
@@ -8019,7 +8019,7 @@
         <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
@@ -8043,16 +8043,16 @@
         <v>55</v>
       </c>
       <c r="AP39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ39" t="n">
         <v>6.2</v>
       </c>
       <c r="AR39" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT39" t="n">
         <v>14.5</v>
@@ -8061,13 +8061,13 @@
         <v>5.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW39" t="n">
         <v>10.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY39" t="n">
         <v>8.4</v>
@@ -8076,16 +8076,16 @@
         <v>11.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC39" t="n">
         <v>18</v>
       </c>
       <c r="BD39" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE39" t="n">
         <v>17.5</v>
@@ -8094,11 +8094,11 @@
         <v>24</v>
       </c>
       <c r="BG39" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -8156,10 +8156,10 @@
         <v>3.3</v>
       </c>
       <c r="O40" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q40" t="n">
         <v>2.28</v>
@@ -8183,7 +8183,7 @@
         <v>1.7</v>
       </c>
       <c r="X40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="n">
         <v>12</v>
@@ -8213,7 +8213,7 @@
         <v>11.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI40" t="n">
         <v>65</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G41" t="n">
         <v>2.74</v>
       </c>
-      <c r="G41" t="n">
-        <v>2.76</v>
-      </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>3.05</v>
@@ -8341,13 +8341,13 @@
         <v>3.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M41" t="n">
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O41" t="n">
         <v>1.6</v>
@@ -8368,16 +8368,16 @@
         <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V41" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W41" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y41" t="n">
         <v>8.800000000000001</v>
@@ -8392,7 +8392,7 @@
         <v>8</v>
       </c>
       <c r="AC41" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD41" t="n">
         <v>15</v>
@@ -8410,7 +8410,7 @@
         <v>25</v>
       </c>
       <c r="AI41" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="n">
         <v>48</v>
@@ -8428,13 +8428,13 @@
         <v>55</v>
       </c>
       <c r="AO41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP41" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR41" t="n">
         <v>17.5</v>
@@ -8464,7 +8464,7 @@
         <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BB41" t="n">
         <v>40</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.61</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.62</v>
       </c>
       <c r="H42" t="n">
         <v>6.4</v>
@@ -8529,10 +8529,10 @@
         <v>6.6</v>
       </c>
       <c r="J42" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L42" t="n">
         <v>1.35</v>
@@ -8541,10 +8541,10 @@
         <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O42" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P42" t="n">
         <v>2.3</v>
@@ -8556,19 +8556,19 @@
         <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T42" t="n">
         <v>1.84</v>
       </c>
       <c r="U42" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V42" t="n">
         <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X42" t="n">
         <v>19</v>
@@ -8577,7 +8577,7 @@
         <v>23</v>
       </c>
       <c r="Z42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA42" t="n">
         <v>170</v>
@@ -8607,7 +8607,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK42" t="n">
         <v>15</v>
@@ -8619,7 +8619,7 @@
         <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO42" t="n">
         <v>100</v>
@@ -8631,10 +8631,10 @@
         <v>22</v>
       </c>
       <c r="AR42" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS42" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AT42" t="n">
         <v>9.199999999999999</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -8714,16 +8714,16 @@
         <v>4.4</v>
       </c>
       <c r="G43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H43" t="n">
         <v>2.06</v>
       </c>
       <c r="I43" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J43" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K43" t="n">
         <v>3.45</v>
@@ -8735,13 +8735,13 @@
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O43" t="n">
         <v>1.45</v>
       </c>
       <c r="P43" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q43" t="n">
         <v>2.38</v>
@@ -8759,10 +8759,10 @@
         <v>1.86</v>
       </c>
       <c r="V43" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X43" t="n">
         <v>10.5</v>
@@ -8858,10 +8858,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE43" t="n">
         <v>36</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J44" t="n">
         <v>2.76</v>
@@ -8944,7 +8944,7 @@
         <v>1.15</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T44" t="n">
         <v>2.16</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -9099,19 +9099,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H45" t="n">
         <v>3.45</v>
       </c>
       <c r="I45" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K45" t="n">
         <v>3.15</v>
@@ -9138,7 +9138,7 @@
         <v>1.16</v>
       </c>
       <c r="S45" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T45" t="n">
         <v>2.24</v>
@@ -9147,19 +9147,19 @@
         <v>1.71</v>
       </c>
       <c r="V45" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X45" t="n">
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA45" t="n">
         <v>100</v>
@@ -9171,10 +9171,10 @@
         <v>7.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF45" t="n">
         <v>18</v>
@@ -9189,7 +9189,7 @@
         <v>120</v>
       </c>
       <c r="AJ45" t="n">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="AK45" t="n">
         <v>50</v>
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>55</v>
+        <v>6.8</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -9240,19 +9240,19 @@
         <v>13</v>
       </c>
       <c r="BA45" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB45" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC45" t="n">
         <v>30</v>
       </c>
       <c r="BD45" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF45" t="n">
         <v>7.4</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G47" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H47" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J47" t="n">
         <v>3.15</v>
@@ -9511,7 +9511,7 @@
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O47" t="n">
         <v>1.45</v>
@@ -9535,10 +9535,10 @@
         <v>1.79</v>
       </c>
       <c r="V47" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W47" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X47" t="n">
         <v>17</v>
@@ -9577,7 +9577,7 @@
         <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
         <v>1000</v>
@@ -9589,7 +9589,7 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
@@ -9601,16 +9601,16 @@
         <v>7</v>
       </c>
       <c r="AR47" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT47" t="n">
         <v>6</v>
       </c>
       <c r="AU47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV47" t="n">
         <v>11.5</v>
@@ -9628,7 +9628,7 @@
         <v>13</v>
       </c>
       <c r="BA47" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB47" t="n">
         <v>10.5</v>
@@ -9640,17 +9640,17 @@
         <v>8</v>
       </c>
       <c r="BE47" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG47" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G48" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
@@ -9693,52 +9693,52 @@
         <v>5.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K48" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M48" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N48" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="O48" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R48" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="T48" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U48" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V48" t="n">
         <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X48" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z48" t="n">
         <v>42</v>
@@ -9747,7 +9747,7 @@
         <v>900</v>
       </c>
       <c r="AB48" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC48" t="n">
         <v>8.199999999999999</v>
@@ -9765,7 +9765,7 @@
         <v>11.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI48" t="n">
         <v>450</v>
@@ -9783,25 +9783,25 @@
         <v>580</v>
       </c>
       <c r="AN48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO48" t="n">
         <v>700</v>
       </c>
       <c r="AP48" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ48" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR48" t="n">
         <v>32</v>
       </c>
       <c r="AS48" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU48" t="n">
         <v>7</v>
@@ -9819,10 +9819,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ48" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA48" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB48" t="n">
         <v>19</v>
@@ -9840,11 +9840,11 @@
         <v>17.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -9917,10 +9917,10 @@
         <v>4.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U49" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V49" t="n">
         <v>1.15</v>
@@ -9935,7 +9935,7 @@
         <v>22</v>
       </c>
       <c r="Z49" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -9977,7 +9977,7 @@
         <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO49" t="n">
         <v>1000</v>
@@ -9992,19 +9992,19 @@
         <v>4.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT49" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU49" t="n">
         <v>7.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX49" t="n">
         <v>6.4</v>
@@ -10016,29 +10016,29 @@
         <v>19.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC49" t="n">
         <v>15</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF49" t="n">
         <v>4</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -10272,16 +10272,16 @@
         <v>4.7</v>
       </c>
       <c r="I51" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K51" t="n">
         <v>4.5</v>
       </c>
       <c r="L51" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M51" t="n">
         <v>1.05</v>
@@ -10296,10 +10296,10 @@
         <v>2.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R51" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
         <v>2.66</v>
@@ -10311,7 +10311,7 @@
         <v>2.08</v>
       </c>
       <c r="V51" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W51" t="n">
         <v>2.2</v>
@@ -10344,7 +10344,7 @@
         <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH51" t="n">
         <v>1000</v>
@@ -10371,62 +10371,62 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR51" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AT51" t="n">
         <v>4</v>
       </c>
       <c r="AU51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX51" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV51" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>4</v>
-      </c>
       <c r="AY51" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA51" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD51" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF51" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BG51" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -10466,16 +10466,16 @@
         <v>3.6</v>
       </c>
       <c r="I52" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>3.2</v>
       </c>
       <c r="K52" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L52" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10487,7 +10487,7 @@
         <v>1.4</v>
       </c>
       <c r="P52" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q52" t="n">
         <v>2.16</v>
@@ -10496,7 +10496,7 @@
         <v>1.26</v>
       </c>
       <c r="S52" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T52" t="n">
         <v>1.86</v>
@@ -10508,7 +10508,7 @@
         <v>1.34</v>
       </c>
       <c r="W52" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X52" t="n">
         <v>13.5</v>
@@ -10526,7 +10526,7 @@
         <v>10.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD52" t="n">
         <v>19</v>
@@ -10574,7 +10574,7 @@
         <v>18.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT52" t="n">
         <v>7.2</v>
@@ -10586,7 +10586,7 @@
         <v>11.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX52" t="n">
         <v>10</v>
@@ -10598,29 +10598,29 @@
         <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB52" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BC52" t="n">
         <v>20</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF52" t="n">
         <v>17.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>1.53</v>
       </c>
       <c r="G53" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H53" t="n">
         <v>8.800000000000001</v>
@@ -10675,7 +10675,7 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -10684,7 +10684,7 @@
         <v>1.56</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R53" t="n">
         <v>1.2</v>
@@ -10702,10 +10702,10 @@
         <v>1.11</v>
       </c>
       <c r="W53" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X53" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y53" t="n">
         <v>21</v>
@@ -10765,10 +10765,10 @@
         <v>17</v>
       </c>
       <c r="AR53" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT53" t="n">
         <v>4.9</v>
@@ -10780,7 +10780,7 @@
         <v>30</v>
       </c>
       <c r="AW53" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX53" t="n">
         <v>6.2</v>
@@ -10789,10 +10789,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ53" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA53" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB53" t="n">
         <v>11.5</v>
@@ -10801,20 +10801,20 @@
         <v>19</v>
       </c>
       <c r="BD53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE53" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF53" t="n">
         <v>11</v>
       </c>
       <c r="BG53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
         <v>1.24</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
         <v>3.7</v>
       </c>
       <c r="T55" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U55" t="n">
         <v>1.9</v>
@@ -11156,7 +11156,7 @@
         <v>11</v>
       </c>
       <c r="AS55" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT55" t="n">
         <v>8.199999999999999</v>
@@ -11168,7 +11168,7 @@
         <v>8.6</v>
       </c>
       <c r="AW55" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX55" t="n">
         <v>4</v>
@@ -11177,7 +11177,7 @@
         <v>11</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA55" t="n">
         <v>4</v>
@@ -11186,7 +11186,7 @@
         <v>4.1</v>
       </c>
       <c r="BC55" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD55" t="n">
         <v>4.1</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-12 22:48:24</t>
+          <t>2026-04-13 00:58:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
         <v>5.9</v>
@@ -766,58 +766,58 @@
         <v>1.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
         <v>34</v>
@@ -829,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -841,7 +841,7 @@
         <v>130</v>
       </c>
       <c r="AH2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
@@ -850,25 +850,25 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AM2" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO2" t="n">
         <v>600</v>
       </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
       <c r="AP2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
         <v>8.6</v>
@@ -889,38 +889,38 @@
         <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA2" t="n">
         <v>11</v>
       </c>
-      <c r="BA2" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
         <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
@@ -984,76 +984,76 @@
         <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AL3" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO3" t="n">
         <v>22</v>
@@ -1062,59 +1062,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1145,43 +1145,43 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
         <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
         <v>4.8</v>
@@ -1190,37 +1190,37 @@
         <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="n">
         <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
         <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
@@ -1232,7 +1232,7 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
         <v>48</v>
@@ -1241,7 +1241,7 @@
         <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
@@ -1253,16 +1253,16 @@
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
@@ -1277,7 +1277,7 @@
         <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1289,26 +1289,26 @@
         <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
         <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
         <v>26</v>
       </c>
       <c r="BF4" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
         <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="n">
         <v>22</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>40</v>
       </c>
-      <c r="Z5" t="n">
-        <v>140</v>
-      </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
         <v>9.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT5" t="n">
         <v>10</v>
       </c>
-      <c r="AT5" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY5" t="n">
         <v>9.4</v>
       </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1533,40 +1533,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
         <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="P6" t="n">
         <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1575,34 +1575,34 @@
         <v>7.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U6" t="n">
         <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y6" t="n">
         <v>8.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
         <v>18.5</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
         <v>80</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.2</v>
@@ -1650,7 +1650,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1662,7 +1662,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF6" t="n">
-        <v>8</v>
-      </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1727,91 +1727,91 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.29</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="H7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
         <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>46</v>
       </c>
       <c r="AE7" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1823,74 +1823,74 @@
         <v>13.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AP7" t="n">
         <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1930,46 +1930,46 @@
         <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
         <v>2.86</v>
       </c>
       <c r="K8" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M8" t="n">
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
         <v>1.61</v>
@@ -1978,7 +1978,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
         <v>28</v>
@@ -1996,7 +1996,7 @@
         <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
@@ -2005,7 +2005,7 @@
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>450</v>
@@ -2038,7 +2038,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2062,29 +2062,29 @@
         <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB8" t="n">
         <v>28</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -2124,37 +2124,37 @@
         <v>2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="M9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P9" t="n">
         <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
         <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T9" t="n">
         <v>2.36</v>
@@ -2163,7 +2163,7 @@
         <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
         <v>9.199999999999999</v>
@@ -2250,13 +2250,13 @@
         <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB9" t="n">
         <v>9.800000000000001</v>
@@ -2265,7 +2265,7 @@
         <v>9.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9" t="n">
         <v>10</v>
@@ -2274,11 +2274,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
         <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
@@ -2369,7 +2369,7 @@
         <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2384,7 +2384,7 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
@@ -2396,7 +2396,7 @@
         <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
         <v>28</v>
@@ -2426,7 +2426,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2435,7 +2435,7 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW10" t="n">
         <v>50</v>
@@ -2450,7 +2450,7 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2462,17 +2462,17 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2503,55 +2503,55 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
         <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
         <v>1.33</v>
@@ -2563,7 +2563,7 @@
         <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2611,7 +2611,7 @@
         <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>7</v>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2641,32 +2641,32 @@
         <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>28</v>
+        <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2697,46 +2697,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
         <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
         <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q12" t="n">
         <v>1.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2781,13 +2781,13 @@
         <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.92</v>
+        <v>1.34</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.82</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>5.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.86</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="BF12" t="n">
         <v>2.38</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -2915,22 +2915,22 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
         <v>1.84</v>
@@ -2939,10 +2939,10 @@
         <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2972,22 +2972,22 @@
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
         <v>60</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV13" t="n">
         <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="BD13" t="n">
         <v>2.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG13" t="n">
         <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G14" t="n">
         <v>1.51</v>
       </c>
       <c r="H14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I14" t="n">
         <v>8.6</v>
@@ -3100,16 +3100,16 @@
         <v>4.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
         <v>1.21</v>
@@ -3118,16 +3118,16 @@
         <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
@@ -3139,7 +3139,7 @@
         <v>2.96</v>
       </c>
       <c r="X14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
         <v>75</v>
@@ -3163,19 +3163,19 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK14" t="n">
         <v>15.5</v>
@@ -3196,13 +3196,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>7.8</v>
@@ -3211,10 +3211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -3223,10 +3223,10 @@
         <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>5.1</v>
@@ -3294,43 +3294,43 @@
         <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X15" t="n">
         <v>18.5</v>
@@ -3348,13 +3348,13 @@
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
@@ -3369,10 +3369,10 @@
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3381,37 +3381,37 @@
         <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO15" t="n">
         <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
@@ -3423,26 +3423,26 @@
         <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
         <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>48</v>
+        <v>14.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3473,55 +3473,55 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
@@ -3530,16 +3530,16 @@
         <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA16" t="n">
         <v>21</v>
       </c>
       <c r="AB16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC16" t="n">
         <v>9</v>
@@ -3551,10 +3551,10 @@
         <v>20</v>
       </c>
       <c r="AF16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
@@ -3566,7 +3566,7 @@
         <v>120</v>
       </c>
       <c r="AK16" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
@@ -3575,22 +3575,22 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
         <v>13.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
         <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT16" t="n">
         <v>14</v>
@@ -3605,7 +3605,7 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY16" t="n">
         <v>15.5</v>
@@ -3614,29 +3614,29 @@
         <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BC16" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BE16" t="n">
         <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H17" t="n">
         <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J17" t="n">
         <v>5.7</v>
@@ -3685,40 +3685,40 @@
         <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
         <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3733,7 +3733,7 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
         <v>42</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3757,10 +3757,10 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3775,31 +3775,31 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>11</v>
-      </c>
       <c r="AV17" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
@@ -3808,29 +3808,29 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -3861,67 +3861,67 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I18" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
         <v>5.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>25</v>
@@ -3945,10 +3945,10 @@
         <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD18" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
         <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>2.04</v>
@@ -4070,10 +4070,10 @@
         <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4082,49 +4082,49 @@
         <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="W19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
         <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -4133,16 +4133,16 @@
         <v>19.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ19" t="n">
         <v>75</v>
@@ -4154,19 +4154,19 @@
         <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
@@ -4178,16 +4178,16 @@
         <v>15.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
@@ -4196,29 +4196,29 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB19" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BC19" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD19" t="n">
         <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4249,61 +4249,61 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
         <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
         <v>15</v>
@@ -4318,7 +4318,7 @@
         <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>13.5</v>
@@ -4357,28 +4357,28 @@
         <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
         <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AT20" t="n">
         <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
@@ -4387,16 +4387,16 @@
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
         <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD20" t="n">
         <v>29</v>
@@ -4408,11 +4408,11 @@
         <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4443,61 +4443,61 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.15</v>
       </c>
       <c r="K21" t="n">
         <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
         <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
         <v>19</v>
@@ -4509,10 +4509,10 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
         <v>25</v>
@@ -4524,7 +4524,7 @@
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>60</v>
@@ -4536,7 +4536,7 @@
         <v>900</v>
       </c>
       <c r="AK21" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR21" t="n">
         <v>9</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AS21" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>5.9</v>
       </c>
       <c r="AV21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE21" t="n">
         <v>6.2</v>
       </c>
-      <c r="AW21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE21" t="n">
+      <c r="BF21" t="n">
         <v>10</v>
       </c>
-      <c r="BF21" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG21" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4643,46 +4643,46 @@
         <v>2.36</v>
       </c>
       <c r="H22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.35</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
@@ -4694,113 +4694,113 @@
         <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AA22" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>100</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="n">
         <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
         <v>85</v>
       </c>
       <c r="AM22" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BF22" t="n">
         <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G23" t="n">
         <v>4.9</v>
@@ -4840,46 +4840,46 @@
         <v>1.76</v>
       </c>
       <c r="I23" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U23" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="V23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W23" t="n">
         <v>1.25</v>
@@ -4924,16 +4924,16 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO23" t="n">
         <v>7.4</v>
@@ -4948,10 +4948,10 @@
         <v>12</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="AU23" t="n">
         <v>9.199999999999999</v>
@@ -4963,10 +4963,10 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ23" t="n">
         <v>13.5</v>
@@ -4975,16 +4975,16 @@
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>8.199999999999999</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>3.1</v>
@@ -5034,55 +5034,55 @@
         <v>2.44</v>
       </c>
       <c r="I24" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V24" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W24" t="n">
         <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
         <v>18</v>
@@ -5100,10 +5100,10 @@
         <v>12</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
@@ -5130,7 +5130,7 @@
         <v>24</v>
       </c>
       <c r="AO24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP24" t="n">
         <v>18.5</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="AS24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
         <v>13</v>
@@ -5154,7 +5154,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
         <v>18.5</v>
@@ -5166,16 +5166,16 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BB24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
         <v>55</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="G25" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="O25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P25" t="n">
         <v>1.2</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q25" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>1.19</v>
       </c>
       <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU25" t="n">
         <v>1.69</v>
       </c>
-      <c r="U25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X25" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>260</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AV25" t="n">
-        <v>6.4</v>
+        <v>1.72</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.4</v>
+        <v>1.81</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>1.84</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.8</v>
+        <v>1.83</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>1.87</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.6</v>
+        <v>1.92</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.2</v>
+        <v>1.91</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G26" t="n">
         <v>2.86</v>
@@ -5422,22 +5422,22 @@
         <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J26" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="K26" t="n">
         <v>2.96</v>
       </c>
       <c r="L26" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O26" t="n">
         <v>1.6</v>
@@ -5446,22 +5446,22 @@
         <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R26" t="n">
         <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U26" t="n">
         <v>1.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
         <v>1.53</v>
@@ -5491,7 +5491,7 @@
         <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
@@ -5503,7 +5503,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AK26" t="n">
         <v>55</v>
@@ -5515,7 +5515,7 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO26" t="n">
         <v>500</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AX26" t="n">
         <v>14.5</v>
@@ -5557,16 +5557,16 @@
         <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
         <v>8</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -5607,55 +5607,55 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>3.15</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="J27" t="n">
         <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
         <v>2.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U27" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V27" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W27" t="n">
         <v>1.46</v>
@@ -5673,7 +5673,7 @@
         <v>42</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
         <v>8.6</v>
@@ -5685,7 +5685,7 @@
         <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>15.5</v>
@@ -5706,13 +5706,13 @@
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
         <v>36</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
@@ -5724,7 +5724,7 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT27" t="n">
         <v>9.800000000000001</v>
@@ -5748,29 +5748,29 @@
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>2.34</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H28" t="n">
         <v>3.8</v>
@@ -5813,34 +5813,34 @@
         <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K28" t="n">
         <v>3.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P28" t="n">
         <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R28" t="n">
         <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T28" t="n">
         <v>2</v>
@@ -5852,7 +5852,7 @@
         <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X28" t="n">
         <v>9.199999999999999</v>
@@ -5903,7 +5903,7 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
@@ -5918,16 +5918,16 @@
         <v>9</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW28" t="n">
         <v>8.800000000000001</v>
@@ -5939,13 +5939,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
         <v>9</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
         <v>16</v>
@@ -5960,11 +5960,11 @@
         <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M29" t="n">
         <v>1.02</v>
@@ -6025,16 +6025,16 @@
         <v>1.11</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S29" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="T29" t="n">
         <v>1.39</v>
@@ -6043,22 +6043,22 @@
         <v>3.05</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X29" t="n">
         <v>55</v>
       </c>
       <c r="Y29" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB29" t="n">
         <v>1000</v>
@@ -6070,7 +6070,7 @@
         <v>20</v>
       </c>
       <c r="AE29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -6082,7 +6082,7 @@
         <v>15.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ29" t="n">
         <v>42</v>
@@ -6097,25 +6097,25 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AU29" t="n">
         <v>10</v>
@@ -6124,10 +6124,10 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AX29" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>9.4</v>
@@ -6136,10 +6136,10 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,17 +6148,17 @@
         <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG29" t="n">
         <v>13</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -6189,79 +6189,79 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H30" t="n">
         <v>3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="S30" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T30" t="n">
         <v>1.52</v>
       </c>
       <c r="U30" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W30" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X30" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="n">
         <v>40</v>
       </c>
       <c r="Z30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AC30" t="n">
         <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6279,37 +6279,37 @@
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR30" t="n">
         <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
@@ -6318,10 +6318,10 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AY30" t="n">
         <v>9.800000000000001</v>
@@ -6330,19 +6330,19 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>19</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF30" t="n">
         <v>7.6</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -6383,46 +6383,46 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="G31" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H31" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R31" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S31" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T31" t="n">
         <v>1.56</v>
@@ -6431,7 +6431,7 @@
         <v>2.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="W31" t="n">
         <v>1.51</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
         <v>2.44</v>
       </c>
       <c r="H32" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J32" t="n">
         <v>3.2</v>
@@ -6595,28 +6595,28 @@
         <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.39</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T32" t="n">
         <v>1.86</v>
@@ -6625,7 +6625,7 @@
         <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
         <v>1.69</v>
@@ -6637,7 +6637,7 @@
         <v>12.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
@@ -6649,7 +6649,7 @@
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE32" t="n">
         <v>230</v>
@@ -6679,7 +6679,7 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="AT32" t="n">
         <v>6.6</v>
@@ -6706,7 +6706,7 @@
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6718,7 +6718,7 @@
         <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB32" t="n">
         <v>14.5</v>
@@ -6727,10 +6727,10 @@
         <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF32" t="n">
         <v>17.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="G33" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H33" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L33" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
@@ -6798,64 +6798,64 @@
         <v>3.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="U33" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
         <v>2.02</v>
       </c>
       <c r="X33" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE33" t="n">
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AG33" t="n">
         <v>20</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
@@ -6873,68 +6873,68 @@
         <v>580</v>
       </c>
       <c r="AN33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR33" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AS33" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT33" t="n">
         <v>7.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G34" t="n">
         <v>3.1</v>
@@ -6983,7 +6983,7 @@
         <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
@@ -7088,7 +7088,7 @@
         <v>6.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV34" t="n">
         <v>9.800000000000001</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="G35" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H35" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I35" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="J35" t="n">
         <v>3.05</v>
@@ -7177,7 +7177,7 @@
         <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
         <v>1.1</v>
@@ -7195,22 +7195,22 @@
         <v>2.28</v>
       </c>
       <c r="R35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V35" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W35" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X35" t="n">
         <v>10.5</v>
@@ -7222,7 +7222,7 @@
         <v>17.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AB35" t="n">
         <v>12.5</v>
@@ -7234,13 +7234,13 @@
         <v>14</v>
       </c>
       <c r="AE35" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF35" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH35" t="n">
         <v>23</v>
@@ -7249,13 +7249,13 @@
         <v>290</v>
       </c>
       <c r="AJ35" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK35" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AL35" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -7264,7 +7264,7 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
         <v>8</v>
@@ -7276,10 +7276,10 @@
         <v>13</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU35" t="n">
         <v>6.4</v>
@@ -7294,35 +7294,35 @@
         <v>17</v>
       </c>
       <c r="AY35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF35" t="n">
         <v>8.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G36" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
@@ -7377,76 +7377,76 @@
         <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O36" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P36" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T36" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U36" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W36" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y36" t="n">
         <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="AA36" t="n">
         <v>700</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AE36" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF36" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG36" t="n">
         <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI36" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL36" t="n">
         <v>85</v>
@@ -7455,31 +7455,31 @@
         <v>700</v>
       </c>
       <c r="AN36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO36" t="n">
         <v>700</v>
       </c>
       <c r="AP36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AR36" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AW36" t="n">
         <v>10</v>
@@ -7491,10 +7491,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB36" t="n">
         <v>12.5</v>
@@ -7503,20 +7503,20 @@
         <v>13.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF36" t="n">
         <v>8.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -7550,10 +7550,10 @@
         <v>3.05</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H37" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I37" t="n">
         <v>2.84</v>
@@ -7565,31 +7565,31 @@
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
         <v>1.44</v>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R37" t="n">
         <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T37" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
         <v>1.97</v>
@@ -7598,7 +7598,7 @@
         <v>1.54</v>
       </c>
       <c r="W37" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X37" t="n">
         <v>11</v>
@@ -7607,16 +7607,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AB37" t="n">
         <v>11</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AD37" t="n">
         <v>13</v>
@@ -7628,7 +7628,7 @@
         <v>22</v>
       </c>
       <c r="AG37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH37" t="n">
         <v>20</v>
@@ -7637,13 +7637,13 @@
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK37" t="n">
         <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7652,10 +7652,10 @@
         <v>55</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP37" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.8</v>
@@ -7664,53 +7664,53 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AT37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV37" t="n">
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX37" t="n">
         <v>17</v>
       </c>
       <c r="AY37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB37" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BE37" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.44</v>
       </c>
       <c r="G38" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H38" t="n">
         <v>3.4</v>
@@ -7759,13 +7759,13 @@
         <v>3.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>1.46</v>
@@ -7774,19 +7774,19 @@
         <v>1.67</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R38" t="n">
         <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T38" t="n">
         <v>1.99</v>
       </c>
       <c r="U38" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V38" t="n">
         <v>1.4</v>
@@ -7795,7 +7795,7 @@
         <v>1.67</v>
       </c>
       <c r="X38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y38" t="n">
         <v>11</v>
@@ -7822,7 +7822,7 @@
         <v>14</v>
       </c>
       <c r="AG38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
@@ -7837,19 +7837,19 @@
         <v>32</v>
       </c>
       <c r="AL38" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM38" t="n">
         <v>140</v>
       </c>
       <c r="AN38" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO38" t="n">
         <v>60</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
         <v>10</v>
@@ -7858,7 +7858,7 @@
         <v>20</v>
       </c>
       <c r="AS38" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AT38" t="n">
         <v>7.8</v>
@@ -7870,7 +7870,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AX38" t="n">
         <v>13</v>
@@ -7879,10 +7879,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA38" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="BB38" t="n">
         <v>30</v>
@@ -7894,17 +7894,17 @@
         <v>42</v>
       </c>
       <c r="BE38" t="n">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="BF38" t="n">
         <v>26</v>
       </c>
       <c r="BG38" t="n">
-        <v>17.5</v>
+        <v>50</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>3.8</v>
       </c>
       <c r="G39" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H39" t="n">
         <v>2.14</v>
@@ -7953,34 +7953,34 @@
         <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
         <v>1.25</v>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S39" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="T39" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U39" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
         <v>1.82</v>
@@ -8004,10 +8004,10 @@
         <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE39" t="n">
         <v>65</v>
@@ -8019,7 +8019,7 @@
         <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
@@ -8034,71 +8034,71 @@
         <v>500</v>
       </c>
       <c r="AM39" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN39" t="n">
         <v>500</v>
       </c>
       <c r="AO39" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AP39" t="n">
         <v>9</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AR39" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT39" t="n">
         <v>14.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW39" t="n">
         <v>10.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY39" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA39" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB39" t="n">
         <v>11</v>
       </c>
       <c r="BC39" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE39" t="n">
         <v>17.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>24</v>
+        <v>5.1</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G40" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2.42</v>
       </c>
       <c r="H40" t="n">
         <v>3.6</v>
@@ -8162,7 +8162,7 @@
         <v>1.76</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8171,19 +8171,19 @@
         <v>4.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U40" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V40" t="n">
         <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y40" t="n">
         <v>12</v>
@@ -8216,7 +8216,7 @@
         <v>18</v>
       </c>
       <c r="AI40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ40" t="n">
         <v>32</v>
@@ -8225,13 +8225,13 @@
         <v>29</v>
       </c>
       <c r="AL40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM40" t="n">
         <v>120</v>
       </c>
       <c r="AN40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO40" t="n">
         <v>55</v>
@@ -8279,20 +8279,20 @@
         <v>25</v>
       </c>
       <c r="BD40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE40" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="BF40" t="n">
         <v>23</v>
       </c>
       <c r="BG40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G41" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
         <v>3.05</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.63</v>
@@ -8347,34 +8347,34 @@
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O41" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P41" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S41" t="n">
         <v>6.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U41" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W41" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X41" t="n">
         <v>8</v>
@@ -8383,37 +8383,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE41" t="n">
         <v>60</v>
       </c>
-      <c r="AB41" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>15</v>
       </c>
-      <c r="AE41" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>16</v>
-      </c>
       <c r="AG41" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH41" t="n">
         <v>25</v>
       </c>
       <c r="AI41" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK41" t="n">
         <v>44</v>
@@ -8422,13 +8422,13 @@
         <v>75</v>
       </c>
       <c r="AM41" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN41" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO41" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP41" t="n">
         <v>7.6</v>
@@ -8437,56 +8437,56 @@
         <v>8.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU41" t="n">
         <v>6.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW41" t="n">
         <v>44</v>
       </c>
       <c r="AX41" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ41" t="n">
         <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD41" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE41" t="n">
         <v>70</v>
       </c>
       <c r="BF41" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BG41" t="n">
         <v>60</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.6</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.61</v>
       </c>
       <c r="H42" t="n">
         <v>6.4</v>
@@ -8541,34 +8541,34 @@
         <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O42" t="n">
         <v>1.24</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q42" t="n">
         <v>1.74</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S42" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T42" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W42" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X42" t="n">
         <v>19</v>
@@ -8580,13 +8580,13 @@
         <v>50</v>
       </c>
       <c r="AA42" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD42" t="n">
         <v>23</v>
@@ -8595,7 +8595,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG42" t="n">
         <v>9.6</v>
@@ -8604,7 +8604,7 @@
         <v>19.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ42" t="n">
         <v>14.5</v>
@@ -8622,7 +8622,7 @@
         <v>7.6</v>
       </c>
       <c r="AO42" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP42" t="n">
         <v>18.5</v>
@@ -8637,7 +8637,7 @@
         <v>140</v>
       </c>
       <c r="AT42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU42" t="n">
         <v>9.6</v>
@@ -8649,7 +8649,7 @@
         <v>70</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY42" t="n">
         <v>9.199999999999999</v>
@@ -8658,13 +8658,13 @@
         <v>19</v>
       </c>
       <c r="BA42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB42" t="n">
         <v>14</v>
       </c>
       <c r="BC42" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD42" t="n">
         <v>28</v>
@@ -8673,14 +8673,14 @@
         <v>90</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG42" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G43" t="n">
         <v>4.7</v>
@@ -8720,31 +8720,31 @@
         <v>2.06</v>
       </c>
       <c r="I43" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J43" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K43" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L43" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N43" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O43" t="n">
         <v>1.45</v>
       </c>
       <c r="P43" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -8759,122 +8759,122 @@
         <v>1.86</v>
       </c>
       <c r="V43" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="W43" t="n">
         <v>1.27</v>
       </c>
       <c r="X43" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y43" t="n">
         <v>7.4</v>
       </c>
       <c r="Z43" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA43" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AB43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE43" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AF43" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="AG43" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AI43" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AJ43" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AK43" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AL43" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AM43" t="n">
         <v>580</v>
       </c>
       <c r="AN43" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AO43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP43" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ43" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR43" t="n">
         <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AT43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV43" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW43" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AX43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA43" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BB43" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BC43" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BD43" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BE43" t="n">
         <v>36</v>
       </c>
       <c r="BF43" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BG43" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -8908,40 +8908,40 @@
         <v>3.05</v>
       </c>
       <c r="G44" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K44" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M44" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O44" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P44" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="R44" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S44" t="n">
         <v>6.2</v>
@@ -8953,7 +8953,7 @@
         <v>1.72</v>
       </c>
       <c r="V44" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W44" t="n">
         <v>1.47</v>
@@ -8962,58 +8962,58 @@
         <v>8</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC44" t="n">
         <v>6.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG44" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ44" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AL44" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AM44" t="n">
         <v>500</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>7.4</v>
@@ -9028,7 +9028,7 @@
         <v>7.2</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV44" t="n">
         <v>12</v>
@@ -9043,13 +9043,13 @@
         <v>12</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA44" t="n">
         <v>50</v>
       </c>
       <c r="BB44" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC44" t="n">
         <v>27</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>2.54</v>
       </c>
       <c r="G45" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H45" t="n">
         <v>3.45</v>
@@ -9114,34 +9114,34 @@
         <v>2.96</v>
       </c>
       <c r="K45" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M45" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O45" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="P45" t="n">
         <v>1.47</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
         <v>1.16</v>
       </c>
       <c r="S45" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
         <v>1.71</v>
@@ -9150,52 +9150,52 @@
         <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X45" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA45" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB45" t="n">
         <v>7.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD45" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE45" t="n">
         <v>65</v>
       </c>
       <c r="AF45" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI45" t="n">
         <v>120</v>
       </c>
       <c r="AJ45" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AK45" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL45" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM45" t="n">
         <v>500</v>
@@ -9204,7 +9204,7 @@
         <v>60</v>
       </c>
       <c r="AO45" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP45" t="n">
         <v>7</v>
@@ -9213,10 +9213,10 @@
         <v>8</v>
       </c>
       <c r="AR45" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -9228,41 +9228,41 @@
         <v>14.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AX45" t="n">
         <v>13</v>
       </c>
       <c r="AY45" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ45" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BA45" t="n">
-        <v>6.8</v>
+        <v>80</v>
       </c>
       <c r="BB45" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BC45" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD45" t="n">
-        <v>6.6</v>
+        <v>65</v>
       </c>
       <c r="BE45" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="BF45" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BG45" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -9293,46 +9293,46 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G46" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L46" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M46" t="n">
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="O46" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P46" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S46" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
@@ -9341,16 +9341,16 @@
         <v>1.82</v>
       </c>
       <c r="V46" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W46" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X46" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z46" t="n">
         <v>32</v>
@@ -9362,28 +9362,28 @@
         <v>7.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE46" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AF46" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI46" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AJ46" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK46" t="n">
         <v>28</v>
@@ -9398,7 +9398,7 @@
         <v>27</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP46" t="n">
         <v>7.8</v>
@@ -9410,10 +9410,10 @@
         <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT46" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU46" t="n">
         <v>6.4</v>
@@ -9422,7 +9422,7 @@
         <v>13.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AX46" t="n">
         <v>9.4</v>
@@ -9434,7 +9434,7 @@
         <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BB46" t="n">
         <v>21</v>
@@ -9443,20 +9443,20 @@
         <v>21</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF46" t="n">
         <v>18.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="G47" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="n">
         <v>4.7</v>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J47" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K47" t="n">
         <v>3.65</v>
       </c>
       <c r="L47" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M47" t="n">
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="O47" t="n">
         <v>1.45</v>
       </c>
       <c r="P47" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R47" t="n">
         <v>1.23</v>
       </c>
       <c r="S47" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T47" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U47" t="n">
         <v>1.79</v>
       </c>
       <c r="V47" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X47" t="n">
         <v>17</v>
@@ -9547,7 +9547,7 @@
         <v>29</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA47" t="n">
         <v>1000</v>
@@ -9589,7 +9589,7 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
@@ -9601,22 +9601,22 @@
         <v>7</v>
       </c>
       <c r="AR47" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="AT47" t="n">
         <v>6</v>
       </c>
       <c r="AU47" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV47" t="n">
         <v>11.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX47" t="n">
         <v>8.6</v>
@@ -9637,20 +9637,20 @@
         <v>13</v>
       </c>
       <c r="BD47" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF47" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG47" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -9681,49 +9681,49 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J48" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K48" t="n">
         <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M48" t="n">
         <v>1.12</v>
       </c>
       <c r="N48" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O48" t="n">
         <v>1.54</v>
       </c>
       <c r="P48" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R48" t="n">
         <v>1.2</v>
       </c>
       <c r="S48" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="T48" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U48" t="n">
         <v>1.72</v>
@@ -9732,7 +9732,7 @@
         <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X48" t="n">
         <v>9.4</v>
@@ -9810,7 +9810,7 @@
         <v>18</v>
       </c>
       <c r="AW48" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AX48" t="n">
         <v>8.800000000000001</v>
@@ -9834,7 +9834,7 @@
         <v>46</v>
       </c>
       <c r="BE48" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BF48" t="n">
         <v>17.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G49" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H49" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I49" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K49" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
         <v>1.49</v>
@@ -9899,34 +9899,34 @@
         <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O49" t="n">
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S49" t="n">
         <v>4.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U49" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V49" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W49" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X49" t="n">
         <v>13.5</v>
@@ -9944,19 +9944,19 @@
         <v>7.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE49" t="n">
         <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG49" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH49" t="n">
         <v>1000</v>
@@ -9968,7 +9968,7 @@
         <v>20</v>
       </c>
       <c r="AK49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL49" t="n">
         <v>1000</v>
@@ -9986,13 +9986,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ49" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT49" t="n">
         <v>5.8</v>
@@ -10001,10 +10001,10 @@
         <v>7.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX49" t="n">
         <v>6.4</v>
@@ -10016,29 +10016,29 @@
         <v>19.5</v>
       </c>
       <c r="BA49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC49" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>15</v>
-      </c>
       <c r="BD49" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF49" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -10069,46 +10069,46 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="H50" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N50" t="n">
-        <v>1.25</v>
+        <v>2.76</v>
       </c>
       <c r="O50" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P50" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R50" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S50" t="n">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -10117,10 +10117,10 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W50" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -10263,58 +10263,58 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="G51" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H51" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="K51" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="O51" t="n">
         <v>1.26</v>
       </c>
       <c r="P51" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="R51" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S51" t="n">
-        <v>2.66</v>
+        <v>1.82</v>
       </c>
       <c r="T51" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U51" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10344,7 +10344,7 @@
         <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
         <v>1000</v>
@@ -10365,68 +10365,68 @@
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.9</v>
+        <v>1.23</v>
       </c>
       <c r="AR51" t="n">
-        <v>7.2</v>
+        <v>1.26</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.55</v>
+        <v>1.3</v>
       </c>
       <c r="AT51" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="BB51" t="n">
-        <v>5</v>
+        <v>1.23</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.9</v>
+        <v>1.22</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="BE51" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="BG51" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -10457,58 +10457,58 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G52" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H52" t="n">
         <v>3.6</v>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K52" t="n">
         <v>3.5</v>
       </c>
       <c r="L52" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O52" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P52" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R52" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T52" t="n">
         <v>1.86</v>
       </c>
       <c r="U52" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V52" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X52" t="n">
         <v>13.5</v>
@@ -10520,7 +10520,7 @@
         <v>32</v>
       </c>
       <c r="AA52" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB52" t="n">
         <v>10.5</v>
@@ -10571,13 +10571,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR52" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS52" t="n">
         <v>4.1</v>
       </c>
       <c r="AT52" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU52" t="n">
         <v>5.7</v>
@@ -10586,7 +10586,7 @@
         <v>11.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX52" t="n">
         <v>10</v>
@@ -10598,7 +10598,7 @@
         <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB52" t="n">
         <v>3.9</v>
@@ -10610,17 +10610,17 @@
         <v>4</v>
       </c>
       <c r="BE52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG52" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF52" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>4</v>
-      </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>1.53</v>
       </c>
       <c r="G53" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H53" t="n">
         <v>8.800000000000001</v>
@@ -10663,34 +10663,34 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
         <v>4.2</v>
       </c>
       <c r="L53" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M53" t="n">
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O53" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P53" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R53" t="n">
         <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T53" t="n">
         <v>2.56</v>
@@ -10702,7 +10702,7 @@
         <v>1.11</v>
       </c>
       <c r="W53" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X53" t="n">
         <v>10</v>
@@ -10711,7 +10711,7 @@
         <v>21</v>
       </c>
       <c r="Z53" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA53" t="n">
         <v>1000</v>
@@ -10735,10 +10735,10 @@
         <v>12</v>
       </c>
       <c r="AH53" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI53" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ53" t="n">
         <v>14.5</v>
@@ -10747,7 +10747,7 @@
         <v>24</v>
       </c>
       <c r="AL53" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM53" t="n">
         <v>410</v>
@@ -10759,16 +10759,16 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ53" t="n">
         <v>17</v>
       </c>
       <c r="AR53" t="n">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="AS53" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT53" t="n">
         <v>4.9</v>
@@ -10780,7 +10780,7 @@
         <v>30</v>
       </c>
       <c r="AW53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX53" t="n">
         <v>6.2</v>
@@ -10789,10 +10789,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ53" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BA53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB53" t="n">
         <v>11.5</v>
@@ -10801,20 +10801,20 @@
         <v>19</v>
       </c>
       <c r="BD53" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE53" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF53" t="n">
         <v>11</v>
       </c>
       <c r="BG53" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -11039,58 +11039,58 @@
         </is>
       </c>
       <c r="F55" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G55" t="n">
         <v>3.2</v>
       </c>
-      <c r="G55" t="n">
-        <v>4.2</v>
-      </c>
       <c r="H55" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="J55" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K55" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M55" t="n">
         <v>1.09</v>
       </c>
       <c r="N55" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O55" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R55" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S55" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T55" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U55" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V55" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W55" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="X55" t="n">
         <v>13.5</v>
@@ -11099,7 +11099,7 @@
         <v>10.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA55" t="n">
         <v>1000</v>
@@ -11108,7 +11108,7 @@
         <v>1000</v>
       </c>
       <c r="AC55" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD55" t="n">
         <v>1000</v>
@@ -11150,59 +11150,59 @@
         <v>8</v>
       </c>
       <c r="AQ55" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW55" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR55" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>4</v>
-      </c>
       <c r="AX55" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AY55" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BA55" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG55" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-13.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.63</v>
@@ -787,10 +787,10 @@
         <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -799,49 +799,49 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V2" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
         <v>130</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
@@ -856,28 +856,28 @@
         <v>700</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>700</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>6.6</v>
@@ -886,25 +886,25 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>18</v>
       </c>
-      <c r="AY2" t="n">
-        <v>20</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
         <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
         <v>12</v>
@@ -913,14 +913,14 @@
         <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -981,10 +981,10 @@
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -993,128 +993,128 @@
         <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="n">
         <v>26</v>
       </c>
-      <c r="AF3" t="n">
-        <v>25</v>
-      </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
         <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
         <v>75</v>
       </c>
       <c r="AK3" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AM3" t="n">
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
         <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L4" t="n">
         <v>1.57</v>
@@ -1169,7 +1169,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
         <v>1.48</v>
@@ -1184,13 +1184,13 @@
         <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
@@ -1199,116 +1199,116 @@
         <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
         <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
         <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BB4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC4" t="n">
         <v>32</v>
       </c>
-      <c r="BC4" t="n">
-        <v>30</v>
-      </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BE4" t="n">
         <v>26</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BG4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
         <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
         <v>40</v>
@@ -1405,104 +1405,104 @@
         <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>17.5</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AR5" t="n">
         <v>29</v>
       </c>
-      <c r="AM5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN5" t="n">
+      <c r="AS5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT5" t="n">
         <v>9.4</v>
       </c>
-      <c r="AO5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10</v>
-      </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
         <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1533,79 +1533,79 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.8</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.15</v>
-      </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="K6" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="L6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
         <v>1.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.79</v>
       </c>
       <c r="P6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
         <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
         <v>6.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1617,25 +1617,25 @@
         <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,37 +1644,37 @@
         <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
@@ -1683,20 +1683,20 @@
         <v>17.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE6" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H7" t="n">
         <v>11.5</v>
       </c>
       <c r="I7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
         <v>1.08</v>
@@ -1781,19 +1781,19 @@
         <v>4.3</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA7" t="n">
-        <v>580</v>
+        <v>720</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>42</v>
@@ -1802,37 +1802,37 @@
         <v>46</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
         <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AP7" t="n">
         <v>21</v>
@@ -1841,56 +1841,56 @@
         <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>13.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1933,10 +1933,10 @@
         <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="L8" t="n">
         <v>1.66</v>
@@ -1948,25 +1948,25 @@
         <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
         <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
         <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
@@ -1978,25 +1978,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
         <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>440</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
@@ -2005,13 +2005,13 @@
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>450</v>
       </c>
       <c r="AJ8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
         <v>42</v>
@@ -2023,7 +2023,7 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO8" t="n">
         <v>600</v>
@@ -2038,19 +2038,19 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>50</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2059,19 +2059,19 @@
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB8" t="n">
         <v>28</v>
       </c>
       <c r="BC8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
         <v>6.2</v>
@@ -2080,11 +2080,11 @@
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -2124,13 +2124,13 @@
         <v>2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L9" t="n">
         <v>1.74</v>
@@ -2154,16 +2154,16 @@
         <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T9" t="n">
         <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
@@ -2202,7 +2202,7 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AJ9" t="n">
         <v>500</v>
@@ -2247,7 +2247,7 @@
         <v>30</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
         <v>19</v>
@@ -2259,26 +2259,26 @@
         <v>9.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BE9" t="n">
         <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BG9" t="n">
         <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
@@ -2369,7 +2369,7 @@
         <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2384,13 +2384,13 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
         <v>25</v>
@@ -2411,10 +2411,10 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AP10" t="n">
         <v>9</v>
@@ -2423,34 +2423,34 @@
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
         <v>16.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2462,17 +2462,17 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
         <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>3.8</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
@@ -2530,13 +2530,13 @@
         <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
         <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
@@ -2545,58 +2545,58 @@
         <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W11" t="n">
         <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2614,22 +2614,22 @@
         <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2638,16 +2638,16 @@
         <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>12.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC11" t="n">
         <v>8.800000000000001</v>
@@ -2659,14 +2659,14 @@
         <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2721,10 +2721,10 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="P12" t="n">
         <v>1.46</v>
@@ -2733,10 +2733,10 @@
         <v>1.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,7 +2745,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
         <v>1.73</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.6</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
         <v>1.74</v>
@@ -2927,22 +2927,22 @@
         <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
         <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2954,41 +2954,41 @@
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
         <v>14</v>
       </c>
       <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
         <v>500</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
       </c>
       <c r="AG13" t="n">
         <v>500</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
+        <v>320</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>250</v>
+      </c>
+      <c r="AL13" t="n">
         <v>500</v>
       </c>
-      <c r="AK13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>340</v>
-      </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
@@ -2999,31 +2999,31 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR13" t="n">
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
@@ -3032,29 +3032,29 @@
         <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.76</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BG13" t="n">
         <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.51</v>
       </c>
       <c r="H14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="n">
         <v>8.6</v>
@@ -3112,13 +3112,13 @@
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
         <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R14" t="n">
         <v>1.54</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
@@ -3294,7 +3294,7 @@
         <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.34</v>
@@ -3303,43 +3303,43 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
         <v>110</v>
@@ -3351,16 +3351,16 @@
         <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
@@ -3378,19 +3378,19 @@
         <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO15" t="n">
         <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR15" t="n">
         <v>34</v>
@@ -3402,13 +3402,13 @@
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,29 @@
         <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG15" t="n">
         <v>38</v>
       </c>
-      <c r="BF15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G16" t="n">
         <v>4.8</v>
       </c>
-      <c r="G16" t="n">
-        <v>4.9</v>
-      </c>
       <c r="H16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3506,7 +3506,7 @@
         <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -3515,43 +3515,43 @@
         <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
         <v>21</v>
       </c>
-      <c r="AB16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>20</v>
-      </c>
       <c r="AF16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG16" t="n">
         <v>18</v>
@@ -3560,28 +3560,28 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO16" t="n">
         <v>13.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.199999999999999</v>
@@ -3590,53 +3590,53 @@
         <v>10.5</v>
       </c>
       <c r="AS16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AT16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB16" t="n">
         <v>17</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>42</v>
       </c>
       <c r="BC16" t="n">
         <v>42</v>
       </c>
       <c r="BD16" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BE16" t="n">
         <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="BG16" t="n">
         <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G17" t="n">
         <v>1.34</v>
@@ -3676,10 +3676,10 @@
         <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K17" t="n">
         <v>6.4</v>
@@ -3691,28 +3691,28 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
         <v>1.08</v>
@@ -3775,28 +3775,28 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS17" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
         <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
         <v>30</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX17" t="n">
         <v>5</v>
@@ -3808,29 +3808,29 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
         <v>9.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>3.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="G18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H18" t="n">
         <v>1.54</v>
@@ -3894,10 +3894,10 @@
         <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
         <v>2.92</v>
@@ -3909,7 +3909,7 @@
         <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W18" t="n">
         <v>1.15</v>
@@ -3939,7 +3939,7 @@
         <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
@@ -3957,7 +3957,7 @@
         <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -4005,7 +4005,7 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BC18" t="n">
         <v>9.800000000000001</v>
@@ -4014,7 +4014,7 @@
         <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>3.95</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
@@ -4067,19 +4067,19 @@
         <v>2.04</v>
       </c>
       <c r="J19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.95</v>
       </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.25</v>
@@ -4091,7 +4091,7 @@
         <v>1.79</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -4103,19 +4103,19 @@
         <v>2.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
         <v>23</v>
@@ -4133,10 +4133,10 @@
         <v>19.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
         <v>17</v>
@@ -4148,7 +4148,7 @@
         <v>75</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
         <v>46</v>
@@ -4175,10 +4175,10 @@
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -4193,32 +4193,32 @@
         <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
         <v>26</v>
       </c>
       <c r="BB19" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BC19" t="n">
         <v>36</v>
       </c>
       <c r="BD19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
         <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG19" t="n">
         <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
         <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
@@ -4264,67 +4264,67 @@
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V20" t="n">
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
         <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF20" t="n">
         <v>18</v>
@@ -4333,10 +4333,10 @@
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="n">
         <v>36</v>
@@ -4345,74 +4345,74 @@
         <v>24</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
         <v>65</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
         <v>19.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
         <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BD20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE20" t="n">
         <v>30</v>
       </c>
       <c r="BF20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>2.54</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.5</v>
@@ -4473,7 +4473,7 @@
         <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
         <v>2.28</v>
@@ -4557,10 +4557,10 @@
         <v>9.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT21" t="n">
         <v>8</v>
@@ -4572,31 +4572,31 @@
         <v>12</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
         <v>13.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF21" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
         <v>3.45</v>
@@ -4652,10 +4652,10 @@
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -4667,13 +4667,13 @@
         <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
         <v>3.35</v>
@@ -4682,22 +4682,22 @@
         <v>1.74</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c